--- a/output/competitor_analysis.xlsx
+++ b/output/competitor_analysis.xlsx
@@ -1103,12 +1103,17 @@
       <c r="F6" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr"/>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Кэшбэк (ставка, категории, механика) — основное: Кэшбэк 1–15% рублями в 3 категориях (4 для зарплатных клиентов) на выбор из 9; п | Bankiros.ru: Карта с беспроцентным периодом до 110 дней и повышенным кешбэком | Как перевести
+Спецусловия по вкладам / накопительным счетам — основное: Накопительный ВТБ-Счёт до 13,75% годовых (повышенная ставка за покупки по карте) | Bankiros.ru: Более 1500 вкладов в 357 банках России | Выгодные вклады | Накопительные счета</t>
+        </is>
+      </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
           <t>ВТБ – Привилегия — Уровень за 3990 ₽ в мес или траты 150 тыс ₽ или 300 тыс зп или 9000 акций (≈639,000₽) ; ВТБ Привилегия | Системно значимый банк
@@ -1143,7 +1148,7 @@
         <is>
           <t>Кэшбэк 1–15% рублями в 3 категориях (4 для зарплатных клиентов) на выбор из 9; по отдельным категориям лимиты (например, «Такси» — до 1 000 ₽/мес)
 [источник: Ручная проверка (первоисточник), проверено: 2026-07-02]
-[прим.: Начисляется рублями, не мультибонусами]</t>
+[прим.: Начисляется рублями, не мультибонусами; числа расходятся с Bankiros.ru]</t>
         </is>
       </c>
       <c r="O6" s="4" t="inlineStr">
@@ -1155,7 +1160,8 @@
       <c r="P6" s="4" t="inlineStr">
         <is>
           <t>Накопительный ВТБ-Счёт до 13,75% годовых (повышенная ставка за покупки по карте); опция «Сбережения»: надбавка +1–3 п.п. к ставке в зависимости от оборота по карте. Ставки на дату проверки
-[источник: Ручная проверка (первоисточник), проверено: 2026-07-02]</t>
+[источник: Ручная проверка (первоисточник), проверено: 2026-07-02]
+[прим.: числа расходятся с Bankiros.ru]</t>
         </is>
       </c>
       <c r="Q6" s="4" t="inlineStr">
@@ -1200,9 +1206,10 @@
           <t>не найдено</t>
         </is>
       </c>
-      <c r="X6" s="7" t="inlineStr">
-        <is>
-          <t>не найдено</t>
+      <c r="X6" s="4" t="inlineStr">
+        <is>
+          <t>Обновлено 02.07
+[источник: Bankiros.ru, проверено: 2026-07-02]</t>
         </is>
       </c>
     </row>
@@ -1229,12 +1236,17 @@
       <c r="F7" s="4" t="n">
         <v>3.4</v>
       </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr"/>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>Кэшбэк (ставка, категории, механика) — основное: Кэшбэк 1–15% рублями в 3 категориях (4 для зарплатных клиентов) на выбор из 9; п | Bankiros.ru: Карта с беспроцентным периодом до 110 дней и повышенным кешбэком | Как перевести
+Спецусловия по вкладам / накопительным счетам — основное: Накопительный ВТБ-Счёт до 13,75% годовых (повышенная ставка за покупки по карте) | Bankiros.ru: Более 1500 вкладов в 357 банках России | Выгодные вклады | Накопительные счета</t>
+        </is>
+      </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
           <t>ВТБ – Привилегия — Уровень за 2.5 млн ₽ для Мск | 2 млн ₽ регионы или 1.5 млн ₽ + траты 125 тыс ₽ ; ВТБ Привилегия | Системно значимый банк
@@ -1270,7 +1282,7 @@
         <is>
           <t>Кэшбэк 1–15% рублями в 3 категориях (4 для зарплатных клиентов) на выбор из 9; по отдельным категориям лимиты (например, «Такси» — до 1 000 ₽/мес)
 [источник: Ручная проверка (первоисточник), проверено: 2026-07-02]
-[прим.: Начисляется рублями, не мультибонусами]</t>
+[прим.: Начисляется рублями, не мультибонусами; числа расходятся с Bankiros.ru]</t>
         </is>
       </c>
       <c r="O7" s="4" t="inlineStr">
@@ -1282,7 +1294,8 @@
       <c r="P7" s="4" t="inlineStr">
         <is>
           <t>Накопительный ВТБ-Счёт до 13,75% годовых (повышенная ставка за покупки по карте); опция «Сбережения»: надбавка +1–3 п.п. к ставке в зависимости от оборота по карте. Ставки на дату проверки
-[источник: Ручная проверка (первоисточник), проверено: 2026-07-02]</t>
+[источник: Ручная проверка (первоисточник), проверено: 2026-07-02]
+[прим.: числа расходятся с Bankiros.ru]</t>
         </is>
       </c>
       <c r="Q7" s="4" t="inlineStr">
@@ -1327,9 +1340,10 @@
 [источник: premiumbanking.info, проверено: 2026-07-02]</t>
         </is>
       </c>
-      <c r="X7" s="7" t="inlineStr">
-        <is>
-          <t>не найдено</t>
+      <c r="X7" s="4" t="inlineStr">
+        <is>
+          <t>Обновлено 02.07
+[источник: Bankiros.ru, проверено: 2026-07-02]</t>
         </is>
       </c>
     </row>
@@ -2815,12 +2829,17 @@
       <c r="F20" s="4" t="n">
         <v>3.7</v>
       </c>
-      <c r="G20" s="4" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="inlineStr"/>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>Кэшбэк (ставка, категории, механика) — основное: Кэшбэк 1–15% рублями в 3 категориях (4 для зарплатных клиентов) на выбор из 9; п | Bankiros.ru: Карта с беспроцентным периодом до 110 дней и повышенным кешбэком | Как перевести
+Спецусловия по вкладам / накопительным счетам — основное: Накопительный ВТБ-Счёт до 13,75% годовых (повышенная ставка за покупки по карте) | Bankiros.ru: Более 1500 вкладов в 357 банках России | Выгодные вклады | Накопительные счета</t>
+        </is>
+      </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
           <t>ВТБ – Привилегия — Уровень за 6 млн ₽ ; ВТБ Привилегия | Системно значимый банк
@@ -2856,7 +2875,7 @@
         <is>
           <t>Кэшбэк 1–15% рублями в 3 категориях (4 для зарплатных клиентов) на выбор из 9; по отдельным категориям лимиты (например, «Такси» — до 1 000 ₽/мес)
 [источник: Ручная проверка (первоисточник), проверено: 2026-07-02]
-[прим.: Начисляется рублями, не мультибонусами]</t>
+[прим.: Начисляется рублями, не мультибонусами; числа расходятся с Bankiros.ru]</t>
         </is>
       </c>
       <c r="O20" s="4" t="inlineStr">
@@ -2868,7 +2887,8 @@
       <c r="P20" s="4" t="inlineStr">
         <is>
           <t>Накопительный ВТБ-Счёт до 13,75% годовых (повышенная ставка за покупки по карте); опция «Сбережения»: надбавка +1–3 п.п. к ставке в зависимости от оборота по карте. Ставки на дату проверки
-[источник: Ручная проверка (первоисточник), проверено: 2026-07-02]</t>
+[источник: Ручная проверка (первоисточник), проверено: 2026-07-02]
+[прим.: числа расходятся с Bankiros.ru]</t>
         </is>
       </c>
       <c r="Q20" s="4" t="inlineStr">
@@ -2913,9 +2933,10 @@
 [источник: premiumbanking.info, проверено: 2026-07-02]</t>
         </is>
       </c>
-      <c r="X20" s="7" t="inlineStr">
-        <is>
-          <t>не найдено</t>
+      <c r="X20" s="4" t="inlineStr">
+        <is>
+          <t>Обновлено 02.07
+[источник: Bankiros.ru, проверено: 2026-07-02]</t>
         </is>
       </c>
     </row>
@@ -2940,7 +2961,7 @@
         <v>3</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
@@ -2949,7 +2970,7 @@
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>Позиционирование (на кого рассчитан) — основное: ВТБ – Прайм+ — Уровень за 16667 ₽ в мес или 90000 акций (≈6,390,000₽) ; ВТБ Прай | Официальный сайт банка: Private Banking ÐÐ¢Ð â Ð¸Ð½Ð´Ð¸Ð²Ð¸Ð´ÑÐ°Ð»ÑÐ½Ð¾Ðµ Ð±Ð°Ð½ÐºÐ¾Ð²ÑÐºÐ¾Ðµ Ð¾Ð</t>
+          <t>Позиционирование (на кого рассчитан) — основное: ВТБ – Прайм+ — Уровень за 16667 ₽ в мес или 90000 акций (≈6,390,000₽) ; ВТБ Прай | Официальный сайт банка: Private Banking ÐÐ¢Ð â Ð¸Ð½Ð´Ð¸Ð²Ð¸Ð´ÑÐ°Ð»ÑÐ½Ð¾Ðµ Ð±Ð°Ð½ÐºÐ¾Ð²ÑÐºÐ¾Ðµ Ð¾Ð; Bankiros.ru: АО «ААА Управление Капиталом» | ООО УК «Альфа-Капитал» | Уставный капитал:</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
@@ -2983,19 +3004,22 @@
 [источник: premiumbanking.info, проверено: 2026-07-02]</t>
         </is>
       </c>
-      <c r="N21" s="7" t="inlineStr">
-        <is>
-          <t>не найдено</t>
-        </is>
-      </c>
-      <c r="O21" s="7" t="inlineStr">
-        <is>
-          <t>не найдено</t>
-        </is>
-      </c>
-      <c r="P21" s="7" t="inlineStr">
-        <is>
-          <t>не найдено</t>
+      <c r="N21" s="4" t="inlineStr">
+        <is>
+          <t>Карта с беспроцентным периодом до 110 дней и повышенным кешбэком | Как перевести Мультибонусы втб на карту? | Личный кабинет Мультибонус ВТБ
+[источник: Bankiros.ru, проверено: 2026-07-02]</t>
+        </is>
+      </c>
+      <c r="O21" s="4" t="inlineStr">
+        <is>
+          <t>Банки-партнеры ВТБ: где снять наличные без комиссии | Снятие наличных в банкомате без карты
+[источник: Bankiros.ru, проверено: 2026-07-02]</t>
+        </is>
+      </c>
+      <c r="P21" s="4" t="inlineStr">
+        <is>
+          <t>Более 1500 вкладов в 357 банках России | Выгодные вклады | Накопительные счета
+[источник: Bankiros.ru, проверено: 2026-07-02]</t>
         </is>
       </c>
       <c r="Q21" s="4" t="inlineStr">
@@ -3004,9 +3028,10 @@
 [источник: premiumbanking.info, проверено: 2026-07-02]</t>
         </is>
       </c>
-      <c r="R21" s="7" t="inlineStr">
-        <is>
-          <t>не найдено</t>
+      <c r="R21" s="4" t="inlineStr">
+        <is>
+          <t>Онлайн-заявка на автокредит | Выгодные автокредиты | Легковые автомобили
+[источник: Bankiros.ru, проверено: 2026-07-02]</t>
         </is>
       </c>
       <c r="S21" s="4" t="inlineStr">
@@ -3039,9 +3064,10 @@
 [источник: premiumbanking.info, проверено: 2026-07-02]</t>
         </is>
       </c>
-      <c r="X21" s="7" t="inlineStr">
-        <is>
-          <t>не найдено</t>
+      <c r="X21" s="4" t="inlineStr">
+        <is>
+          <t>Обновлено 02.07
+[источник: Bankiros.ru, проверено: 2026-07-02]</t>
         </is>
       </c>
     </row>
@@ -3880,12 +3906,17 @@
       <c r="F29" s="4" t="n">
         <v>3.9</v>
       </c>
-      <c r="G29" s="4" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="H29" s="4" t="inlineStr"/>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>Кэшбэк (ставка, категории, механика) — основное: Кэшбэк 1–15% рублями в 3 категориях (4 для зарплатных клиентов) на выбор из 9; п | Bankiros.ru: Карта с беспроцентным периодом до 110 дней и повышенным кешбэком | Как перевести
+Спецусловия по вкладам / накопительным счетам — основное: Накопительный ВТБ-Счёт до 13,75% годовых (повышенная ставка за покупки по карте) | Bankiros.ru: Более 1500 вкладов в 357 банках России | Выгодные вклады | Накопительные счета</t>
+        </is>
+      </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
           <t>ВТБ – Привилегия — Уровень за 10 млн ₽ ; ВТБ Привилегия | Системно значимый банк
@@ -3921,7 +3952,7 @@
         <is>
           <t>Кэшбэк 1–15% рублями в 3 категориях (4 для зарплатных клиентов) на выбор из 9; по отдельным категориям лимиты (например, «Такси» — до 1 000 ₽/мес)
 [источник: Ручная проверка (первоисточник), проверено: 2026-07-02]
-[прим.: Начисляется рублями, не мультибонусами]</t>
+[прим.: Начисляется рублями, не мультибонусами; числа расходятся с Bankiros.ru]</t>
         </is>
       </c>
       <c r="O29" s="4" t="inlineStr">
@@ -3933,7 +3964,8 @@
       <c r="P29" s="4" t="inlineStr">
         <is>
           <t>Накопительный ВТБ-Счёт до 13,75% годовых (повышенная ставка за покупки по карте); опция «Сбережения»: надбавка +1–3 п.п. к ставке в зависимости от оборота по карте. Ставки на дату проверки
-[источник: Ручная проверка (первоисточник), проверено: 2026-07-02]</t>
+[источник: Ручная проверка (первоисточник), проверено: 2026-07-02]
+[прим.: числа расходятся с Bankiros.ru]</t>
         </is>
       </c>
       <c r="Q29" s="4" t="inlineStr">
@@ -3978,9 +4010,10 @@
 [источник: premiumbanking.info, проверено: 2026-07-02]</t>
         </is>
       </c>
-      <c r="X29" s="7" t="inlineStr">
-        <is>
-          <t>не найдено</t>
+      <c r="X29" s="4" t="inlineStr">
+        <is>
+          <t>Обновлено 02.07
+[источник: Bankiros.ru, проверено: 2026-07-02]</t>
         </is>
       </c>
     </row>
@@ -4005,7 +4038,7 @@
         <v>3</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
@@ -4014,7 +4047,7 @@
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>Позиционирование (на кого рассчитан) — основное: ВТБ – Прайм+ — Уровень за 15 млн ₽ ; ВТБ Прайм+ | Системно значимый банк | Официальный сайт банка: Private Banking ÐÐ¢Ð â Ð¸Ð½Ð´Ð¸Ð²Ð¸Ð´ÑÐ°Ð»ÑÐ½Ð¾Ðµ Ð±Ð°Ð½ÐºÐ¾Ð²ÑÐºÐ¾Ðµ Ð¾Ð</t>
+          <t>Позиционирование (на кого рассчитан) — основное: ВТБ – Прайм+ — Уровень за 15 млн ₽ ; ВТБ Прайм+ | Системно значимый банк | Официальный сайт банка: Private Banking ÐÐ¢Ð â Ð¸Ð½Ð´Ð¸Ð²Ð¸Ð´ÑÐ°Ð»ÑÐ½Ð¾Ðµ Ð±Ð°Ð½ÐºÐ¾Ð²ÑÐºÐ¾Ðµ Ð¾Ð; Bankiros.ru: АО «ААА Управление Капиталом» | ООО УК «Альфа-Капитал» | Уставный капитал:</t>
         </is>
       </c>
       <c r="I30" s="4" t="inlineStr">
@@ -4049,19 +4082,22 @@
 [источник: premiumbanking.info, проверено: 2026-07-02]</t>
         </is>
       </c>
-      <c r="N30" s="7" t="inlineStr">
-        <is>
-          <t>не найдено</t>
-        </is>
-      </c>
-      <c r="O30" s="7" t="inlineStr">
-        <is>
-          <t>не найдено</t>
-        </is>
-      </c>
-      <c r="P30" s="7" t="inlineStr">
-        <is>
-          <t>не найдено</t>
+      <c r="N30" s="4" t="inlineStr">
+        <is>
+          <t>Карта с беспроцентным периодом до 110 дней и повышенным кешбэком | Как перевести Мультибонусы втб на карту? | Личный кабинет Мультибонус ВТБ
+[источник: Bankiros.ru, проверено: 2026-07-02]</t>
+        </is>
+      </c>
+      <c r="O30" s="4" t="inlineStr">
+        <is>
+          <t>Банки-партнеры ВТБ: где снять наличные без комиссии | Снятие наличных в банкомате без карты
+[источник: Bankiros.ru, проверено: 2026-07-02]</t>
+        </is>
+      </c>
+      <c r="P30" s="4" t="inlineStr">
+        <is>
+          <t>Более 1500 вкладов в 357 банках России | Выгодные вклады | Накопительные счета
+[источник: Bankiros.ru, проверено: 2026-07-02]</t>
         </is>
       </c>
       <c r="Q30" s="4" t="inlineStr">
@@ -4070,9 +4106,10 @@
 [источник: premiumbanking.info, проверено: 2026-07-02]</t>
         </is>
       </c>
-      <c r="R30" s="7" t="inlineStr">
-        <is>
-          <t>не найдено</t>
+      <c r="R30" s="4" t="inlineStr">
+        <is>
+          <t>Онлайн-заявка на автокредит | Выгодные автокредиты | Легковые автомобили
+[источник: Bankiros.ru, проверено: 2026-07-02]</t>
         </is>
       </c>
       <c r="S30" s="4" t="inlineStr">
@@ -4105,9 +4142,10 @@
 [источник: premiumbanking.info, проверено: 2026-07-02]</t>
         </is>
       </c>
-      <c r="X30" s="7" t="inlineStr">
-        <is>
-          <t>не найдено</t>
+      <c r="X30" s="4" t="inlineStr">
+        <is>
+          <t>Обновлено 02.07
+[источник: Bankiros.ru, проверено: 2026-07-02]</t>
         </is>
       </c>
     </row>
@@ -4823,7 +4861,7 @@
         <v>3</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
@@ -4832,7 +4870,7 @@
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>Позиционирование (на кого рассчитан) — основное: ВТБ – Прайм+ — Уровень за 50 млн ₽ для Мск | 30 млн ₽ регионы ; ВТБ Прайм+ | Сис | Официальный сайт банка: Private Banking ÐÐ¢Ð â Ð¸Ð½Ð´Ð¸Ð²Ð¸Ð´ÑÐ°Ð»ÑÐ½Ð¾Ðµ Ð±Ð°Ð½ÐºÐ¾Ð²ÑÐºÐ¾Ðµ Ð¾Ð</t>
+          <t>Позиционирование (на кого рассчитан) — основное: ВТБ – Прайм+ — Уровень за 50 млн ₽ для Мск | 30 млн ₽ регионы ; ВТБ Прайм+ | Сис | Официальный сайт банка: Private Banking ÐÐ¢Ð â Ð¸Ð½Ð´Ð¸Ð²Ð¸Ð´ÑÐ°Ð»ÑÐ½Ð¾Ðµ Ð±Ð°Ð½ÐºÐ¾Ð²ÑÐºÐ¾Ðµ Ð¾Ð; Bankiros.ru: АО «ААА Управление Капиталом» | ООО УК «Альфа-Капитал» | Уставный капитал:</t>
         </is>
       </c>
       <c r="I37" s="4" t="inlineStr">
@@ -4867,19 +4905,22 @@
 [источник: premiumbanking.info, проверено: 2026-07-02]</t>
         </is>
       </c>
-      <c r="N37" s="7" t="inlineStr">
-        <is>
-          <t>не найдено</t>
-        </is>
-      </c>
-      <c r="O37" s="7" t="inlineStr">
-        <is>
-          <t>не найдено</t>
-        </is>
-      </c>
-      <c r="P37" s="7" t="inlineStr">
-        <is>
-          <t>не найдено</t>
+      <c r="N37" s="4" t="inlineStr">
+        <is>
+          <t>Карта с беспроцентным периодом до 110 дней и повышенным кешбэком | Как перевести Мультибонусы втб на карту? | Личный кабинет Мультибонус ВТБ
+[источник: Bankiros.ru, проверено: 2026-07-02]</t>
+        </is>
+      </c>
+      <c r="O37" s="4" t="inlineStr">
+        <is>
+          <t>Банки-партнеры ВТБ: где снять наличные без комиссии | Снятие наличных в банкомате без карты
+[источник: Bankiros.ru, проверено: 2026-07-02]</t>
+        </is>
+      </c>
+      <c r="P37" s="4" t="inlineStr">
+        <is>
+          <t>Более 1500 вкладов в 357 банках России | Выгодные вклады | Накопительные счета
+[источник: Bankiros.ru, проверено: 2026-07-02]</t>
         </is>
       </c>
       <c r="Q37" s="4" t="inlineStr">
@@ -4888,9 +4929,10 @@
 [источник: premiumbanking.info, проверено: 2026-07-02]</t>
         </is>
       </c>
-      <c r="R37" s="7" t="inlineStr">
-        <is>
-          <t>не найдено</t>
+      <c r="R37" s="4" t="inlineStr">
+        <is>
+          <t>Онлайн-заявка на автокредит | Выгодные автокредиты | Легковые автомобили
+[источник: Bankiros.ru, проверено: 2026-07-02]</t>
         </is>
       </c>
       <c r="S37" s="4" t="inlineStr">
@@ -4923,9 +4965,10 @@
 [источник: premiumbanking.info, проверено: 2026-07-02]</t>
         </is>
       </c>
-      <c r="X37" s="7" t="inlineStr">
-        <is>
-          <t>не найдено</t>
+      <c r="X37" s="4" t="inlineStr">
+        <is>
+          <t>Обновлено 02.07
+[источник: Bankiros.ru, проверено: 2026-07-02]</t>
         </is>
       </c>
     </row>
@@ -4950,7 +4993,7 @@
         <v>3</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="G38" s="6" t="inlineStr">
         <is>
@@ -4959,7 +5002,7 @@
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t>Позиционирование (на кого рассчитан) — основное: ВТБ – Прайм+ — Уровень за 100 млн ₽ для Мск | 50 млн ₽ регионы ; ВТБ Прайм+ | Си | Официальный сайт банка: Private Banking ÐÐ¢Ð â Ð¸Ð½Ð´Ð¸Ð²Ð¸Ð´ÑÐ°Ð»ÑÐ½Ð¾Ðµ Ð±Ð°Ð½ÐºÐ¾Ð²ÑÐºÐ¾Ðµ Ð¾Ð</t>
+          <t>Позиционирование (на кого рассчитан) — основное: ВТБ – Прайм+ — Уровень за 100 млн ₽ для Мск | 50 млн ₽ регионы ; ВТБ Прайм+ | Си | Официальный сайт банка: Private Banking ÐÐ¢Ð â Ð¸Ð½Ð´Ð¸Ð²Ð¸Ð´ÑÐ°Ð»ÑÐ½Ð¾Ðµ Ð±Ð°Ð½ÐºÐ¾Ð²ÑÐºÐ¾Ðµ Ð¾Ð; Bankiros.ru: АО «ААА Управление Капиталом» | ООО УК «Альфа-Капитал» | Уставный капитал:</t>
         </is>
       </c>
       <c r="I38" s="4" t="inlineStr">
@@ -4994,19 +5037,22 @@
 [источник: premiumbanking.info, проверено: 2026-07-02]</t>
         </is>
       </c>
-      <c r="N38" s="7" t="inlineStr">
-        <is>
-          <t>не найдено</t>
-        </is>
-      </c>
-      <c r="O38" s="7" t="inlineStr">
-        <is>
-          <t>не найдено</t>
-        </is>
-      </c>
-      <c r="P38" s="7" t="inlineStr">
-        <is>
-          <t>не найдено</t>
+      <c r="N38" s="4" t="inlineStr">
+        <is>
+          <t>Карта с беспроцентным периодом до 110 дней и повышенным кешбэком | Как перевести Мультибонусы втб на карту? | Личный кабинет Мультибонус ВТБ
+[источник: Bankiros.ru, проверено: 2026-07-02]</t>
+        </is>
+      </c>
+      <c r="O38" s="4" t="inlineStr">
+        <is>
+          <t>Банки-партнеры ВТБ: где снять наличные без комиссии | Снятие наличных в банкомате без карты
+[источник: Bankiros.ru, проверено: 2026-07-02]</t>
+        </is>
+      </c>
+      <c r="P38" s="4" t="inlineStr">
+        <is>
+          <t>Более 1500 вкладов в 357 банках России | Выгодные вклады | Накопительные счета
+[источник: Bankiros.ru, проверено: 2026-07-02]</t>
         </is>
       </c>
       <c r="Q38" s="4" t="inlineStr">
@@ -5015,9 +5061,10 @@
 [источник: premiumbanking.info, проверено: 2026-07-02]</t>
         </is>
       </c>
-      <c r="R38" s="7" t="inlineStr">
-        <is>
-          <t>не найдено</t>
+      <c r="R38" s="4" t="inlineStr">
+        <is>
+          <t>Онлайн-заявка на автокредит | Выгодные автокредиты | Легковые автомобили
+[источник: Bankiros.ru, проверено: 2026-07-02]</t>
         </is>
       </c>
       <c r="S38" s="4" t="inlineStr">
@@ -5050,9 +5097,10 @@
 [источник: premiumbanking.info, проверено: 2026-07-02]</t>
         </is>
       </c>
-      <c r="X38" s="7" t="inlineStr">
-        <is>
-          <t>не найдено</t>
+      <c r="X38" s="4" t="inlineStr">
+        <is>
+          <t>Обновлено 02.07
+[источник: Bankiros.ru, проверено: 2026-07-02]</t>
         </is>
       </c>
     </row>
@@ -8017,7 +8065,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H896"/>
+  <dimension ref="A1:H921"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -43522,6 +43570,1052 @@
       </c>
       <c r="H896" s="4" t="inlineStr"/>
     </row>
+    <row r="897">
+      <c r="A897" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-02T16:47</t>
+        </is>
+      </c>
+      <c r="B897" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-02T16:40</t>
+        </is>
+      </c>
+      <c r="C897" s="4" t="inlineStr">
+        <is>
+          <t>ВТБ</t>
+        </is>
+      </c>
+      <c r="D897" s="4" t="inlineStr">
+        <is>
+          <t>Привилегия — уровень 1</t>
+        </is>
+      </c>
+      <c r="E897" s="4" t="inlineStr">
+        <is>
+          <t>Дата последнего изменения условий</t>
+        </is>
+      </c>
+      <c r="F897" s="7" t="inlineStr">
+        <is>
+          <t>не найдено</t>
+        </is>
+      </c>
+      <c r="G897" s="4" t="inlineStr">
+        <is>
+          <t>Обновлено 02.07</t>
+        </is>
+      </c>
+      <c r="H897" s="4" t="inlineStr">
+        <is>
+          <t>Bankiros.ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-02T16:47</t>
+        </is>
+      </c>
+      <c r="B898" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-02T16:40</t>
+        </is>
+      </c>
+      <c r="C898" s="4" t="inlineStr">
+        <is>
+          <t>ВТБ</t>
+        </is>
+      </c>
+      <c r="D898" s="4" t="inlineStr">
+        <is>
+          <t>Привилегия — уровень 2</t>
+        </is>
+      </c>
+      <c r="E898" s="4" t="inlineStr">
+        <is>
+          <t>Дата последнего изменения условий</t>
+        </is>
+      </c>
+      <c r="F898" s="7" t="inlineStr">
+        <is>
+          <t>не найдено</t>
+        </is>
+      </c>
+      <c r="G898" s="4" t="inlineStr">
+        <is>
+          <t>Обновлено 02.07</t>
+        </is>
+      </c>
+      <c r="H898" s="4" t="inlineStr">
+        <is>
+          <t>Bankiros.ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-02T16:47</t>
+        </is>
+      </c>
+      <c r="B899" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-02T16:40</t>
+        </is>
+      </c>
+      <c r="C899" s="4" t="inlineStr">
+        <is>
+          <t>ВТБ</t>
+        </is>
+      </c>
+      <c r="D899" s="4" t="inlineStr">
+        <is>
+          <t>Привилегия — уровень 3</t>
+        </is>
+      </c>
+      <c r="E899" s="4" t="inlineStr">
+        <is>
+          <t>Дата последнего изменения условий</t>
+        </is>
+      </c>
+      <c r="F899" s="7" t="inlineStr">
+        <is>
+          <t>не найдено</t>
+        </is>
+      </c>
+      <c r="G899" s="4" t="inlineStr">
+        <is>
+          <t>Обновлено 02.07</t>
+        </is>
+      </c>
+      <c r="H899" s="4" t="inlineStr">
+        <is>
+          <t>Bankiros.ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-02T16:47</t>
+        </is>
+      </c>
+      <c r="B900" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-02T16:40</t>
+        </is>
+      </c>
+      <c r="C900" s="4" t="inlineStr">
+        <is>
+          <t>ВТБ</t>
+        </is>
+      </c>
+      <c r="D900" s="4" t="inlineStr">
+        <is>
+          <t>Привилегия — уровень 4</t>
+        </is>
+      </c>
+      <c r="E900" s="4" t="inlineStr">
+        <is>
+          <t>Дата последнего изменения условий</t>
+        </is>
+      </c>
+      <c r="F900" s="7" t="inlineStr">
+        <is>
+          <t>не найдено</t>
+        </is>
+      </c>
+      <c r="G900" s="4" t="inlineStr">
+        <is>
+          <t>Обновлено 02.07</t>
+        </is>
+      </c>
+      <c r="H900" s="4" t="inlineStr">
+        <is>
+          <t>Bankiros.ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-02T16:47</t>
+        </is>
+      </c>
+      <c r="B901" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-02T16:40</t>
+        </is>
+      </c>
+      <c r="C901" s="4" t="inlineStr">
+        <is>
+          <t>ВТБ</t>
+        </is>
+      </c>
+      <c r="D901" s="4" t="inlineStr">
+        <is>
+          <t>Прайм+ — уровень 5</t>
+        </is>
+      </c>
+      <c r="E901" s="4" t="inlineStr">
+        <is>
+          <t>Кэшбэк / баллы</t>
+        </is>
+      </c>
+      <c r="F901" s="7" t="inlineStr">
+        <is>
+          <t>не найдено</t>
+        </is>
+      </c>
+      <c r="G901" s="4" t="inlineStr">
+        <is>
+          <t>Карта с беспроцентным периодом до 110 дней и повышенным кешбэком | Как перевести Мультибонусы втб на карту? | Личный кабинет Мультибонус ВТБ</t>
+        </is>
+      </c>
+      <c r="H901" s="4" t="inlineStr">
+        <is>
+          <t>Bankiros.ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-02T16:47</t>
+        </is>
+      </c>
+      <c r="B902" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-02T16:40</t>
+        </is>
+      </c>
+      <c r="C902" s="4" t="inlineStr">
+        <is>
+          <t>ВТБ</t>
+        </is>
+      </c>
+      <c r="D902" s="4" t="inlineStr">
+        <is>
+          <t>Прайм+ — уровень 5</t>
+        </is>
+      </c>
+      <c r="E902" s="4" t="inlineStr">
+        <is>
+          <t>Карты (тип, лимиты переводов/снятия, выпуск)</t>
+        </is>
+      </c>
+      <c r="F902" s="7" t="inlineStr">
+        <is>
+          <t>не найдено</t>
+        </is>
+      </c>
+      <c r="G902" s="4" t="inlineStr">
+        <is>
+          <t>Банки-партнеры ВТБ: где снять наличные без комиссии | Снятие наличных в банкомате без карты</t>
+        </is>
+      </c>
+      <c r="H902" s="4" t="inlineStr">
+        <is>
+          <t>Bankiros.ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-02T16:47</t>
+        </is>
+      </c>
+      <c r="B903" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-02T16:40</t>
+        </is>
+      </c>
+      <c r="C903" s="4" t="inlineStr">
+        <is>
+          <t>ВТБ</t>
+        </is>
+      </c>
+      <c r="D903" s="4" t="inlineStr">
+        <is>
+          <t>Прайм+ — уровень 5</t>
+        </is>
+      </c>
+      <c r="E903" s="4" t="inlineStr">
+        <is>
+          <t>Спецусловия по вкладам / накопительным счетам</t>
+        </is>
+      </c>
+      <c r="F903" s="7" t="inlineStr">
+        <is>
+          <t>не найдено</t>
+        </is>
+      </c>
+      <c r="G903" s="4" t="inlineStr">
+        <is>
+          <t>Более 1500 вкладов в 357 банках России | Выгодные вклады | Накопительные счета</t>
+        </is>
+      </c>
+      <c r="H903" s="4" t="inlineStr">
+        <is>
+          <t>Bankiros.ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-02T16:47</t>
+        </is>
+      </c>
+      <c r="B904" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-02T16:40</t>
+        </is>
+      </c>
+      <c r="C904" s="4" t="inlineStr">
+        <is>
+          <t>ВТБ</t>
+        </is>
+      </c>
+      <c r="D904" s="4" t="inlineStr">
+        <is>
+          <t>Прайм+ — уровень 5</t>
+        </is>
+      </c>
+      <c r="E904" s="4" t="inlineStr">
+        <is>
+          <t>Автоуслуги</t>
+        </is>
+      </c>
+      <c r="F904" s="7" t="inlineStr">
+        <is>
+          <t>не найдено</t>
+        </is>
+      </c>
+      <c r="G904" s="4" t="inlineStr">
+        <is>
+          <t>Онлайн-заявка на автокредит | Выгодные автокредиты | Легковые автомобили</t>
+        </is>
+      </c>
+      <c r="H904" s="4" t="inlineStr">
+        <is>
+          <t>Bankiros.ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-02T16:47</t>
+        </is>
+      </c>
+      <c r="B905" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-02T16:40</t>
+        </is>
+      </c>
+      <c r="C905" s="4" t="inlineStr">
+        <is>
+          <t>ВТБ</t>
+        </is>
+      </c>
+      <c r="D905" s="4" t="inlineStr">
+        <is>
+          <t>Прайм+ — уровень 5</t>
+        </is>
+      </c>
+      <c r="E905" s="4" t="inlineStr">
+        <is>
+          <t>Дата последнего изменения условий</t>
+        </is>
+      </c>
+      <c r="F905" s="7" t="inlineStr">
+        <is>
+          <t>не найдено</t>
+        </is>
+      </c>
+      <c r="G905" s="4" t="inlineStr">
+        <is>
+          <t>Обновлено 02.07</t>
+        </is>
+      </c>
+      <c r="H905" s="4" t="inlineStr">
+        <is>
+          <t>Bankiros.ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-02T16:47</t>
+        </is>
+      </c>
+      <c r="B906" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-02T16:40</t>
+        </is>
+      </c>
+      <c r="C906" s="4" t="inlineStr">
+        <is>
+          <t>ВТБ</t>
+        </is>
+      </c>
+      <c r="D906" s="4" t="inlineStr">
+        <is>
+          <t>Прайм+ — уровень 6</t>
+        </is>
+      </c>
+      <c r="E906" s="4" t="inlineStr">
+        <is>
+          <t>Кэшбэк / баллы</t>
+        </is>
+      </c>
+      <c r="F906" s="7" t="inlineStr">
+        <is>
+          <t>не найдено</t>
+        </is>
+      </c>
+      <c r="G906" s="4" t="inlineStr">
+        <is>
+          <t>Карта с беспроцентным периодом до 110 дней и повышенным кешбэком | Как перевести Мультибонусы втб на карту? | Личный кабинет Мультибонус ВТБ</t>
+        </is>
+      </c>
+      <c r="H906" s="4" t="inlineStr">
+        <is>
+          <t>Bankiros.ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-02T16:47</t>
+        </is>
+      </c>
+      <c r="B907" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-02T16:40</t>
+        </is>
+      </c>
+      <c r="C907" s="4" t="inlineStr">
+        <is>
+          <t>ВТБ</t>
+        </is>
+      </c>
+      <c r="D907" s="4" t="inlineStr">
+        <is>
+          <t>Прайм+ — уровень 6</t>
+        </is>
+      </c>
+      <c r="E907" s="4" t="inlineStr">
+        <is>
+          <t>Карты (тип, лимиты переводов/снятия, выпуск)</t>
+        </is>
+      </c>
+      <c r="F907" s="7" t="inlineStr">
+        <is>
+          <t>не найдено</t>
+        </is>
+      </c>
+      <c r="G907" s="4" t="inlineStr">
+        <is>
+          <t>Банки-партнеры ВТБ: где снять наличные без комиссии | Снятие наличных в банкомате без карты</t>
+        </is>
+      </c>
+      <c r="H907" s="4" t="inlineStr">
+        <is>
+          <t>Bankiros.ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-02T16:47</t>
+        </is>
+      </c>
+      <c r="B908" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-02T16:40</t>
+        </is>
+      </c>
+      <c r="C908" s="4" t="inlineStr">
+        <is>
+          <t>ВТБ</t>
+        </is>
+      </c>
+      <c r="D908" s="4" t="inlineStr">
+        <is>
+          <t>Прайм+ — уровень 6</t>
+        </is>
+      </c>
+      <c r="E908" s="4" t="inlineStr">
+        <is>
+          <t>Спецусловия по вкладам / накопительным счетам</t>
+        </is>
+      </c>
+      <c r="F908" s="7" t="inlineStr">
+        <is>
+          <t>не найдено</t>
+        </is>
+      </c>
+      <c r="G908" s="4" t="inlineStr">
+        <is>
+          <t>Более 1500 вкладов в 357 банках России | Выгодные вклады | Накопительные счета</t>
+        </is>
+      </c>
+      <c r="H908" s="4" t="inlineStr">
+        <is>
+          <t>Bankiros.ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-02T16:47</t>
+        </is>
+      </c>
+      <c r="B909" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-02T16:40</t>
+        </is>
+      </c>
+      <c r="C909" s="4" t="inlineStr">
+        <is>
+          <t>ВТБ</t>
+        </is>
+      </c>
+      <c r="D909" s="4" t="inlineStr">
+        <is>
+          <t>Прайм+ — уровень 6</t>
+        </is>
+      </c>
+      <c r="E909" s="4" t="inlineStr">
+        <is>
+          <t>Автоуслуги</t>
+        </is>
+      </c>
+      <c r="F909" s="7" t="inlineStr">
+        <is>
+          <t>не найдено</t>
+        </is>
+      </c>
+      <c r="G909" s="4" t="inlineStr">
+        <is>
+          <t>Онлайн-заявка на автокредит | Выгодные автокредиты | Легковые автомобили</t>
+        </is>
+      </c>
+      <c r="H909" s="4" t="inlineStr">
+        <is>
+          <t>Bankiros.ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-02T16:47</t>
+        </is>
+      </c>
+      <c r="B910" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-02T16:40</t>
+        </is>
+      </c>
+      <c r="C910" s="4" t="inlineStr">
+        <is>
+          <t>ВТБ</t>
+        </is>
+      </c>
+      <c r="D910" s="4" t="inlineStr">
+        <is>
+          <t>Прайм+ — уровень 6</t>
+        </is>
+      </c>
+      <c r="E910" s="4" t="inlineStr">
+        <is>
+          <t>Дата последнего изменения условий</t>
+        </is>
+      </c>
+      <c r="F910" s="7" t="inlineStr">
+        <is>
+          <t>не найдено</t>
+        </is>
+      </c>
+      <c r="G910" s="4" t="inlineStr">
+        <is>
+          <t>Обновлено 02.07</t>
+        </is>
+      </c>
+      <c r="H910" s="4" t="inlineStr">
+        <is>
+          <t>Bankiros.ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-02T16:47</t>
+        </is>
+      </c>
+      <c r="B911" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-02T16:40</t>
+        </is>
+      </c>
+      <c r="C911" s="4" t="inlineStr">
+        <is>
+          <t>ВТБ</t>
+        </is>
+      </c>
+      <c r="D911" s="4" t="inlineStr">
+        <is>
+          <t>Прайм+ — уровень 7</t>
+        </is>
+      </c>
+      <c r="E911" s="4" t="inlineStr">
+        <is>
+          <t>Кэшбэк / баллы</t>
+        </is>
+      </c>
+      <c r="F911" s="7" t="inlineStr">
+        <is>
+          <t>не найдено</t>
+        </is>
+      </c>
+      <c r="G911" s="4" t="inlineStr">
+        <is>
+          <t>Карта с беспроцентным периодом до 110 дней и повышенным кешбэком | Как перевести Мультибонусы втб на карту? | Личный кабинет Мультибонус ВТБ</t>
+        </is>
+      </c>
+      <c r="H911" s="4" t="inlineStr">
+        <is>
+          <t>Bankiros.ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-02T16:47</t>
+        </is>
+      </c>
+      <c r="B912" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-02T16:40</t>
+        </is>
+      </c>
+      <c r="C912" s="4" t="inlineStr">
+        <is>
+          <t>ВТБ</t>
+        </is>
+      </c>
+      <c r="D912" s="4" t="inlineStr">
+        <is>
+          <t>Прайм+ — уровень 7</t>
+        </is>
+      </c>
+      <c r="E912" s="4" t="inlineStr">
+        <is>
+          <t>Карты (тип, лимиты переводов/снятия, выпуск)</t>
+        </is>
+      </c>
+      <c r="F912" s="7" t="inlineStr">
+        <is>
+          <t>не найдено</t>
+        </is>
+      </c>
+      <c r="G912" s="4" t="inlineStr">
+        <is>
+          <t>Банки-партнеры ВТБ: где снять наличные без комиссии | Снятие наличных в банкомате без карты</t>
+        </is>
+      </c>
+      <c r="H912" s="4" t="inlineStr">
+        <is>
+          <t>Bankiros.ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-02T16:47</t>
+        </is>
+      </c>
+      <c r="B913" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-02T16:40</t>
+        </is>
+      </c>
+      <c r="C913" s="4" t="inlineStr">
+        <is>
+          <t>ВТБ</t>
+        </is>
+      </c>
+      <c r="D913" s="4" t="inlineStr">
+        <is>
+          <t>Прайм+ — уровень 7</t>
+        </is>
+      </c>
+      <c r="E913" s="4" t="inlineStr">
+        <is>
+          <t>Спецусловия по вкладам / накопительным счетам</t>
+        </is>
+      </c>
+      <c r="F913" s="7" t="inlineStr">
+        <is>
+          <t>не найдено</t>
+        </is>
+      </c>
+      <c r="G913" s="4" t="inlineStr">
+        <is>
+          <t>Более 1500 вкладов в 357 банках России | Выгодные вклады | Накопительные счета</t>
+        </is>
+      </c>
+      <c r="H913" s="4" t="inlineStr">
+        <is>
+          <t>Bankiros.ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-02T16:47</t>
+        </is>
+      </c>
+      <c r="B914" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-02T16:40</t>
+        </is>
+      </c>
+      <c r="C914" s="4" t="inlineStr">
+        <is>
+          <t>ВТБ</t>
+        </is>
+      </c>
+      <c r="D914" s="4" t="inlineStr">
+        <is>
+          <t>Прайм+ — уровень 7</t>
+        </is>
+      </c>
+      <c r="E914" s="4" t="inlineStr">
+        <is>
+          <t>Автоуслуги</t>
+        </is>
+      </c>
+      <c r="F914" s="7" t="inlineStr">
+        <is>
+          <t>не найдено</t>
+        </is>
+      </c>
+      <c r="G914" s="4" t="inlineStr">
+        <is>
+          <t>Онлайн-заявка на автокредит | Выгодные автокредиты | Легковые автомобили</t>
+        </is>
+      </c>
+      <c r="H914" s="4" t="inlineStr">
+        <is>
+          <t>Bankiros.ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-02T16:47</t>
+        </is>
+      </c>
+      <c r="B915" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-02T16:40</t>
+        </is>
+      </c>
+      <c r="C915" s="4" t="inlineStr">
+        <is>
+          <t>ВТБ</t>
+        </is>
+      </c>
+      <c r="D915" s="4" t="inlineStr">
+        <is>
+          <t>Прайм+ — уровень 7</t>
+        </is>
+      </c>
+      <c r="E915" s="4" t="inlineStr">
+        <is>
+          <t>Дата последнего изменения условий</t>
+        </is>
+      </c>
+      <c r="F915" s="7" t="inlineStr">
+        <is>
+          <t>не найдено</t>
+        </is>
+      </c>
+      <c r="G915" s="4" t="inlineStr">
+        <is>
+          <t>Обновлено 02.07</t>
+        </is>
+      </c>
+      <c r="H915" s="4" t="inlineStr">
+        <is>
+          <t>Bankiros.ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-02T16:47</t>
+        </is>
+      </c>
+      <c r="B916" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-02T16:40</t>
+        </is>
+      </c>
+      <c r="C916" s="4" t="inlineStr">
+        <is>
+          <t>ВТБ</t>
+        </is>
+      </c>
+      <c r="D916" s="4" t="inlineStr">
+        <is>
+          <t>Прайм+ — уровень 8</t>
+        </is>
+      </c>
+      <c r="E916" s="4" t="inlineStr">
+        <is>
+          <t>Кэшбэк / баллы</t>
+        </is>
+      </c>
+      <c r="F916" s="7" t="inlineStr">
+        <is>
+          <t>не найдено</t>
+        </is>
+      </c>
+      <c r="G916" s="4" t="inlineStr">
+        <is>
+          <t>Карта с беспроцентным периодом до 110 дней и повышенным кешбэком | Как перевести Мультибонусы втб на карту? | Личный кабинет Мультибонус ВТБ</t>
+        </is>
+      </c>
+      <c r="H916" s="4" t="inlineStr">
+        <is>
+          <t>Bankiros.ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-02T16:47</t>
+        </is>
+      </c>
+      <c r="B917" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-02T16:40</t>
+        </is>
+      </c>
+      <c r="C917" s="4" t="inlineStr">
+        <is>
+          <t>ВТБ</t>
+        </is>
+      </c>
+      <c r="D917" s="4" t="inlineStr">
+        <is>
+          <t>Прайм+ — уровень 8</t>
+        </is>
+      </c>
+      <c r="E917" s="4" t="inlineStr">
+        <is>
+          <t>Карты (тип, лимиты переводов/снятия, выпуск)</t>
+        </is>
+      </c>
+      <c r="F917" s="7" t="inlineStr">
+        <is>
+          <t>не найдено</t>
+        </is>
+      </c>
+      <c r="G917" s="4" t="inlineStr">
+        <is>
+          <t>Банки-партнеры ВТБ: где снять наличные без комиссии | Снятие наличных в банкомате без карты</t>
+        </is>
+      </c>
+      <c r="H917" s="4" t="inlineStr">
+        <is>
+          <t>Bankiros.ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-02T16:47</t>
+        </is>
+      </c>
+      <c r="B918" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-02T16:40</t>
+        </is>
+      </c>
+      <c r="C918" s="4" t="inlineStr">
+        <is>
+          <t>ВТБ</t>
+        </is>
+      </c>
+      <c r="D918" s="4" t="inlineStr">
+        <is>
+          <t>Прайм+ — уровень 8</t>
+        </is>
+      </c>
+      <c r="E918" s="4" t="inlineStr">
+        <is>
+          <t>Спецусловия по вкладам / накопительным счетам</t>
+        </is>
+      </c>
+      <c r="F918" s="7" t="inlineStr">
+        <is>
+          <t>не найдено</t>
+        </is>
+      </c>
+      <c r="G918" s="4" t="inlineStr">
+        <is>
+          <t>Более 1500 вкладов в 357 банках России | Выгодные вклады | Накопительные счета</t>
+        </is>
+      </c>
+      <c r="H918" s="4" t="inlineStr">
+        <is>
+          <t>Bankiros.ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-02T16:47</t>
+        </is>
+      </c>
+      <c r="B919" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-02T16:40</t>
+        </is>
+      </c>
+      <c r="C919" s="4" t="inlineStr">
+        <is>
+          <t>ВТБ</t>
+        </is>
+      </c>
+      <c r="D919" s="4" t="inlineStr">
+        <is>
+          <t>Прайм+ — уровень 8</t>
+        </is>
+      </c>
+      <c r="E919" s="4" t="inlineStr">
+        <is>
+          <t>Автоуслуги</t>
+        </is>
+      </c>
+      <c r="F919" s="7" t="inlineStr">
+        <is>
+          <t>не найдено</t>
+        </is>
+      </c>
+      <c r="G919" s="4" t="inlineStr">
+        <is>
+          <t>Онлайн-заявка на автокредит | Выгодные автокредиты | Легковые автомобили</t>
+        </is>
+      </c>
+      <c r="H919" s="4" t="inlineStr">
+        <is>
+          <t>Bankiros.ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-02T16:47</t>
+        </is>
+      </c>
+      <c r="B920" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-02T16:40</t>
+        </is>
+      </c>
+      <c r="C920" s="4" t="inlineStr">
+        <is>
+          <t>ВТБ</t>
+        </is>
+      </c>
+      <c r="D920" s="4" t="inlineStr">
+        <is>
+          <t>Прайм+ — уровень 8</t>
+        </is>
+      </c>
+      <c r="E920" s="4" t="inlineStr">
+        <is>
+          <t>Дата последнего изменения условий</t>
+        </is>
+      </c>
+      <c r="F920" s="7" t="inlineStr">
+        <is>
+          <t>не найдено</t>
+        </is>
+      </c>
+      <c r="G920" s="4" t="inlineStr">
+        <is>
+          <t>Обновлено 02.07</t>
+        </is>
+      </c>
+      <c r="H920" s="4" t="inlineStr">
+        <is>
+          <t>Bankiros.ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-02T16:47</t>
+        </is>
+      </c>
+      <c r="B921" s="4" t="inlineStr"/>
+      <c r="C921" s="4" t="inlineStr">
+        <is>
+          <t>— система —</t>
+        </is>
+      </c>
+      <c r="D921" s="4" t="inlineStr">
+        <is>
+          <t>ВТБ</t>
+        </is>
+      </c>
+      <c r="E921" s="4" t="inlineStr">
+        <is>
+          <t>целевое дозаполнение пустых полей</t>
+        </is>
+      </c>
+      <c r="F921" s="4" t="inlineStr">
+        <is>
+          <t>было пустых: 24</t>
+        </is>
+      </c>
+      <c r="G921" s="4" t="inlineStr">
+        <is>
+          <t>закрыто: 24; осталось на ручную проверку: 0</t>
+        </is>
+      </c>
+      <c r="H921" s="4" t="inlineStr">
+        <is>
+          <t>итог дозаполнения</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -43533,7 +44627,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D86"/>
+  <dimension ref="A1:D62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -44249,17 +45343,17 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>ВТБ</t>
+          <t>Газпромбанк</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Привилегия — уровень 1</t>
+          <t>Премиум — уровень 1</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Дата последнего изменения условий</t>
+          <t>Прочее (из источника)</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -44271,12 +45365,12 @@
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>ВТБ</t>
+          <t>Газпромбанк</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Привилегия — уровень 2</t>
+          <t>Премиум — уровень 1</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -44293,17 +45387,17 @@
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>ВТБ</t>
+          <t>Газпромбанк</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Привилегия — уровень 3</t>
+          <t>Премиум — уровень 2</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Дата последнего изменения условий</t>
+          <t>Прочее (из источника)</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -44315,12 +45409,12 @@
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>ВТБ</t>
+          <t>Газпромбанк</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>Привилегия — уровень 4</t>
+          <t>Премиум — уровень 2</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -44337,61 +45431,61 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>ВТБ</t>
+          <t>Газпромбанк</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Прайм+ — уровень 5</t>
+          <t>Премиум — уровень 3</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Кэшбэк / баллы</t>
+          <t>Прочее (из источника)</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>целевой поиск публичных данных результата не дал — проверить тарифные PDF банка / запросить у банка</t>
+          <t>справочное поле — заполняется при появлении данных</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>ВТБ</t>
+          <t>Газпромбанк</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>Прайм+ — уровень 5</t>
+          <t>Премиум — уровень 3</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Карты (тип, лимиты переводов/снятия, выпуск)</t>
+          <t>Дата последнего изменения условий</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>целевой поиск публичных данных результата не дал — проверить тарифные PDF банка / запросить у банка</t>
+          <t>справочное поле — заполняется при появлении данных</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>ВТБ</t>
+          <t>Газпромбанк</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Прайм+ — уровень 5</t>
+          <t>Private Banking</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Спецусловия по вкладам / накопительным счетам</t>
+          <t>Карты (тип, лимиты переводов/снятия, выпуск)</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -44403,12 +45497,12 @@
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>ВТБ</t>
+          <t>Газпромбанк</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Прайм+ — уровень 5</t>
+          <t>Private Banking</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -44425,78 +45519,78 @@
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>ВТБ</t>
+          <t>Газпромбанк</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Прайм+ — уровень 5</t>
+          <t>Private Banking</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Дата последнего изменения условий</t>
+          <t>Докупаемые опции и их цена</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>справочное поле — заполняется при появлении данных</t>
+          <t>целевой поиск публичных данных результата не дал — проверить тарифные PDF банка / запросить у банка</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>ВТБ</t>
+          <t>Газпромбанк</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>Прайм+ — уровень 6</t>
+          <t>Private Banking</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Кэшбэк / баллы</t>
+          <t>Прочее (из источника)</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>целевой поиск публичных данных результата не дал — проверить тарифные PDF банка / запросить у банка</t>
+          <t>справочное поле — заполняется при появлении данных</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>ВТБ</t>
+          <t>Газпромбанк</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Прайм+ — уровень 6</t>
+          <t>Private Banking</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Карты (тип, лимиты переводов/снятия, выпуск)</t>
+          <t>Дата последнего изменения условий</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>целевой поиск публичных данных результата не дал — проверить тарифные PDF банка / запросить у банка</t>
+          <t>справочное поле — заполняется при появлении данных</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>ВТБ</t>
+          <t>Озон Банк</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>Прайм+ — уровень 6</t>
+          <t>Ultra Bronze</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -44513,34 +45607,34 @@
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>ВТБ</t>
+          <t>Озон Банк</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Прайм+ — уровень 6</t>
+          <t>Ultra Bronze</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Автоуслуги</t>
+          <t>Прочее (из источника)</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>целевой поиск публичных данных результата не дал — проверить тарифные PDF банка / запросить у банка</t>
+          <t>справочное поле — заполняется при появлении данных</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>ВТБ</t>
+          <t>Озон Банк</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>Прайм+ — уровень 6</t>
+          <t>Ultra Bronze</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -44557,17 +45651,17 @@
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>ВТБ</t>
+          <t>Озон Банк</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Прайм+ — уровень 7</t>
+          <t>Ultra Silver</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>Кэшбэк / баллы</t>
+          <t>Спецусловия по вкладам / накопительным счетам</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -44579,61 +45673,61 @@
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>ВТБ</t>
+          <t>Озон Банк</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>Прайм+ — уровень 7</t>
+          <t>Ultra Silver</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>Карты (тип, лимиты переводов/снятия, выпуск)</t>
+          <t>Прочее (из источника)</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>целевой поиск публичных данных результата не дал — проверить тарифные PDF банка / запросить у банка</t>
+          <t>справочное поле — заполняется при появлении данных</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>ВТБ</t>
+          <t>Озон Банк</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Прайм+ — уровень 7</t>
+          <t>Ultra Silver</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>Спецусловия по вкладам / накопительным счетам</t>
+          <t>Дата последнего изменения условий</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>целевой поиск публичных данных результата не дал — проверить тарифные PDF банка / запросить у банка</t>
+          <t>справочное поле — заполняется при появлении данных</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>ВТБ</t>
+          <t>Озон Банк</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>Прайм+ — уровень 7</t>
+          <t>Ultra Gold</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>Автоуслуги</t>
+          <t>Спецусловия по вкладам / накопительным счетам</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -44645,17 +45739,17 @@
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>ВТБ</t>
+          <t>Озон Банк</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Прайм+ — уровень 7</t>
+          <t>Ultra Gold</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>Дата последнего изменения условий</t>
+          <t>Прочее (из источника)</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -44667,39 +45761,39 @@
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>ВТБ</t>
+          <t>Озон Банк</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>Прайм+ — уровень 8</t>
+          <t>Ultra Gold</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>Кэшбэк / баллы</t>
+          <t>Дата последнего изменения условий</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>целевой поиск публичных данных результата не дал — проверить тарифные PDF банка / запросить у банка</t>
+          <t>справочное поле — заполняется при появлении данных</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>ВТБ</t>
+          <t>Озон Банк</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Прайм+ — уровень 8</t>
+          <t>Ultra Platinum</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>Карты (тип, лимиты переводов/снятия, выпуск)</t>
+          <t>Спецусловия по вкладам / накопительным счетам</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -44711,61 +45805,61 @@
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>ВТБ</t>
+          <t>Озон Банк</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>Прайм+ — уровень 8</t>
+          <t>Ultra Platinum</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>Спецусловия по вкладам / накопительным счетам</t>
+          <t>Прочее (из источника)</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>целевой поиск публичных данных результата не дал — проверить тарифные PDF банка / запросить у банка</t>
+          <t>справочное поле — заполняется при появлении данных</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>ВТБ</t>
+          <t>Озон Банк</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Прайм+ — уровень 8</t>
+          <t>Ultra Platinum</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>Автоуслуги</t>
+          <t>Дата последнего изменения условий</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>целевой поиск публичных данных результата не дал — проверить тарифные PDF банка / запросить у банка</t>
+          <t>справочное поле — заполняется при появлении данных</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>ВТБ</t>
+          <t>Райффайзен Банк</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>Прайм+ — уровень 8</t>
+          <t>Premium (за плату)</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>Дата последнего изменения условий</t>
+          <t>Прочее (из источника)</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -44777,17 +45871,17 @@
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>Газпромбанк</t>
+          <t>Райффайзен Банк</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Премиум — уровень 1</t>
+          <t>Premium (за плату)</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>Прочее (из источника)</t>
+          <t>Дата последнего изменения условий</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -44799,17 +45893,17 @@
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>Газпромбанк</t>
+          <t>Райффайзен Банк</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>Премиум — уровень 1</t>
+          <t>Premium (за траты)</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>Дата последнего изменения условий</t>
+          <t>Прочее (из источника)</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -44821,17 +45915,17 @@
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>Газпромбанк</t>
+          <t>Райффайзен Банк</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Премиум — уровень 2</t>
+          <t>Premium (за траты)</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>Прочее (из источника)</t>
+          <t>Дата последнего изменения условий</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -44843,17 +45937,17 @@
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>Газпромбанк</t>
+          <t>Райффайзен Банк</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>Премиум — уровень 2</t>
+          <t>Premium (за остаток)</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>Дата последнего изменения условий</t>
+          <t>Прочее (из источника)</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -44865,17 +45959,17 @@
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>Газпромбанк</t>
+          <t>Райффайзен Банк</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Премиум — уровень 3</t>
+          <t>Premium (за остаток)</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>Прочее (из источника)</t>
+          <t>Дата последнего изменения условий</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -44887,548 +45981,20 @@
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>Газпромбанк</t>
+          <t>Wildberries (Клуб покупателей)</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Премиум — уровень 3</t>
+          <t>WB Клуб</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>Дата последнего изменения условий</t>
+          <t>Доставка</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
-        <is>
-          <t>справочное поле — заполняется при появлении данных</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="4" t="inlineStr">
-        <is>
-          <t>Газпромбанк</t>
-        </is>
-      </c>
-      <c r="B63" s="4" t="inlineStr">
-        <is>
-          <t>Private Banking</t>
-        </is>
-      </c>
-      <c r="C63" s="4" t="inlineStr">
-        <is>
-          <t>Карты (тип, лимиты переводов/снятия, выпуск)</t>
-        </is>
-      </c>
-      <c r="D63" s="4" t="inlineStr">
-        <is>
-          <t>целевой поиск публичных данных результата не дал — проверить тарифные PDF банка / запросить у банка</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="4" t="inlineStr">
-        <is>
-          <t>Газпромбанк</t>
-        </is>
-      </c>
-      <c r="B64" s="4" t="inlineStr">
-        <is>
-          <t>Private Banking</t>
-        </is>
-      </c>
-      <c r="C64" s="4" t="inlineStr">
-        <is>
-          <t>Автоуслуги</t>
-        </is>
-      </c>
-      <c r="D64" s="4" t="inlineStr">
-        <is>
-          <t>целевой поиск публичных данных результата не дал — проверить тарифные PDF банка / запросить у банка</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="4" t="inlineStr">
-        <is>
-          <t>Газпромбанк</t>
-        </is>
-      </c>
-      <c r="B65" s="4" t="inlineStr">
-        <is>
-          <t>Private Banking</t>
-        </is>
-      </c>
-      <c r="C65" s="4" t="inlineStr">
-        <is>
-          <t>Докупаемые опции и их цена</t>
-        </is>
-      </c>
-      <c r="D65" s="4" t="inlineStr">
-        <is>
-          <t>целевой поиск публичных данных результата не дал — проверить тарифные PDF банка / запросить у банка</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="4" t="inlineStr">
-        <is>
-          <t>Газпромбанк</t>
-        </is>
-      </c>
-      <c r="B66" s="4" t="inlineStr">
-        <is>
-          <t>Private Banking</t>
-        </is>
-      </c>
-      <c r="C66" s="4" t="inlineStr">
-        <is>
-          <t>Прочее (из источника)</t>
-        </is>
-      </c>
-      <c r="D66" s="4" t="inlineStr">
-        <is>
-          <t>справочное поле — заполняется при появлении данных</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="4" t="inlineStr">
-        <is>
-          <t>Газпромбанк</t>
-        </is>
-      </c>
-      <c r="B67" s="4" t="inlineStr">
-        <is>
-          <t>Private Banking</t>
-        </is>
-      </c>
-      <c r="C67" s="4" t="inlineStr">
-        <is>
-          <t>Дата последнего изменения условий</t>
-        </is>
-      </c>
-      <c r="D67" s="4" t="inlineStr">
-        <is>
-          <t>справочное поле — заполняется при появлении данных</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="4" t="inlineStr">
-        <is>
-          <t>Озон Банк</t>
-        </is>
-      </c>
-      <c r="B68" s="4" t="inlineStr">
-        <is>
-          <t>Ultra Bronze</t>
-        </is>
-      </c>
-      <c r="C68" s="4" t="inlineStr">
-        <is>
-          <t>Спецусловия по вкладам / накопительным счетам</t>
-        </is>
-      </c>
-      <c r="D68" s="4" t="inlineStr">
-        <is>
-          <t>целевой поиск публичных данных результата не дал — проверить тарифные PDF банка / запросить у банка</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="4" t="inlineStr">
-        <is>
-          <t>Озон Банк</t>
-        </is>
-      </c>
-      <c r="B69" s="4" t="inlineStr">
-        <is>
-          <t>Ultra Bronze</t>
-        </is>
-      </c>
-      <c r="C69" s="4" t="inlineStr">
-        <is>
-          <t>Прочее (из источника)</t>
-        </is>
-      </c>
-      <c r="D69" s="4" t="inlineStr">
-        <is>
-          <t>справочное поле — заполняется при появлении данных</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="4" t="inlineStr">
-        <is>
-          <t>Озон Банк</t>
-        </is>
-      </c>
-      <c r="B70" s="4" t="inlineStr">
-        <is>
-          <t>Ultra Bronze</t>
-        </is>
-      </c>
-      <c r="C70" s="4" t="inlineStr">
-        <is>
-          <t>Дата последнего изменения условий</t>
-        </is>
-      </c>
-      <c r="D70" s="4" t="inlineStr">
-        <is>
-          <t>справочное поле — заполняется при появлении данных</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="4" t="inlineStr">
-        <is>
-          <t>Озон Банк</t>
-        </is>
-      </c>
-      <c r="B71" s="4" t="inlineStr">
-        <is>
-          <t>Ultra Silver</t>
-        </is>
-      </c>
-      <c r="C71" s="4" t="inlineStr">
-        <is>
-          <t>Спецусловия по вкладам / накопительным счетам</t>
-        </is>
-      </c>
-      <c r="D71" s="4" t="inlineStr">
-        <is>
-          <t>целевой поиск публичных данных результата не дал — проверить тарифные PDF банка / запросить у банка</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="4" t="inlineStr">
-        <is>
-          <t>Озон Банк</t>
-        </is>
-      </c>
-      <c r="B72" s="4" t="inlineStr">
-        <is>
-          <t>Ultra Silver</t>
-        </is>
-      </c>
-      <c r="C72" s="4" t="inlineStr">
-        <is>
-          <t>Прочее (из источника)</t>
-        </is>
-      </c>
-      <c r="D72" s="4" t="inlineStr">
-        <is>
-          <t>справочное поле — заполняется при появлении данных</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="4" t="inlineStr">
-        <is>
-          <t>Озон Банк</t>
-        </is>
-      </c>
-      <c r="B73" s="4" t="inlineStr">
-        <is>
-          <t>Ultra Silver</t>
-        </is>
-      </c>
-      <c r="C73" s="4" t="inlineStr">
-        <is>
-          <t>Дата последнего изменения условий</t>
-        </is>
-      </c>
-      <c r="D73" s="4" t="inlineStr">
-        <is>
-          <t>справочное поле — заполняется при появлении данных</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="4" t="inlineStr">
-        <is>
-          <t>Озон Банк</t>
-        </is>
-      </c>
-      <c r="B74" s="4" t="inlineStr">
-        <is>
-          <t>Ultra Gold</t>
-        </is>
-      </c>
-      <c r="C74" s="4" t="inlineStr">
-        <is>
-          <t>Спецусловия по вкладам / накопительным счетам</t>
-        </is>
-      </c>
-      <c r="D74" s="4" t="inlineStr">
-        <is>
-          <t>целевой поиск публичных данных результата не дал — проверить тарифные PDF банка / запросить у банка</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="4" t="inlineStr">
-        <is>
-          <t>Озон Банк</t>
-        </is>
-      </c>
-      <c r="B75" s="4" t="inlineStr">
-        <is>
-          <t>Ultra Gold</t>
-        </is>
-      </c>
-      <c r="C75" s="4" t="inlineStr">
-        <is>
-          <t>Прочее (из источника)</t>
-        </is>
-      </c>
-      <c r="D75" s="4" t="inlineStr">
-        <is>
-          <t>справочное поле — заполняется при появлении данных</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="4" t="inlineStr">
-        <is>
-          <t>Озон Банк</t>
-        </is>
-      </c>
-      <c r="B76" s="4" t="inlineStr">
-        <is>
-          <t>Ultra Gold</t>
-        </is>
-      </c>
-      <c r="C76" s="4" t="inlineStr">
-        <is>
-          <t>Дата последнего изменения условий</t>
-        </is>
-      </c>
-      <c r="D76" s="4" t="inlineStr">
-        <is>
-          <t>справочное поле — заполняется при появлении данных</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="4" t="inlineStr">
-        <is>
-          <t>Озон Банк</t>
-        </is>
-      </c>
-      <c r="B77" s="4" t="inlineStr">
-        <is>
-          <t>Ultra Platinum</t>
-        </is>
-      </c>
-      <c r="C77" s="4" t="inlineStr">
-        <is>
-          <t>Спецусловия по вкладам / накопительным счетам</t>
-        </is>
-      </c>
-      <c r="D77" s="4" t="inlineStr">
-        <is>
-          <t>целевой поиск публичных данных результата не дал — проверить тарифные PDF банка / запросить у банка</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="4" t="inlineStr">
-        <is>
-          <t>Озон Банк</t>
-        </is>
-      </c>
-      <c r="B78" s="4" t="inlineStr">
-        <is>
-          <t>Ultra Platinum</t>
-        </is>
-      </c>
-      <c r="C78" s="4" t="inlineStr">
-        <is>
-          <t>Прочее (из источника)</t>
-        </is>
-      </c>
-      <c r="D78" s="4" t="inlineStr">
-        <is>
-          <t>справочное поле — заполняется при появлении данных</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="4" t="inlineStr">
-        <is>
-          <t>Озон Банк</t>
-        </is>
-      </c>
-      <c r="B79" s="4" t="inlineStr">
-        <is>
-          <t>Ultra Platinum</t>
-        </is>
-      </c>
-      <c r="C79" s="4" t="inlineStr">
-        <is>
-          <t>Дата последнего изменения условий</t>
-        </is>
-      </c>
-      <c r="D79" s="4" t="inlineStr">
-        <is>
-          <t>справочное поле — заполняется при появлении данных</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="4" t="inlineStr">
-        <is>
-          <t>Райффайзен Банк</t>
-        </is>
-      </c>
-      <c r="B80" s="4" t="inlineStr">
-        <is>
-          <t>Premium (за плату)</t>
-        </is>
-      </c>
-      <c r="C80" s="4" t="inlineStr">
-        <is>
-          <t>Прочее (из источника)</t>
-        </is>
-      </c>
-      <c r="D80" s="4" t="inlineStr">
-        <is>
-          <t>справочное поле — заполняется при появлении данных</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="4" t="inlineStr">
-        <is>
-          <t>Райффайзен Банк</t>
-        </is>
-      </c>
-      <c r="B81" s="4" t="inlineStr">
-        <is>
-          <t>Premium (за плату)</t>
-        </is>
-      </c>
-      <c r="C81" s="4" t="inlineStr">
-        <is>
-          <t>Дата последнего изменения условий</t>
-        </is>
-      </c>
-      <c r="D81" s="4" t="inlineStr">
-        <is>
-          <t>справочное поле — заполняется при появлении данных</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="4" t="inlineStr">
-        <is>
-          <t>Райффайзен Банк</t>
-        </is>
-      </c>
-      <c r="B82" s="4" t="inlineStr">
-        <is>
-          <t>Premium (за траты)</t>
-        </is>
-      </c>
-      <c r="C82" s="4" t="inlineStr">
-        <is>
-          <t>Прочее (из источника)</t>
-        </is>
-      </c>
-      <c r="D82" s="4" t="inlineStr">
-        <is>
-          <t>справочное поле — заполняется при появлении данных</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="4" t="inlineStr">
-        <is>
-          <t>Райффайзен Банк</t>
-        </is>
-      </c>
-      <c r="B83" s="4" t="inlineStr">
-        <is>
-          <t>Premium (за траты)</t>
-        </is>
-      </c>
-      <c r="C83" s="4" t="inlineStr">
-        <is>
-          <t>Дата последнего изменения условий</t>
-        </is>
-      </c>
-      <c r="D83" s="4" t="inlineStr">
-        <is>
-          <t>справочное поле — заполняется при появлении данных</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="4" t="inlineStr">
-        <is>
-          <t>Райффайзен Банк</t>
-        </is>
-      </c>
-      <c r="B84" s="4" t="inlineStr">
-        <is>
-          <t>Premium (за остаток)</t>
-        </is>
-      </c>
-      <c r="C84" s="4" t="inlineStr">
-        <is>
-          <t>Прочее (из источника)</t>
-        </is>
-      </c>
-      <c r="D84" s="4" t="inlineStr">
-        <is>
-          <t>справочное поле — заполняется при появлении данных</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="4" t="inlineStr">
-        <is>
-          <t>Райффайзен Банк</t>
-        </is>
-      </c>
-      <c r="B85" s="4" t="inlineStr">
-        <is>
-          <t>Premium (за остаток)</t>
-        </is>
-      </c>
-      <c r="C85" s="4" t="inlineStr">
-        <is>
-          <t>Дата последнего изменения условий</t>
-        </is>
-      </c>
-      <c r="D85" s="4" t="inlineStr">
-        <is>
-          <t>справочное поле — заполняется при появлении данных</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="4" t="inlineStr">
-        <is>
-          <t>Wildberries (Клуб покупателей)</t>
-        </is>
-      </c>
-      <c r="B86" s="4" t="inlineStr">
-        <is>
-          <t>WB Клуб</t>
-        </is>
-      </c>
-      <c r="C86" s="4" t="inlineStr">
-        <is>
-          <t>Доставка</t>
-        </is>
-      </c>
-      <c r="D86" s="4" t="inlineStr">
         <is>
           <t>все источники недоступны (антибот/блокировка) — проверить вручную или найти зеркальный источник</t>
         </is>
@@ -49408,19 +49974,19 @@
           <t>Кэшбэк (ставка, категории, механика)</t>
         </is>
       </c>
-      <c r="C230" s="7" t="inlineStr">
-        <is>
-          <t>не найдено</t>
+      <c r="C230" s="4" t="inlineStr">
+        <is>
+          <t>механика без ставки</t>
         </is>
       </c>
       <c r="D230" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E230" s="4" t="n">
         <v>0.2</v>
       </c>
       <c r="F230" s="4" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="231">
@@ -49430,19 +49996,19 @@
           <t>Спецусловия по вкладам / накопительным счетам</t>
         </is>
       </c>
-      <c r="C231" s="7" t="inlineStr">
-        <is>
-          <t>не найдено</t>
+      <c r="C231" s="4" t="inlineStr">
+        <is>
+          <t>спецусловия без опубликованной ставки</t>
         </is>
       </c>
       <c r="D231" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E231" s="4" t="n">
         <v>0.15</v>
       </c>
       <c r="F231" s="4" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="232">
@@ -49540,19 +50106,19 @@
           <t>Автоуслуги</t>
         </is>
       </c>
-      <c r="C236" s="7" t="inlineStr">
-        <is>
-          <t>не найдено</t>
+      <c r="C236" s="4" t="inlineStr">
+        <is>
+          <t>опция есть</t>
         </is>
       </c>
       <c r="D236" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E236" s="4" t="n">
         <v>0.05</v>
       </c>
       <c r="F236" s="4" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="237">
@@ -49562,7 +50128,7 @@
         </is>
       </c>
       <c r="F237" s="14" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="239">
@@ -49598,19 +50164,19 @@
           <t>Кэшбэк (ставка, категории, механика)</t>
         </is>
       </c>
-      <c r="C240" s="7" t="inlineStr">
-        <is>
-          <t>не найдено</t>
+      <c r="C240" s="4" t="inlineStr">
+        <is>
+          <t>механика без ставки</t>
         </is>
       </c>
       <c r="D240" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E240" s="4" t="n">
         <v>0.2</v>
       </c>
       <c r="F240" s="4" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="241">
@@ -49620,19 +50186,19 @@
           <t>Спецусловия по вкладам / накопительным счетам</t>
         </is>
       </c>
-      <c r="C241" s="7" t="inlineStr">
-        <is>
-          <t>не найдено</t>
+      <c r="C241" s="4" t="inlineStr">
+        <is>
+          <t>спецусловия без опубликованной ставки</t>
         </is>
       </c>
       <c r="D241" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E241" s="4" t="n">
         <v>0.15</v>
       </c>
       <c r="F241" s="4" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="242">
@@ -49730,19 +50296,19 @@
           <t>Автоуслуги</t>
         </is>
       </c>
-      <c r="C246" s="7" t="inlineStr">
-        <is>
-          <t>не найдено</t>
+      <c r="C246" s="4" t="inlineStr">
+        <is>
+          <t>опция есть</t>
         </is>
       </c>
       <c r="D246" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E246" s="4" t="n">
         <v>0.05</v>
       </c>
       <c r="F246" s="4" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="247">
@@ -49752,7 +50318,7 @@
         </is>
       </c>
       <c r="F247" s="14" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="249">
@@ -49788,19 +50354,19 @@
           <t>Кэшбэк (ставка, категории, механика)</t>
         </is>
       </c>
-      <c r="C250" s="7" t="inlineStr">
-        <is>
-          <t>не найдено</t>
+      <c r="C250" s="4" t="inlineStr">
+        <is>
+          <t>механика без ставки</t>
         </is>
       </c>
       <c r="D250" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E250" s="4" t="n">
         <v>0.2</v>
       </c>
       <c r="F250" s="4" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="251">
@@ -49810,19 +50376,19 @@
           <t>Спецусловия по вкладам / накопительным счетам</t>
         </is>
       </c>
-      <c r="C251" s="7" t="inlineStr">
-        <is>
-          <t>не найдено</t>
+      <c r="C251" s="4" t="inlineStr">
+        <is>
+          <t>спецусловия без опубликованной ставки</t>
         </is>
       </c>
       <c r="D251" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E251" s="4" t="n">
         <v>0.15</v>
       </c>
       <c r="F251" s="4" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="252">
@@ -49920,19 +50486,19 @@
           <t>Автоуслуги</t>
         </is>
       </c>
-      <c r="C256" s="7" t="inlineStr">
-        <is>
-          <t>не найдено</t>
+      <c r="C256" s="4" t="inlineStr">
+        <is>
+          <t>опция есть</t>
         </is>
       </c>
       <c r="D256" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E256" s="4" t="n">
         <v>0.05</v>
       </c>
       <c r="F256" s="4" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="257">
@@ -49942,7 +50508,7 @@
         </is>
       </c>
       <c r="F257" s="14" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="259">
@@ -49978,19 +50544,19 @@
           <t>Кэшбэк (ставка, категории, механика)</t>
         </is>
       </c>
-      <c r="C260" s="7" t="inlineStr">
-        <is>
-          <t>не найдено</t>
+      <c r="C260" s="4" t="inlineStr">
+        <is>
+          <t>механика без ставки</t>
         </is>
       </c>
       <c r="D260" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E260" s="4" t="n">
         <v>0.2</v>
       </c>
       <c r="F260" s="4" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="261">
@@ -50000,19 +50566,19 @@
           <t>Спецусловия по вкладам / накопительным счетам</t>
         </is>
       </c>
-      <c r="C261" s="7" t="inlineStr">
-        <is>
-          <t>не найдено</t>
+      <c r="C261" s="4" t="inlineStr">
+        <is>
+          <t>спецусловия без опубликованной ставки</t>
         </is>
       </c>
       <c r="D261" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E261" s="4" t="n">
         <v>0.15</v>
       </c>
       <c r="F261" s="4" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="262">
@@ -50110,19 +50676,19 @@
           <t>Автоуслуги</t>
         </is>
       </c>
-      <c r="C266" s="7" t="inlineStr">
-        <is>
-          <t>не найдено</t>
+      <c r="C266" s="4" t="inlineStr">
+        <is>
+          <t>опция есть</t>
         </is>
       </c>
       <c r="D266" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E266" s="4" t="n">
         <v>0.05</v>
       </c>
       <c r="F266" s="4" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="267">
@@ -50132,7 +50698,7 @@
         </is>
       </c>
       <c r="F267" s="14" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="269">
@@ -52253,7 +52819,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B133"/>
+  <dimension ref="A1:B140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -52280,7 +52846,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>2026-07-02T16:40:32</t>
+          <t>2026-07-02T16:47:30</t>
         </is>
       </c>
     </row>
@@ -52328,7 +52894,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>645</t>
         </is>
       </c>
     </row>
@@ -52340,7 +52906,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -52352,7 +52918,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-02T16:00:10</t>
+          <t>2026-07-02T16:40:32</t>
         </is>
       </c>
     </row>
@@ -52376,7 +52942,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Сбер / СберПремьер — уровень 1 [official]; Сбер / СберПремьер — уровень 1 [official]; Сбер / СберПремьер — уровень 1 [official]; Сбер / СберПремьер — уровень 1 [pbi]; Сбер / СберПремьер — уровень 1 [sravni_ru]; Сбер / СберПремьер — уровень 1 [bankiros]; Сбер / СберПремьер — уровень 2 [official]; Сбер / СберПремьер — уровень 2 [official]; Сбер / СберПремьер — уровень 2 [official]; Сбер / СберПремьер — уровень 2 [pbi]; Сбер / СберПремьер — уровень 2 [sravni_ru]; Сбер / СберПремьер — уровень 2 [bankiros]; Сбер / СберПремьер — уровень 3 [official]; Сбер / СберПремьер — уровень 3 [official]; Сбер / СберПремьер — уровень 3 [official]; Сбер / СберПремьер — уровень 3 [pbi]; Сбер / СберПремьер — уровень 3 [sravni_ru]; Сбер / СберПремьер — уровень 3 [bankiros]; Сбер / СберПервый — уровень 4 [official]; Сбер / СберПервый — уровень 4 [official]; Сбер / СберПервый — уровень 4 [official]; Сбер / СберПервый — уровень 4 [pbi]; Сбер / СберПервый — уровень 4 [sravni_ru]; Сбер / СберПервый — уровень 4 [bankiros]; Сбер / СберПервый — уровень 5 [official]; Сбер / СберПервый — уровень 5 [official]; Сбер / СберПервый — уровень 5 [official]; Сбер / СберПервый — уровень 5 [pbi]; Сбер / СберПервый — уровень 5 [sravni_ru]; Сбер / СберПервый — уровень 5 [bankiros]; Сбер / Sber Private Banking — уровень 6 [official]; Сбер / Sber Private Banking — уровень 6 [official]; Сбер / Sber Private Banking — уровень 6 [pbi]; Сбер / Sber Private Banking — уровень 6 [sravni_ru]; Сбер / Sber Private Banking — уровень 6 [bankiros]; Т-Банк / Premium Bronze [official]; Т-Банк / Premium Bronze [pbi]; Т-Банк / Premium Silver [official]; Т-Банк / Premium Silver [pbi]; Т-Банк / Premium Gold [official]; Т-Банк / Premium Gold [pbi]; Т-Банк / Private (Diamond) [official]; Т-Банк / Private (Diamond) [pbi]; Альфа-Банк / Alfa Only — уровень 1 [official]; Альфа-Банк / Alfa Only — уровень 1 [pbi]; Альфа-Банк / Alfa Only — уровень 1 [bankiros]; Альфа-Банк / Alfa Only — уровень 2 [official]; Альфа-Банк / Alfa Only — уровень 2 [pbi]; Альфа-Банк / Alfa Only — уровень 2 [bankiros]; Альфа-Банк / Alfa Only — уровень 3 [official]; Альфа-Банк / Alfa Only — уровень 3 [pbi]; Альфа-Банк / Alfa Only — уровень 3 [bankiros]; Альфа-Банк / Alfa Only — уровень 4 [official]; Альфа-Банк / Alfa Only — уровень 4 [pbi]; Альфа-Банк / Alfa Only — уровень 4 [bankiros]; Альфа-Банк / A-Club (private) [official]; Альфа-Банк / A-Club (private) [pbi]; Альфа-Банк / A-Club (private) [bankiros]; ВТБ / Привилегия — уровень 1 [official]; ВТБ / Привилегия — уровень 1 [pbi]; ВТБ / Привилегия — уровень 1 [bankiros]; ВТБ / Привилегия — уровень 2 [official]; ВТБ / Привилегия — уровень 2 [pbi]; ВТБ / Привилегия — уровень 2 [bankiros]; ВТБ / Привилегия — уровень 3 [official]; ВТБ / Привилегия — уровень 3 [pbi]; ВТБ / Привилегия — уровень 3 [bankiros]; ВТБ / Привилегия — уровень 4 [official]; ВТБ / Привилегия — уровень 4 [pbi]; ВТБ / Привилегия — уровень 4 [bankiros]; ВТБ / Прайм+ — уровень 5 [official]; ВТБ / Прайм+ — уровень 5 [pbi]; ВТБ / Прайм+ — уровень 5 [bankiros]; ВТБ / Прайм+ — уровень 6 [official]; ВТБ / Прайм+ — уровень 6 [pbi]; ВТБ / Прайм+ — уровень 6 [bankiros]; ВТБ / Прайм+ — уровень 7 [official]; ВТБ / Прайм+ — уровень 7 [pbi]; ВТБ / Прайм+ — уровень 7 [bankiros]; ВТБ / Прайм+ — уровень 8 [official]; ВТБ / Прайм+ — уровень 8 [pbi]; ВТБ / Прайм+ — уровень 8 [bankiros]; Газпромбанк / Премиум — уровень 1 [official]; Газпромбанк / Премиум — уровень 1 [pbi]; Газпромбанк / Премиум — уровень 1 [bankiros]; Газпромбанк / Премиум — уровень 2 [official]; Газпромбанк / Премиум — уровень 2 [pbi]; Газпромбанк / Премиум — уровень 2 [bankiros]; Газпромбанк / Премиум — уровень 3 [official]; Газпромбанк / Премиум — уровень 3 [pbi]; Газпромбанк / Премиум — уровень 3 [bankiros]; Газпромбанк / Private Banking [official]; Газпромбанк / Private Banking [pbi]; Газпромбанк / Private Banking [bankiros]; Озон Банк / Ultra Bronze [official]; Озон Банк / Ultra Bronze [pbi]; Озон Банк / Ultra Silver [official]; Озон Банк / Ultra Silver [pbi]; Озон Банк / Ultra Gold [official]; Озон Банк / Ultra Gold [pbi]; Озон Банк / Ultra Platinum [official]; Озон Банк / Ultra Platinum [pbi]; Райффайзен Банк / Premium (за плату) [official]; Райффайзен Банк / Premium (за плату) [pbi]; Райффайзен Банк / Premium (за траты) [official]; Райффайзен Банк / Premium (за траты) [pbi]; Райффайзен Банк / Premium (за остаток) [official]; Райффайзен Банк / Premium (за остаток) [pbi]; HSBC / Premier [official]; HSBC / Premier Elite (экс-Jade) [official]; HSBC / Global Private Banking [official]; Citi / Citigold [official]; Citi / Citi Private Bank [official]; JPMorgan Chase / Chase Private Client [official]; JPMorgan Chase / J.P. Morgan Private Bank [official]; Bank of America / Preferred Rewards [official]; Standard Chartered / Priority Banking [official]; DBS (Сингапур) / Treasures [official]; DBS (Сингапур) / Treasures Private Client [official]; Deutsche Bank / Wealth Management [official]; BNP Paribas / Wealth Management [official]; Barclays / Premier Banking [official]; Яндекс Плюс / Яндекс Плюс [official]; premiumbanking.info (обзорная)</t>
+          <t>Сбер / СберПремьер — уровень 1 [official]; Сбер / СберПремьер — уровень 1 [official]; Сбер / СберПремьер — уровень 1 [official]; Сбер / СберПремьер — уровень 1 [pbi]; Сбер / СберПремьер — уровень 1 [sravni_ru]; Сбер / СберПремьер — уровень 1 [bankiros]; Сбер / СберПремьер — уровень 2 [official]; Сбер / СберПремьер — уровень 2 [official]; Сбер / СберПремьер — уровень 2 [official]; Сбер / СберПремьер — уровень 2 [pbi]; Сбер / СберПремьер — уровень 2 [sravni_ru]; Сбер / СберПремьер — уровень 2 [bankiros]; Сбер / СберПремьер — уровень 3 [official]; Сбер / СберПремьер — уровень 3 [official]; Сбер / СберПремьер — уровень 3 [official]; Сбер / СберПремьер — уровень 3 [pbi]; Сбер / СберПремьер — уровень 3 [sravni_ru]; Сбер / СберПремьер — уровень 3 [bankiros]; Сбер / СберПервый — уровень 4 [official]; Сбер / СберПервый — уровень 4 [official]; Сбер / СберПервый — уровень 4 [official]; Сбер / СберПервый — уровень 4 [pbi]; Сбер / СберПервый — уровень 4 [sravni_ru]; Сбер / СберПервый — уровень 4 [bankiros]; Сбер / СберПервый — уровень 5 [official]; Сбер / СберПервый — уровень 5 [official]; Сбер / СберПервый — уровень 5 [official]; Сбер / СберПервый — уровень 5 [pbi]; Сбер / СберПервый — уровень 5 [sravni_ru]; Сбер / СберПервый — уровень 5 [bankiros]; Сбер / Sber Private Banking — уровень 6 [official]; Сбер / Sber Private Banking — уровень 6 [official]; Сбер / Sber Private Banking — уровень 6 [pbi]; Сбер / Sber Private Banking — уровень 6 [sravni_ru]; Сбер / Sber Private Banking — уровень 6 [bankiros]; Т-Банк / Premium Bronze [official]; Т-Банк / Premium Bronze [pbi]; Т-Банк / Premium Silver [official]; Т-Банк / Premium Silver [pbi]; Т-Банк / Premium Gold [official]; Т-Банк / Premium Gold [pbi]; Т-Банк / Private (Diamond) [official]; Т-Банк / Private (Diamond) [pbi]; Альфа-Банк / Alfa Only — уровень 1 [official]; Альфа-Банк / Alfa Only — уровень 1 [pbi]; Альфа-Банк / Alfa Only — уровень 1 [bankiros]; Альфа-Банк / Alfa Only — уровень 2 [official]; Альфа-Банк / Alfa Only — уровень 2 [pbi]; Альфа-Банк / Alfa Only — уровень 2 [bankiros]; Альфа-Банк / Alfa Only — уровень 3 [official]; Альфа-Банк / Alfa Only — уровень 3 [pbi]; Альфа-Банк / Alfa Only — уровень 3 [bankiros]; Альфа-Банк / Alfa Only — уровень 4 [official]; Альфа-Банк / Alfa Only — уровень 4 [pbi]; Альфа-Банк / Alfa Only — уровень 4 [bankiros]; Альфа-Банк / A-Club (private) [official]; Альфа-Банк / A-Club (private) [pbi]; Альфа-Банк / A-Club (private) [bankiros]; ВТБ / Привилегия — уровень 1 [official]; ВТБ / Привилегия — уровень 1 [pbi]; ВТБ / Привилегия — уровень 1 [bankiros]; ВТБ / Привилегия — уровень 2 [official]; ВТБ / Привилегия — уровень 2 [pbi]; ВТБ / Привилегия — уровень 2 [bankiros]; ВТБ / Привилегия — уровень 3 [official]; ВТБ / Привилегия — уровень 3 [pbi]; ВТБ / Привилегия — уровень 3 [bankiros]; ВТБ / Привилегия — уровень 4 [official]; ВТБ / Привилегия — уровень 4 [pbi]; ВТБ / Привилегия — уровень 4 [bankiros]; ВТБ / Прайм+ — уровень 5 [official]; ВТБ / Прайм+ — уровень 5 [pbi]; ВТБ / Прайм+ — уровень 5 [bankiros]; ВТБ / Прайм+ — уровень 6 [official]; ВТБ / Прайм+ — уровень 6 [pbi]; ВТБ / Прайм+ — уровень 6 [bankiros]; ВТБ / Прайм+ — уровень 7 [official]; ВТБ / Прайм+ — уровень 7 [pbi]; ВТБ / Прайм+ — уровень 7 [bankiros]; ВТБ / Прайм+ — уровень 8 [official]; ВТБ / Прайм+ — уровень 8 [pbi]; ВТБ / Прайм+ — уровень 8 [bankiros]; Газпромбанк / Премиум — уровень 1 [official]; Газпромбанк / Премиум — уровень 1 [pbi]; Газпромбанк / Премиум — уровень 1 [bankiros]; Газпромбанк / Премиум — уровень 2 [official]; Газпромбанк / Премиум — уровень 2 [pbi]; Газпромбанк / Премиум — уровень 2 [bankiros]; Газпромбанк / Премиум — уровень 3 [official]; Газпромбанк / Премиум — уровень 3 [pbi]; Газпромбанк / Премиум — уровень 3 [bankiros]; Газпромбанк / Private Banking [official]; Газпромбанк / Private Banking [pbi]; Газпромбанк / Private Banking [bankiros]; Озон Банк / Ultra Bronze [official]; Озон Банк / Ultra Bronze [pbi]; Озон Банк / Ultra Silver [official]; Озон Банк / Ultra Silver [pbi]; Озон Банк / Ultra Gold [official]; Озон Банк / Ultra Gold [pbi]; Озон Банк / Ultra Platinum [official]; Озон Банк / Ultra Platinum [pbi]; Райффайзен Банк / Premium (за плату) [official]; Райффайзен Банк / Premium (за плату) [pbi]; Райффайзен Банк / Premium (за траты) [official]; Райффайзен Банк / Premium (за траты) [pbi]; Райффайзен Банк / Premium (за остаток) [official]; Райффайзен Банк / Premium (за остаток) [pbi]; Revolut / Premium [official]; Revolut / Metal [official]; Revolut / Ultra [official]; N26 / Go (экс-You) [official]; N26 / Metal [official]; Wise / Wise (multi-currency, без тиров) [official]; Monzo / Extra [official]; Monzo / Perks [official]; Monzo / Max [official]; Яндекс Плюс / Яндекс Плюс [official]; premiumbanking.info (обзорная)</t>
         </is>
       </c>
     </row>
@@ -52388,7 +52954,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Сбер / СберПремьер — уровень 1 [banki_ru]: blocked_robots: запрещено robots.txt; Сбер / СберПремьер — уровень 2 [banki_ru]: blocked_robots: запрещено robots.txt; Сбер / СберПремьер — уровень 3 [banki_ru]: blocked_robots: запрещено robots.txt; Сбер / СберПервый — уровень 4 [banki_ru]: blocked_robots: запрещено robots.txt; Сбер / СберПервый — уровень 5 [banki_ru]: blocked_robots: запрещено robots.txt; Сбер / Sber Private Banking — уровень 6 [banki_ru]: blocked_robots: запрещено robots.txt; Т-Банк / Premium Bronze [banki_ru]: blocked_robots: запрещено robots.txt; Т-Банк / Premium Silver [banki_ru]: blocked_robots: запрещено robots.txt; Т-Банк / Premium Gold [banki_ru]: blocked_robots: запрещено robots.txt; Т-Банк / Private (Diamond) [banki_ru]: blocked_robots: запрещено robots.txt; Альфа-Банк / Alfa Only — уровень 1 [banki_ru]: blocked_robots: запрещено robots.txt; Альфа-Банк / Alfa Only — уровень 2 [banki_ru]: blocked_robots: запрещено robots.txt; Альфа-Банк / Alfa Only — уровень 3 [banki_ru]: blocked_robots: запрещено robots.txt; Альфа-Банк / Alfa Only — уровень 4 [banki_ru]: blocked_robots: запрещено robots.txt; Альфа-Банк / A-Club (private) [banki_ru]: blocked_robots: запрещено robots.txt; ВТБ / Привилегия — уровень 1 [banki_ru]: blocked_robots: запрещено robots.txt; ВТБ / Привилегия — уровень 2 [banki_ru]: blocked_robots: запрещено robots.txt; ВТБ / Привилегия — уровень 3 [banki_ru]: blocked_robots: запрещено robots.txt; ВТБ / Привилегия — уровень 4 [banki_ru]: blocked_robots: запрещено robots.txt; ВТБ / Прайм+ — уровень 5 [banki_ru]: blocked_robots: запрещено robots.txt; ВТБ / Прайм+ — уровень 6 [banki_ru]: blocked_robots: запрещено robots.txt; ВТБ / Прайм+ — уровень 7 [banki_ru]: blocked_robots: запрещено robots.txt; ВТБ / Прайм+ — уровень 8 [banki_ru]: blocked_robots: запрещено robots.txt; Газпромбанк / Премиум — уровень 1 [banki_ru]: blocked_robots: запрещено robots.txt; Газпромбанк / Премиум — уровень 2 [banki_ru]: blocked_robots: запрещено robots.txt; Газпромбанк / Премиум — уровень 3 [banki_ru]: blocked_robots: запрещено robots.txt; Газпромбанк / Private Banking [banki_ru]: blocked_robots: запрещено robots.txt; Райффайзен Банк / Premium (за плату) [banki_ru]: blocked_robots: запрещено robots.txt; Райффайзен Банк / Premium (за траты) [banki_ru]: blocked_robots: запрещено robots.txt; Райффайзен Банк / Premium (за остаток) [banki_ru]: blocked_robots: запрещено robots.txt; Citi / Citigold Private Client [official]: js_required: страница требует JS-рендеринга (playwright недоступен); Bank of America / BofA Private Bank [official]: js_required: страница требует JS-рендеринга (playwright недоступен); UBS / Global Wealth Management [official]: unavailable: ConnectionError: ('Connection aborted.', ConnectionResetError(54, 'Connection reset by peer')); Standard Chartered / Priority Private [official]: unavailable: HTTP 404; Emirates NBD / Priority Banking [official]: unavailable: HTTP 403; Ozon Premium / Ozon Premium [official]: unavailable: HTTP 403; Wildberries (Клуб покупателей) / WB Клуб [official]: unavailable: HTTP 498; Frank RG (рейтинги Premium/Private Banking): unavailable: ConnectionError: ('Connection aborted.', ConnectionResetError(54, 'Connection reset by peer'))</t>
+          <t>Сбер / СберПремьер — уровень 1 [banki_ru]: blocked_robots: запрещено robots.txt; Сбер / СберПремьер — уровень 2 [banki_ru]: blocked_robots: запрещено robots.txt; Сбер / СберПремьер — уровень 3 [banki_ru]: blocked_robots: запрещено robots.txt; Сбер / СберПервый — уровень 4 [banki_ru]: blocked_robots: запрещено robots.txt; Сбер / СберПервый — уровень 5 [banki_ru]: blocked_robots: запрещено robots.txt; Сбер / Sber Private Banking — уровень 6 [banki_ru]: blocked_robots: запрещено robots.txt; Т-Банк / Premium Bronze [banki_ru]: blocked_robots: запрещено robots.txt; Т-Банк / Premium Silver [banki_ru]: blocked_robots: запрещено robots.txt; Т-Банк / Premium Gold [banki_ru]: blocked_robots: запрещено robots.txt; Т-Банк / Private (Diamond) [banki_ru]: blocked_robots: запрещено robots.txt; Альфа-Банк / Alfa Only — уровень 1 [banki_ru]: blocked_robots: запрещено robots.txt; Альфа-Банк / Alfa Only — уровень 2 [banki_ru]: blocked_robots: запрещено robots.txt; Альфа-Банк / Alfa Only — уровень 3 [banki_ru]: blocked_robots: запрещено robots.txt; Альфа-Банк / Alfa Only — уровень 4 [banki_ru]: blocked_robots: запрещено robots.txt; Альфа-Банк / A-Club (private) [banki_ru]: blocked_robots: запрещено robots.txt; ВТБ / Привилегия — уровень 1 [banki_ru]: blocked_robots: запрещено robots.txt; ВТБ / Привилегия — уровень 2 [banki_ru]: blocked_robots: запрещено robots.txt; ВТБ / Привилегия — уровень 3 [banki_ru]: blocked_robots: запрещено robots.txt; ВТБ / Привилегия — уровень 4 [banki_ru]: blocked_robots: запрещено robots.txt; ВТБ / Прайм+ — уровень 5 [banki_ru]: blocked_robots: запрещено robots.txt; ВТБ / Прайм+ — уровень 6 [banki_ru]: blocked_robots: запрещено robots.txt; ВТБ / Прайм+ — уровень 7 [banki_ru]: blocked_robots: запрещено robots.txt; ВТБ / Прайм+ — уровень 8 [banki_ru]: blocked_robots: запрещено robots.txt; Газпромбанк / Премиум — уровень 1 [banki_ru]: blocked_robots: запрещено robots.txt; Газпромбанк / Премиум — уровень 2 [banki_ru]: blocked_robots: запрещено robots.txt; Газпромбанк / Премиум — уровень 3 [banki_ru]: blocked_robots: запрещено robots.txt; Газпромбанк / Private Banking [banki_ru]: blocked_robots: запрещено robots.txt; Райффайзен Банк / Premium (за плату) [banki_ru]: blocked_robots: запрещено robots.txt; Райффайзен Банк / Premium (за траты) [banki_ru]: blocked_robots: запрещено robots.txt; Райффайзен Банк / Premium (за остаток) [banki_ru]: blocked_robots: запрещено robots.txt; Ozon Premium / Ozon Premium [official]: unavailable: HTTP 403; Wildberries (Клуб покупателей) / WB Клуб [official]: unavailable: HTTP 498; Frank RG (рейтинги Premium/Private Banking): unavailable: ConnectionError: ('Connection aborted.', ConnectionResetError(54, 'Connection reset by peer'))</t>
         </is>
       </c>
     </row>
@@ -52400,7 +52966,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>542</t>
+          <t>621</t>
         </is>
       </c>
     </row>
@@ -52412,7 +52978,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -52424,7 +52990,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>2026-07-02T15:49:02</t>
+          <t>2026-07-02T16:00:10</t>
         </is>
       </c>
     </row>
@@ -52448,7 +53014,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Сбер / СберПремьер — уровень 1 [official]; Сбер / СберПремьер — уровень 1 [official]; Сбер / СберПремьер — уровень 1 [official]; Сбер / СберПремьер — уровень 1 [pbi]; Сбер / СберПремьер — уровень 1 [sravni_ru]; Сбер / СберПремьер — уровень 1 [bankiros]; Сбер / СберПремьер — уровень 2 [official]; Сбер / СберПремьер — уровень 2 [official]; Сбер / СберПремьер — уровень 2 [official]; Сбер / СберПремьер — уровень 2 [pbi]; Сбер / СберПремьер — уровень 2 [sravni_ru]; Сбер / СберПремьер — уровень 2 [bankiros]; Сбер / СберПремьер — уровень 3 [official]; Сбер / СберПремьер — уровень 3 [official]; Сбер / СберПремьер — уровень 3 [official]; Сбер / СберПремьер — уровень 3 [pbi]; Сбер / СберПремьер — уровень 3 [sravni_ru]; Сбер / СберПремьер — уровень 3 [bankiros]; Сбер / СберПервый — уровень 4 [official]; Сбер / СберПервый — уровень 4 [official]; Сбер / СберПервый — уровень 4 [official]; Сбер / СберПервый — уровень 4 [pbi]; Сбер / СберПервый — уровень 4 [sravni_ru]; Сбер / СберПервый — уровень 4 [bankiros]; Сбер / СберПервый — уровень 5 [official]; Сбер / СберПервый — уровень 5 [official]; Сбер / СберПервый — уровень 5 [official]; Сбер / СберПервый — уровень 5 [pbi]; Сбер / СберПервый — уровень 5 [sravni_ru]; Сбер / СберПервый — уровень 5 [bankiros]; Сбер / Sber Private Banking — уровень 6 [official]; Сбер / Sber Private Banking — уровень 6 [official]; Сбер / Sber Private Banking — уровень 6 [pbi]; Сбер / Sber Private Banking — уровень 6 [sravni_ru]; Сбер / Sber Private Banking — уровень 6 [bankiros]; Т-Банк / Premium Bronze [official]; Т-Банк / Premium Bronze [pbi]; Т-Банк / Premium Silver [official]; Т-Банк / Premium Silver [pbi]; Т-Банк / Premium Gold [official]; Т-Банк / Premium Gold [pbi]; Т-Банк / Private (Diamond) [official]; Т-Банк / Private (Diamond) [pbi]; Альфа-Банк / Alfa Only — уровень 1 [official]; Альфа-Банк / Alfa Only — уровень 1 [pbi]; Альфа-Банк / Alfa Only — уровень 1 [bankiros]; Альфа-Банк / Alfa Only — уровень 2 [official]; Альфа-Банк / Alfa Only — уровень 2 [pbi]; Альфа-Банк / Alfa Only — уровень 2 [bankiros]; Альфа-Банк / Alfa Only — уровень 3 [official]; Альфа-Банк / Alfa Only — уровень 3 [pbi]; Альфа-Банк / Alfa Only — уровень 3 [bankiros]; Альфа-Банк / Alfa Only — уровень 4 [official]; Альфа-Банк / Alfa Only — уровень 4 [pbi]; Альфа-Банк / Alfa Only — уровень 4 [bankiros]; Альфа-Банк / A-Club (private) [official]; Альфа-Банк / A-Club (private) [pbi]; Альфа-Банк / A-Club (private) [bankiros]; ВТБ / Привилегия — уровень 1 [official]; ВТБ / Привилегия — уровень 1 [pbi]; ВТБ / Привилегия — уровень 1 [bankiros]; ВТБ / Привилегия — уровень 2 [official]; ВТБ / Привилегия — уровень 2 [pbi]; ВТБ / Привилегия — уровень 2 [bankiros]; ВТБ / Привилегия — уровень 3 [official]; ВТБ / Привилегия — уровень 3 [pbi]; ВТБ / Привилегия — уровень 3 [bankiros]; ВТБ / Привилегия — уровень 4 [official]; ВТБ / Привилегия — уровень 4 [pbi]; ВТБ / Привилегия — уровень 4 [bankiros]; ВТБ / Прайм+ — уровень 5 [official]; ВТБ / Прайм+ — уровень 5 [pbi]; ВТБ / Прайм+ — уровень 5 [bankiros]; ВТБ / Прайм+ — уровень 6 [official]; ВТБ / Прайм+ — уровень 6 [pbi]; ВТБ / Прайм+ — уровень 6 [bankiros]; ВТБ / Прайм+ — уровень 7 [official]; ВТБ / Прайм+ — уровень 7 [pbi]; ВТБ / Прайм+ — уровень 7 [bankiros]; ВТБ / Прайм+ — уровень 8 [official]; ВТБ / Прайм+ — уровень 8 [pbi]; ВТБ / Прайм+ — уровень 8 [bankiros]; Газпромбанк / Премиум — уровень 1 [official]; Газпромбанк / Премиум — уровень 1 [pbi]; Газпромбанк / Премиум — уровень 1 [bankiros]; Газпромбанк / Премиум — уровень 2 [official]; Газпромбанк / Премиум — уровень 2 [pbi]; Газпромбанк / Премиум — уровень 2 [bankiros]; Газпромбанк / Премиум — уровень 3 [official]; Газпромбанк / Премиум — уровень 3 [pbi]; Газпромбанк / Премиум — уровень 3 [bankiros]; Газпромбанк / Private Banking [official]; Газпромбанк / Private Banking [pbi]; Газпромбанк / Private Banking [bankiros]; Озон Банк / Ultra Bronze [official]; Озон Банк / Ultra Bronze [pbi]; Озон Банк / Ultra Silver [official]; Озон Банк / Ultra Silver [pbi]; Озон Банк / Ultra Gold [official]; Озон Банк / Ultra Gold [pbi]; Озон Банк / Ultra Platinum [official]; Озон Банк / Ultra Platinum [pbi]; Райффайзен Банк / Premium (за плату) [official]; Райффайзен Банк / Premium (за плату) [pbi]; Райффайзен Банк / Premium (за траты) [official]; Райффайзен Банк / Premium (за траты) [pbi]; Райффайзен Банк / Premium (за остаток) [official]; Райффайзен Банк / Premium (за остаток) [pbi]; HSBC / Premier [official]; HSBC / Premier Elite (экс-Jade) [official]; HSBC / Global Private Banking [official]; Citi / Citigold [official]; Citi / Citi Private Bank [official]; JPMorgan Chase / Chase Private Client [official]; JPMorgan Chase / J.P. Morgan Private Bank [official]; Bank of America / Preferred Rewards [official]; Standard Chartered / Priority Banking [official]; Standard Chartered / Priority Private [official]; DBS (Сингапур) / Treasures [official]; DBS (Сингапур) / Treasures Private Client [official]; Deutsche Bank / Wealth Management [official]; BNP Paribas / Wealth Management [official]; Barclays / Premier Banking [official]; Яндекс Плюс / Яндекс Плюс [official]; premiumbanking.info (обзорная)</t>
+          <t>Сбер / СберПремьер — уровень 1 [official]; Сбер / СберПремьер — уровень 1 [official]; Сбер / СберПремьер — уровень 1 [official]; Сбер / СберПремьер — уровень 1 [pbi]; Сбер / СберПремьер — уровень 1 [sravni_ru]; Сбер / СберПремьер — уровень 1 [bankiros]; Сбер / СберПремьер — уровень 2 [official]; Сбер / СберПремьер — уровень 2 [official]; Сбер / СберПремьер — уровень 2 [official]; Сбер / СберПремьер — уровень 2 [pbi]; Сбер / СберПремьер — уровень 2 [sravni_ru]; Сбер / СберПремьер — уровень 2 [bankiros]; Сбер / СберПремьер — уровень 3 [official]; Сбер / СберПремьер — уровень 3 [official]; Сбер / СберПремьер — уровень 3 [official]; Сбер / СберПремьер — уровень 3 [pbi]; Сбер / СберПремьер — уровень 3 [sravni_ru]; Сбер / СберПремьер — уровень 3 [bankiros]; Сбер / СберПервый — уровень 4 [official]; Сбер / СберПервый — уровень 4 [official]; Сбер / СберПервый — уровень 4 [official]; Сбер / СберПервый — уровень 4 [pbi]; Сбер / СберПервый — уровень 4 [sravni_ru]; Сбер / СберПервый — уровень 4 [bankiros]; Сбер / СберПервый — уровень 5 [official]; Сбер / СберПервый — уровень 5 [official]; Сбер / СберПервый — уровень 5 [official]; Сбер / СберПервый — уровень 5 [pbi]; Сбер / СберПервый — уровень 5 [sravni_ru]; Сбер / СберПервый — уровень 5 [bankiros]; Сбер / Sber Private Banking — уровень 6 [official]; Сбер / Sber Private Banking — уровень 6 [official]; Сбер / Sber Private Banking — уровень 6 [pbi]; Сбер / Sber Private Banking — уровень 6 [sravni_ru]; Сбер / Sber Private Banking — уровень 6 [bankiros]; Т-Банк / Premium Bronze [official]; Т-Банк / Premium Bronze [pbi]; Т-Банк / Premium Silver [official]; Т-Банк / Premium Silver [pbi]; Т-Банк / Premium Gold [official]; Т-Банк / Premium Gold [pbi]; Т-Банк / Private (Diamond) [official]; Т-Банк / Private (Diamond) [pbi]; Альфа-Банк / Alfa Only — уровень 1 [official]; Альфа-Банк / Alfa Only — уровень 1 [pbi]; Альфа-Банк / Alfa Only — уровень 1 [bankiros]; Альфа-Банк / Alfa Only — уровень 2 [official]; Альфа-Банк / Alfa Only — уровень 2 [pbi]; Альфа-Банк / Alfa Only — уровень 2 [bankiros]; Альфа-Банк / Alfa Only — уровень 3 [official]; Альфа-Банк / Alfa Only — уровень 3 [pbi]; Альфа-Банк / Alfa Only — уровень 3 [bankiros]; Альфа-Банк / Alfa Only — уровень 4 [official]; Альфа-Банк / Alfa Only — уровень 4 [pbi]; Альфа-Банк / Alfa Only — уровень 4 [bankiros]; Альфа-Банк / A-Club (private) [official]; Альфа-Банк / A-Club (private) [pbi]; Альфа-Банк / A-Club (private) [bankiros]; ВТБ / Привилегия — уровень 1 [official]; ВТБ / Привилегия — уровень 1 [pbi]; ВТБ / Привилегия — уровень 1 [bankiros]; ВТБ / Привилегия — уровень 2 [official]; ВТБ / Привилегия — уровень 2 [pbi]; ВТБ / Привилегия — уровень 2 [bankiros]; ВТБ / Привилегия — уровень 3 [official]; ВТБ / Привилегия — уровень 3 [pbi]; ВТБ / Привилегия — уровень 3 [bankiros]; ВТБ / Привилегия — уровень 4 [official]; ВТБ / Привилегия — уровень 4 [pbi]; ВТБ / Привилегия — уровень 4 [bankiros]; ВТБ / Прайм+ — уровень 5 [official]; ВТБ / Прайм+ — уровень 5 [pbi]; ВТБ / Прайм+ — уровень 5 [bankiros]; ВТБ / Прайм+ — уровень 6 [official]; ВТБ / Прайм+ — уровень 6 [pbi]; ВТБ / Прайм+ — уровень 6 [bankiros]; ВТБ / Прайм+ — уровень 7 [official]; ВТБ / Прайм+ — уровень 7 [pbi]; ВТБ / Прайм+ — уровень 7 [bankiros]; ВТБ / Прайм+ — уровень 8 [official]; ВТБ / Прайм+ — уровень 8 [pbi]; ВТБ / Прайм+ — уровень 8 [bankiros]; Газпромбанк / Премиум — уровень 1 [official]; Газпромбанк / Премиум — уровень 1 [pbi]; Газпромбанк / Премиум — уровень 1 [bankiros]; Газпромбанк / Премиум — уровень 2 [official]; Газпромбанк / Премиум — уровень 2 [pbi]; Газпромбанк / Премиум — уровень 2 [bankiros]; Газпромбанк / Премиум — уровень 3 [official]; Газпромбанк / Премиум — уровень 3 [pbi]; Газпромбанк / Премиум — уровень 3 [bankiros]; Газпромбанк / Private Banking [official]; Газпромбанк / Private Banking [pbi]; Газпромбанк / Private Banking [bankiros]; Озон Банк / Ultra Bronze [official]; Озон Банк / Ultra Bronze [pbi]; Озон Банк / Ultra Silver [official]; Озон Банк / Ultra Silver [pbi]; Озон Банк / Ultra Gold [official]; Озон Банк / Ultra Gold [pbi]; Озон Банк / Ultra Platinum [official]; Озон Банк / Ultra Platinum [pbi]; Райффайзен Банк / Premium (за плату) [official]; Райффайзен Банк / Premium (за плату) [pbi]; Райффайзен Банк / Premium (за траты) [official]; Райффайзен Банк / Premium (за траты) [pbi]; Райффайзен Банк / Premium (за остаток) [official]; Райффайзен Банк / Premium (за остаток) [pbi]; HSBC / Premier [official]; HSBC / Premier Elite (экс-Jade) [official]; HSBC / Global Private Banking [official]; Citi / Citigold [official]; Citi / Citi Private Bank [official]; JPMorgan Chase / Chase Private Client [official]; JPMorgan Chase / J.P. Morgan Private Bank [official]; Bank of America / Preferred Rewards [official]; Standard Chartered / Priority Banking [official]; DBS (Сингапур) / Treasures [official]; DBS (Сингапур) / Treasures Private Client [official]; Deutsche Bank / Wealth Management [official]; BNP Paribas / Wealth Management [official]; Barclays / Premier Banking [official]; Яндекс Плюс / Яндекс Плюс [official]; premiumbanking.info (обзорная)</t>
         </is>
       </c>
     </row>
@@ -52460,7 +53026,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Сбер / СберПремьер — уровень 1 [banki_ru]: blocked_robots: запрещено robots.txt; Сбер / СберПремьер — уровень 2 [banki_ru]: blocked_robots: запрещено robots.txt; Сбер / СберПремьер — уровень 3 [banki_ru]: blocked_robots: запрещено robots.txt; Сбер / СберПервый — уровень 4 [banki_ru]: blocked_robots: запрещено robots.txt; Сбер / СберПервый — уровень 5 [banki_ru]: blocked_robots: запрещено robots.txt; Сбер / Sber Private Banking — уровень 6 [banki_ru]: blocked_robots: запрещено robots.txt; Т-Банк / Premium Bronze [banki_ru]: blocked_robots: запрещено robots.txt; Т-Банк / Premium Silver [banki_ru]: blocked_robots: запрещено robots.txt; Т-Банк / Premium Gold [banki_ru]: blocked_robots: запрещено robots.txt; Т-Банк / Private (Diamond) [banki_ru]: blocked_robots: запрещено robots.txt; Альфа-Банк / Alfa Only — уровень 1 [banki_ru]: blocked_robots: запрещено robots.txt; Альфа-Банк / Alfa Only — уровень 2 [banki_ru]: blocked_robots: запрещено robots.txt; Альфа-Банк / Alfa Only — уровень 3 [banki_ru]: blocked_robots: запрещено robots.txt; Альфа-Банк / Alfa Only — уровень 4 [banki_ru]: blocked_robots: запрещено robots.txt; Альфа-Банк / A-Club (private) [banki_ru]: blocked_robots: запрещено robots.txt; ВТБ / Привилегия — уровень 1 [banki_ru]: blocked_robots: запрещено robots.txt; ВТБ / Привилегия — уровень 2 [banki_ru]: blocked_robots: запрещено robots.txt; ВТБ / Привилегия — уровень 3 [banki_ru]: blocked_robots: запрещено robots.txt; ВТБ / Привилегия — уровень 4 [banki_ru]: blocked_robots: запрещено robots.txt; ВТБ / Прайм+ — уровень 5 [banki_ru]: blocked_robots: запрещено robots.txt; ВТБ / Прайм+ — уровень 6 [banki_ru]: blocked_robots: запрещено robots.txt; ВТБ / Прайм+ — уровень 7 [banki_ru]: blocked_robots: запрещено robots.txt; ВТБ / Прайм+ — уровень 8 [banki_ru]: blocked_robots: запрещено robots.txt; Газпромбанк / Премиум — уровень 1 [banki_ru]: blocked_robots: запрещено robots.txt; Газпромбанк / Премиум — уровень 2 [banki_ru]: blocked_robots: запрещено robots.txt; Газпромбанк / Премиум — уровень 3 [banki_ru]: blocked_robots: запрещено robots.txt; Газпромбанк / Private Banking [banki_ru]: blocked_robots: запрещено robots.txt; Райффайзен Банк / Premium (за плату) [banki_ru]: blocked_robots: запрещено robots.txt; Райффайзен Банк / Premium (за траты) [banki_ru]: blocked_robots: запрещено robots.txt; Райффайзен Банк / Premium (за остаток) [banki_ru]: blocked_robots: запрещено robots.txt; Citi / Citigold Private Client [official]: js_required: страница требует JS-рендеринга (playwright недоступен); Bank of America / BofA Private Bank [official]: js_required: страница требует JS-рендеринга (playwright недоступен); UBS / Global Wealth Management [official]: unavailable: ConnectionError: ('Connection aborted.', ConnectionResetError(54, 'Connection reset by peer')); Emirates NBD / Priority Banking [official]: unavailable: HTTP 403; Ozon Premium / Ozon Premium [official]: unavailable: HTTP 403; Wildberries (Клуб покупателей) / WB Клуб [official]: unavailable: HTTP 498; Frank RG (рейтинги Premium/Private Banking): unavailable: ConnectionError: ('Connection aborted.', ConnectionResetError(54, 'Connection reset by peer'))</t>
+          <t>Сбер / СберПремьер — уровень 1 [banki_ru]: blocked_robots: запрещено robots.txt; Сбер / СберПремьер — уровень 2 [banki_ru]: blocked_robots: запрещено robots.txt; Сбер / СберПремьер — уровень 3 [banki_ru]: blocked_robots: запрещено robots.txt; Сбер / СберПервый — уровень 4 [banki_ru]: blocked_robots: запрещено robots.txt; Сбер / СберПервый — уровень 5 [banki_ru]: blocked_robots: запрещено robots.txt; Сбер / Sber Private Banking — уровень 6 [banki_ru]: blocked_robots: запрещено robots.txt; Т-Банк / Premium Bronze [banki_ru]: blocked_robots: запрещено robots.txt; Т-Банк / Premium Silver [banki_ru]: blocked_robots: запрещено robots.txt; Т-Банк / Premium Gold [banki_ru]: blocked_robots: запрещено robots.txt; Т-Банк / Private (Diamond) [banki_ru]: blocked_robots: запрещено robots.txt; Альфа-Банк / Alfa Only — уровень 1 [banki_ru]: blocked_robots: запрещено robots.txt; Альфа-Банк / Alfa Only — уровень 2 [banki_ru]: blocked_robots: запрещено robots.txt; Альфа-Банк / Alfa Only — уровень 3 [banki_ru]: blocked_robots: запрещено robots.txt; Альфа-Банк / Alfa Only — уровень 4 [banki_ru]: blocked_robots: запрещено robots.txt; Альфа-Банк / A-Club (private) [banki_ru]: blocked_robots: запрещено robots.txt; ВТБ / Привилегия — уровень 1 [banki_ru]: blocked_robots: запрещено robots.txt; ВТБ / Привилегия — уровень 2 [banki_ru]: blocked_robots: запрещено robots.txt; ВТБ / Привилегия — уровень 3 [banki_ru]: blocked_robots: запрещено robots.txt; ВТБ / Привилегия — уровень 4 [banki_ru]: blocked_robots: запрещено robots.txt; ВТБ / Прайм+ — уровень 5 [banki_ru]: blocked_robots: запрещено robots.txt; ВТБ / Прайм+ — уровень 6 [banki_ru]: blocked_robots: запрещено robots.txt; ВТБ / Прайм+ — уровень 7 [banki_ru]: blocked_robots: запрещено robots.txt; ВТБ / Прайм+ — уровень 8 [banki_ru]: blocked_robots: запрещено robots.txt; Газпромбанк / Премиум — уровень 1 [banki_ru]: blocked_robots: запрещено robots.txt; Газпромбанк / Премиум — уровень 2 [banki_ru]: blocked_robots: запрещено robots.txt; Газпромбанк / Премиум — уровень 3 [banki_ru]: blocked_robots: запрещено robots.txt; Газпромбанк / Private Banking [banki_ru]: blocked_robots: запрещено robots.txt; Райффайзен Банк / Premium (за плату) [banki_ru]: blocked_robots: запрещено robots.txt; Райффайзен Банк / Premium (за траты) [banki_ru]: blocked_robots: запрещено robots.txt; Райффайзен Банк / Premium (за остаток) [banki_ru]: blocked_robots: запрещено robots.txt; Citi / Citigold Private Client [official]: js_required: страница требует JS-рендеринга (playwright недоступен); Bank of America / BofA Private Bank [official]: js_required: страница требует JS-рендеринга (playwright недоступен); UBS / Global Wealth Management [official]: unavailable: ConnectionError: ('Connection aborted.', ConnectionResetError(54, 'Connection reset by peer')); Standard Chartered / Priority Private [official]: unavailable: HTTP 404; Emirates NBD / Priority Banking [official]: unavailable: HTTP 403; Ozon Premium / Ozon Premium [official]: unavailable: HTTP 403; Wildberries (Клуб покупателей) / WB Клуб [official]: unavailable: HTTP 498; Frank RG (рейтинги Premium/Private Banking): unavailable: ConnectionError: ('Connection aborted.', ConnectionResetError(54, 'Connection reset by peer'))</t>
         </is>
       </c>
     </row>
@@ -52472,7 +53038,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>529</t>
+          <t>542</t>
         </is>
       </c>
     </row>
@@ -52484,7 +53050,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>38</t>
         </is>
       </c>
     </row>
@@ -52496,7 +53062,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>2026-07-02T15:22:09</t>
+          <t>2026-07-02T15:49:02</t>
         </is>
       </c>
     </row>
@@ -52520,7 +53086,7 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Сбер / СберПремьер — уровень 1 [official]; Сбер / СберПремьер — уровень 1 [official]; Сбер / СберПремьер — уровень 1 [official]; Сбер / СберПремьер — уровень 1 [pbi]; Сбер / СберПремьер — уровень 1 [sravni_ru]; Сбер / СберПремьер — уровень 1 [bankiros]; Сбер / СберПремьер — уровень 2 [official]; Сбер / СберПремьер — уровень 2 [official]; Сбер / СберПремьер — уровень 2 [official]; Сбер / СберПремьер — уровень 2 [pbi]; Сбер / СберПремьер — уровень 2 [sravni_ru]; Сбер / СберПремьер — уровень 2 [bankiros]; Сбер / СберПремьер — уровень 3 [official]; Сбер / СберПремьер — уровень 3 [official]; Сбер / СберПремьер — уровень 3 [official]; Сбер / СберПремьер — уровень 3 [pbi]; Сбер / СберПремьер — уровень 3 [sravni_ru]; Сбер / СберПремьер — уровень 3 [bankiros]; Сбер / СберПервый — уровень 4 [official]; Сбер / СберПервый — уровень 4 [official]; Сбер / СберПервый — уровень 4 [official]; Сбер / СберПервый — уровень 4 [pbi]; Сбер / СберПервый — уровень 4 [sravni_ru]; Сбер / СберПервый — уровень 4 [bankiros]; Сбер / СберПервый — уровень 5 [official]; Сбер / СберПервый — уровень 5 [official]; Сбер / СберПервый — уровень 5 [official]; Сбер / СберПервый — уровень 5 [pbi]; Сбер / СберПервый — уровень 5 [sravni_ru]; Сбер / СберПервый — уровень 5 [bankiros]; Сбер / Sber Private Banking — уровень 6 [official]; Сбер / Sber Private Banking — уровень 6 [official]; Сбер / Sber Private Banking — уровень 6 [pbi]; Сбер / Sber Private Banking — уровень 6 [sravni_ru]; Сбер / Sber Private Banking — уровень 6 [bankiros]; Т-Банк / Premium Bronze [official]; Т-Банк / Premium Bronze [pbi]; Т-Банк / Premium Silver [official]; Т-Банк / Premium Silver [pbi]; Т-Банк / Premium Gold [official]; Т-Банк / Premium Gold [pbi]; Т-Банк / Private (Diamond) [official]; Т-Банк / Private (Diamond) [pbi]; Альфа-Банк / Alfa Only — уровень 1 [official]; Альфа-Банк / Alfa Only — уровень 1 [pbi]; Альфа-Банк / Alfa Only — уровень 1 [bankiros]; Альфа-Банк / Alfa Only — уровень 2 [official]; Альфа-Банк / Alfa Only — уровень 2 [pbi]; Альфа-Банк / Alfa Only — уровень 2 [bankiros]; Альфа-Банк / Alfa Only — уровень 3 [official]; Альфа-Банк / Alfa Only — уровень 3 [pbi]; Альфа-Банк / Alfa Only — уровень 3 [bankiros]; Альфа-Банк / Alfa Only — уровень 4 [official]; Альфа-Банк / Alfa Only — уровень 4 [pbi]; Альфа-Банк / Alfa Only — уровень 4 [bankiros]; Альфа-Банк / A-Club (private) [official]; Альфа-Банк / A-Club (private) [pbi]; Альфа-Банк / A-Club (private) [bankiros]; ВТБ / Привилегия — уровень 1 [official]; ВТБ / Привилегия — уровень 1 [pbi]; ВТБ / Привилегия — уровень 1 [bankiros]; ВТБ / Привилегия — уровень 2 [official]; ВТБ / Привилегия — уровень 2 [pbi]; ВТБ / Привилегия — уровень 2 [bankiros]; ВТБ / Привилегия — уровень 3 [official]; ВТБ / Привилегия — уровень 3 [pbi]; ВТБ / Привилегия — уровень 3 [bankiros]; ВТБ / Привилегия — уровень 4 [official]; ВТБ / Привилегия — уровень 4 [pbi]; ВТБ / Привилегия — уровень 4 [bankiros]; ВТБ / Прайм+ — уровень 5 [official]; ВТБ / Прайм+ — уровень 5 [pbi]; ВТБ / Прайм+ — уровень 5 [bankiros]; ВТБ / Прайм+ — уровень 6 [official]; ВТБ / Прайм+ — уровень 6 [pbi]; ВТБ / Прайм+ — уровень 6 [bankiros]; ВТБ / Прайм+ — уровень 7 [official]; ВТБ / Прайм+ — уровень 7 [pbi]; ВТБ / Прайм+ — уровень 7 [bankiros]; ВТБ / Прайм+ — уровень 8 [official]; ВТБ / Прайм+ — уровень 8 [pbi]; ВТБ / Прайм+ — уровень 8 [bankiros]; Газпромбанк / Премиум — уровень 1 [official]; Газпромбанк / Премиум — уровень 1 [pbi]; Газпромбанк / Премиум — уровень 1 [bankiros]; Газпромбанк / Премиум — уровень 2 [official]; Газпромбанк / Премиум — уровень 2 [pbi]; Газпромбанк / Премиум — уровень 2 [bankiros]; Газпромбанк / Премиум — уровень 3 [official]; Газпромбанк / Премиум — уровень 3 [pbi]; Газпромбанк / Премиум — уровень 3 [bankiros]; Газпромбанк / Private Banking [official]; Газпромбанк / Private Banking [pbi]; Газпромбанк / Private Banking [bankiros]; Озон Банк / Ultra Bronze [official]; Озон Банк / Ultra Bronze [pbi]; Озон Банк / Ultra Silver [official]; Озон Банк / Ultra Silver [pbi]; Озон Банк / Ultra Gold [official]; Озон Банк / Ultra Gold [pbi]; Озон Банк / Ultra Platinum [official]; Озон Банк / Ultra Platinum [pbi]; Райффайзен Банк / Premium (за плату) [official]; Райффайзен Банк / Premium (за плату) [pbi]; Райффайзен Банк / Premium (за траты) [official]; Райффайзен Банк / Premium (за траты) [pbi]; Райффайзен Банк / Premium (за остаток) [official]; Райффайзен Банк / Premium (за остаток) [pbi]; Яндекс Плюс / Яндекс Плюс [official]; premiumbanking.info (обзорная)</t>
+          <t>Сбер / СберПремьер — уровень 1 [official]; Сбер / СберПремьер — уровень 1 [official]; Сбер / СберПремьер — уровень 1 [official]; Сбер / СберПремьер — уровень 1 [pbi]; Сбер / СберПремьер — уровень 1 [sravni_ru]; Сбер / СберПремьер — уровень 1 [bankiros]; Сбер / СберПремьер — уровень 2 [official]; Сбер / СберПремьер — уровень 2 [official]; Сбер / СберПремьер — уровень 2 [official]; Сбер / СберПремьер — уровень 2 [pbi]; Сбер / СберПремьер — уровень 2 [sravni_ru]; Сбер / СберПремьер — уровень 2 [bankiros]; Сбер / СберПремьер — уровень 3 [official]; Сбер / СберПремьер — уровень 3 [official]; Сбер / СберПремьер — уровень 3 [official]; Сбер / СберПремьер — уровень 3 [pbi]; Сбер / СберПремьер — уровень 3 [sravni_ru]; Сбер / СберПремьер — уровень 3 [bankiros]; Сбер / СберПервый — уровень 4 [official]; Сбер / СберПервый — уровень 4 [official]; Сбер / СберПервый — уровень 4 [official]; Сбер / СберПервый — уровень 4 [pbi]; Сбер / СберПервый — уровень 4 [sravni_ru]; Сбер / СберПервый — уровень 4 [bankiros]; Сбер / СберПервый — уровень 5 [official]; Сбер / СберПервый — уровень 5 [official]; Сбер / СберПервый — уровень 5 [official]; Сбер / СберПервый — уровень 5 [pbi]; Сбер / СберПервый — уровень 5 [sravni_ru]; Сбер / СберПервый — уровень 5 [bankiros]; Сбер / Sber Private Banking — уровень 6 [official]; Сбер / Sber Private Banking — уровень 6 [official]; Сбер / Sber Private Banking — уровень 6 [pbi]; Сбер / Sber Private Banking — уровень 6 [sravni_ru]; Сбер / Sber Private Banking — уровень 6 [bankiros]; Т-Банк / Premium Bronze [official]; Т-Банк / Premium Bronze [pbi]; Т-Банк / Premium Silver [official]; Т-Банк / Premium Silver [pbi]; Т-Банк / Premium Gold [official]; Т-Банк / Premium Gold [pbi]; Т-Банк / Private (Diamond) [official]; Т-Банк / Private (Diamond) [pbi]; Альфа-Банк / Alfa Only — уровень 1 [official]; Альфа-Банк / Alfa Only — уровень 1 [pbi]; Альфа-Банк / Alfa Only — уровень 1 [bankiros]; Альфа-Банк / Alfa Only — уровень 2 [official]; Альфа-Банк / Alfa Only — уровень 2 [pbi]; Альфа-Банк / Alfa Only — уровень 2 [bankiros]; Альфа-Банк / Alfa Only — уровень 3 [official]; Альфа-Банк / Alfa Only — уровень 3 [pbi]; Альфа-Банк / Alfa Only — уровень 3 [bankiros]; Альфа-Банк / Alfa Only — уровень 4 [official]; Альфа-Банк / Alfa Only — уровень 4 [pbi]; Альфа-Банк / Alfa Only — уровень 4 [bankiros]; Альфа-Банк / A-Club (private) [official]; Альфа-Банк / A-Club (private) [pbi]; Альфа-Банк / A-Club (private) [bankiros]; ВТБ / Привилегия — уровень 1 [official]; ВТБ / Привилегия — уровень 1 [pbi]; ВТБ / Привилегия — уровень 1 [bankiros]; ВТБ / Привилегия — уровень 2 [official]; ВТБ / Привилегия — уровень 2 [pbi]; ВТБ / Привилегия — уровень 2 [bankiros]; ВТБ / Привилегия — уровень 3 [official]; ВТБ / Привилегия — уровень 3 [pbi]; ВТБ / Привилегия — уровень 3 [bankiros]; ВТБ / Привилегия — уровень 4 [official]; ВТБ / Привилегия — уровень 4 [pbi]; ВТБ / Привилегия — уровень 4 [bankiros]; ВТБ / Прайм+ — уровень 5 [official]; ВТБ / Прайм+ — уровень 5 [pbi]; ВТБ / Прайм+ — уровень 5 [bankiros]; ВТБ / Прайм+ — уровень 6 [official]; ВТБ / Прайм+ — уровень 6 [pbi]; ВТБ / Прайм+ — уровень 6 [bankiros]; ВТБ / Прайм+ — уровень 7 [official]; ВТБ / Прайм+ — уровень 7 [pbi]; ВТБ / Прайм+ — уровень 7 [bankiros]; ВТБ / Прайм+ — уровень 8 [official]; ВТБ / Прайм+ — уровень 8 [pbi]; ВТБ / Прайм+ — уровень 8 [bankiros]; Газпромбанк / Премиум — уровень 1 [official]; Газпромбанк / Премиум — уровень 1 [pbi]; Газпромбанк / Премиум — уровень 1 [bankiros]; Газпромбанк / Премиум — уровень 2 [official]; Газпромбанк / Премиум — уровень 2 [pbi]; Газпромбанк / Премиум — уровень 2 [bankiros]; Газпромбанк / Премиум — уровень 3 [official]; Газпромбанк / Премиум — уровень 3 [pbi]; Газпромбанк / Премиум — уровень 3 [bankiros]; Газпромбанк / Private Banking [official]; Газпромбанк / Private Banking [pbi]; Газпромбанк / Private Banking [bankiros]; Озон Банк / Ultra Bronze [official]; Озон Банк / Ultra Bronze [pbi]; Озон Банк / Ultra Silver [official]; Озон Банк / Ultra Silver [pbi]; Озон Банк / Ultra Gold [official]; Озон Банк / Ultra Gold [pbi]; Озон Банк / Ultra Platinum [official]; Озон Банк / Ultra Platinum [pbi]; Райффайзен Банк / Premium (за плату) [official]; Райффайзен Банк / Premium (за плату) [pbi]; Райффайзен Банк / Premium (за траты) [official]; Райффайзен Банк / Premium (за траты) [pbi]; Райффайзен Банк / Premium (за остаток) [official]; Райффайзен Банк / Premium (за остаток) [pbi]; HSBC / Premier [official]; HSBC / Premier Elite (экс-Jade) [official]; HSBC / Global Private Banking [official]; Citi / Citigold [official]; Citi / Citi Private Bank [official]; JPMorgan Chase / Chase Private Client [official]; JPMorgan Chase / J.P. Morgan Private Bank [official]; Bank of America / Preferred Rewards [official]; Standard Chartered / Priority Banking [official]; Standard Chartered / Priority Private [official]; DBS (Сингапур) / Treasures [official]; DBS (Сингапур) / Treasures Private Client [official]; Deutsche Bank / Wealth Management [official]; BNP Paribas / Wealth Management [official]; Barclays / Premier Banking [official]; Яндекс Плюс / Яндекс Плюс [official]; premiumbanking.info (обзорная)</t>
         </is>
       </c>
     </row>
@@ -52532,7 +53098,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Сбер / СберПремьер — уровень 1 [banki_ru]: blocked_robots: запрещено robots.txt; Сбер / СберПремьер — уровень 2 [banki_ru]: blocked_robots: запрещено robots.txt; Сбер / СберПремьер — уровень 3 [banki_ru]: blocked_robots: запрещено robots.txt; Сбер / СберПервый — уровень 4 [banki_ru]: blocked_robots: запрещено robots.txt; Сбер / СберПервый — уровень 5 [banki_ru]: blocked_robots: запрещено robots.txt; Сбер / Sber Private Banking — уровень 6 [banki_ru]: blocked_robots: запрещено robots.txt; Т-Банк / Premium Bronze [banki_ru]: blocked_robots: запрещено robots.txt; Т-Банк / Premium Silver [banki_ru]: blocked_robots: запрещено robots.txt; Т-Банк / Premium Gold [banki_ru]: blocked_robots: запрещено robots.txt; Т-Банк / Private (Diamond) [banki_ru]: blocked_robots: запрещено robots.txt; Альфа-Банк / Alfa Only — уровень 1 [banki_ru]: blocked_robots: запрещено robots.txt; Альфа-Банк / Alfa Only — уровень 2 [banki_ru]: blocked_robots: запрещено robots.txt; Альфа-Банк / Alfa Only — уровень 3 [banki_ru]: blocked_robots: запрещено robots.txt; Альфа-Банк / Alfa Only — уровень 4 [banki_ru]: blocked_robots: запрещено robots.txt; Альфа-Банк / A-Club (private) [banki_ru]: blocked_robots: запрещено robots.txt; ВТБ / Привилегия — уровень 1 [banki_ru]: blocked_robots: запрещено robots.txt; ВТБ / Привилегия — уровень 2 [banki_ru]: blocked_robots: запрещено robots.txt; ВТБ / Привилегия — уровень 3 [banki_ru]: blocked_robots: запрещено robots.txt; ВТБ / Привилегия — уровень 4 [banki_ru]: blocked_robots: запрещено robots.txt; ВТБ / Прайм+ — уровень 5 [banki_ru]: blocked_robots: запрещено robots.txt; ВТБ / Прайм+ — уровень 6 [banki_ru]: blocked_robots: запрещено robots.txt; ВТБ / Прайм+ — уровень 7 [banki_ru]: blocked_robots: запрещено robots.txt; ВТБ / Прайм+ — уровень 8 [banki_ru]: blocked_robots: запрещено robots.txt; Газпромбанк / Премиум — уровень 1 [banki_ru]: blocked_robots: запрещено robots.txt; Газпромбанк / Премиум — уровень 2 [banki_ru]: blocked_robots: запрещено robots.txt; Газпромбанк / Премиум — уровень 3 [banki_ru]: blocked_robots: запрещено robots.txt; Газпромбанк / Private Banking [banki_ru]: blocked_robots: запрещено robots.txt; Райффайзен Банк / Premium (за плату) [banki_ru]: blocked_robots: запрещено robots.txt; Райффайзен Банк / Premium (за траты) [banki_ru]: blocked_robots: запрещено robots.txt; Райффайзен Банк / Premium (за остаток) [banki_ru]: blocked_robots: запрещено robots.txt; Ozon Premium / Ozon Premium [official]: unavailable: HTTP 403; Wildberries (Клуб покупателей) / WB Клуб [official]: unavailable: HTTP 498; Frank RG (рейтинги Premium/Private Banking): unavailable: ConnectionError: ('Connection aborted.', ConnectionResetError(54, 'Connection reset by peer'))</t>
+          <t>Сбер / СберПремьер — уровень 1 [banki_ru]: blocked_robots: запрещено robots.txt; Сбер / СберПремьер — уровень 2 [banki_ru]: blocked_robots: запрещено robots.txt; Сбер / СберПремьер — уровень 3 [banki_ru]: blocked_robots: запрещено robots.txt; Сбер / СберПервый — уровень 4 [banki_ru]: blocked_robots: запрещено robots.txt; Сбер / СберПервый — уровень 5 [banki_ru]: blocked_robots: запрещено robots.txt; Сбер / Sber Private Banking — уровень 6 [banki_ru]: blocked_robots: запрещено robots.txt; Т-Банк / Premium Bronze [banki_ru]: blocked_robots: запрещено robots.txt; Т-Банк / Premium Silver [banki_ru]: blocked_robots: запрещено robots.txt; Т-Банк / Premium Gold [banki_ru]: blocked_robots: запрещено robots.txt; Т-Банк / Private (Diamond) [banki_ru]: blocked_robots: запрещено robots.txt; Альфа-Банк / Alfa Only — уровень 1 [banki_ru]: blocked_robots: запрещено robots.txt; Альфа-Банк / Alfa Only — уровень 2 [banki_ru]: blocked_robots: запрещено robots.txt; Альфа-Банк / Alfa Only — уровень 3 [banki_ru]: blocked_robots: запрещено robots.txt; Альфа-Банк / Alfa Only — уровень 4 [banki_ru]: blocked_robots: запрещено robots.txt; Альфа-Банк / A-Club (private) [banki_ru]: blocked_robots: запрещено robots.txt; ВТБ / Привилегия — уровень 1 [banki_ru]: blocked_robots: запрещено robots.txt; ВТБ / Привилегия — уровень 2 [banki_ru]: blocked_robots: запрещено robots.txt; ВТБ / Привилегия — уровень 3 [banki_ru]: blocked_robots: запрещено robots.txt; ВТБ / Привилегия — уровень 4 [banki_ru]: blocked_robots: запрещено robots.txt; ВТБ / Прайм+ — уровень 5 [banki_ru]: blocked_robots: запрещено robots.txt; ВТБ / Прайм+ — уровень 6 [banki_ru]: blocked_robots: запрещено robots.txt; ВТБ / Прайм+ — уровень 7 [banki_ru]: blocked_robots: запрещено robots.txt; ВТБ / Прайм+ — уровень 8 [banki_ru]: blocked_robots: запрещено robots.txt; Газпромбанк / Премиум — уровень 1 [banki_ru]: blocked_robots: запрещено robots.txt; Газпромбанк / Премиум — уровень 2 [banki_ru]: blocked_robots: запрещено robots.txt; Газпромбанк / Премиум — уровень 3 [banki_ru]: blocked_robots: запрещено robots.txt; Газпромбанк / Private Banking [banki_ru]: blocked_robots: запрещено robots.txt; Райффайзен Банк / Premium (за плату) [banki_ru]: blocked_robots: запрещено robots.txt; Райффайзен Банк / Premium (за траты) [banki_ru]: blocked_robots: запрещено robots.txt; Райффайзен Банк / Premium (за остаток) [banki_ru]: blocked_robots: запрещено robots.txt; Citi / Citigold Private Client [official]: js_required: страница требует JS-рендеринга (playwright недоступен); Bank of America / BofA Private Bank [official]: js_required: страница требует JS-рендеринга (playwright недоступен); UBS / Global Wealth Management [official]: unavailable: ConnectionError: ('Connection aborted.', ConnectionResetError(54, 'Connection reset by peer')); Emirates NBD / Priority Banking [official]: unavailable: HTTP 403; Ozon Premium / Ozon Premium [official]: unavailable: HTTP 403; Wildberries (Клуб покупателей) / WB Клуб [official]: unavailable: HTTP 498; Frank RG (рейтинги Premium/Private Banking): unavailable: ConnectionError: ('Connection aborted.', ConnectionResetError(54, 'Connection reset by peer'))</t>
         </is>
       </c>
     </row>
@@ -52544,7 +53110,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>477</t>
+          <t>529</t>
         </is>
       </c>
     </row>
@@ -52556,7 +53122,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>45</t>
         </is>
       </c>
     </row>
@@ -52568,7 +53134,7 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>2026-07-02T15:19:39</t>
+          <t>2026-07-02T15:22:09</t>
         </is>
       </c>
     </row>
@@ -52580,7 +53146,7 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>lifestyle</t>
+          <t>all</t>
         </is>
       </c>
     </row>
@@ -52592,7 +53158,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Яндекс Плюс / Яндекс Плюс [official]</t>
+          <t>Сбер / СберПремьер — уровень 1 [official]; Сбер / СберПремьер — уровень 1 [official]; Сбер / СберПремьер — уровень 1 [official]; Сбер / СберПремьер — уровень 1 [pbi]; Сбер / СберПремьер — уровень 1 [sravni_ru]; Сбер / СберПремьер — уровень 1 [bankiros]; Сбер / СберПремьер — уровень 2 [official]; Сбер / СберПремьер — уровень 2 [official]; Сбер / СберПремьер — уровень 2 [official]; Сбер / СберПремьер — уровень 2 [pbi]; Сбер / СберПремьер — уровень 2 [sravni_ru]; Сбер / СберПремьер — уровень 2 [bankiros]; Сбер / СберПремьер — уровень 3 [official]; Сбер / СберПремьер — уровень 3 [official]; Сбер / СберПремьер — уровень 3 [official]; Сбер / СберПремьер — уровень 3 [pbi]; Сбер / СберПремьер — уровень 3 [sravni_ru]; Сбер / СберПремьер — уровень 3 [bankiros]; Сбер / СберПервый — уровень 4 [official]; Сбер / СберПервый — уровень 4 [official]; Сбер / СберПервый — уровень 4 [official]; Сбер / СберПервый — уровень 4 [pbi]; Сбер / СберПервый — уровень 4 [sravni_ru]; Сбер / СберПервый — уровень 4 [bankiros]; Сбер / СберПервый — уровень 5 [official]; Сбер / СберПервый — уровень 5 [official]; Сбер / СберПервый — уровень 5 [official]; Сбер / СберПервый — уровень 5 [pbi]; Сбер / СберПервый — уровень 5 [sravni_ru]; Сбер / СберПервый — уровень 5 [bankiros]; Сбер / Sber Private Banking — уровень 6 [official]; Сбер / Sber Private Banking — уровень 6 [official]; Сбер / Sber Private Banking — уровень 6 [pbi]; Сбер / Sber Private Banking — уровень 6 [sravni_ru]; Сбер / Sber Private Banking — уровень 6 [bankiros]; Т-Банк / Premium Bronze [official]; Т-Банк / Premium Bronze [pbi]; Т-Банк / Premium Silver [official]; Т-Банк / Premium Silver [pbi]; Т-Банк / Premium Gold [official]; Т-Банк / Premium Gold [pbi]; Т-Банк / Private (Diamond) [official]; Т-Банк / Private (Diamond) [pbi]; Альфа-Банк / Alfa Only — уровень 1 [official]; Альфа-Банк / Alfa Only — уровень 1 [pbi]; Альфа-Банк / Alfa Only — уровень 1 [bankiros]; Альфа-Банк / Alfa Only — уровень 2 [official]; Альфа-Банк / Alfa Only — уровень 2 [pbi]; Альфа-Банк / Alfa Only — уровень 2 [bankiros]; Альфа-Банк / Alfa Only — уровень 3 [official]; Альфа-Банк / Alfa Only — уровень 3 [pbi]; Альфа-Банк / Alfa Only — уровень 3 [bankiros]; Альфа-Банк / Alfa Only — уровень 4 [official]; Альфа-Банк / Alfa Only — уровень 4 [pbi]; Альфа-Банк / Alfa Only — уровень 4 [bankiros]; Альфа-Банк / A-Club (private) [official]; Альфа-Банк / A-Club (private) [pbi]; Альфа-Банк / A-Club (private) [bankiros]; ВТБ / Привилегия — уровень 1 [official]; ВТБ / Привилегия — уровень 1 [pbi]; ВТБ / Привилегия — уровень 1 [bankiros]; ВТБ / Привилегия — уровень 2 [official]; ВТБ / Привилегия — уровень 2 [pbi]; ВТБ / Привилегия — уровень 2 [bankiros]; ВТБ / Привилегия — уровень 3 [official]; ВТБ / Привилегия — уровень 3 [pbi]; ВТБ / Привилегия — уровень 3 [bankiros]; ВТБ / Привилегия — уровень 4 [official]; ВТБ / Привилегия — уровень 4 [pbi]; ВТБ / Привилегия — уровень 4 [bankiros]; ВТБ / Прайм+ — уровень 5 [official]; ВТБ / Прайм+ — уровень 5 [pbi]; ВТБ / Прайм+ — уровень 5 [bankiros]; ВТБ / Прайм+ — уровень 6 [official]; ВТБ / Прайм+ — уровень 6 [pbi]; ВТБ / Прайм+ — уровень 6 [bankiros]; ВТБ / Прайм+ — уровень 7 [official]; ВТБ / Прайм+ — уровень 7 [pbi]; ВТБ / Прайм+ — уровень 7 [bankiros]; ВТБ / Прайм+ — уровень 8 [official]; ВТБ / Прайм+ — уровень 8 [pbi]; ВТБ / Прайм+ — уровень 8 [bankiros]; Газпромбанк / Премиум — уровень 1 [official]; Газпромбанк / Премиум — уровень 1 [pbi]; Газпромбанк / Премиум — уровень 1 [bankiros]; Газпромбанк / Премиум — уровень 2 [official]; Газпромбанк / Премиум — уровень 2 [pbi]; Газпромбанк / Премиум — уровень 2 [bankiros]; Газпромбанк / Премиум — уровень 3 [official]; Газпромбанк / Премиум — уровень 3 [pbi]; Газпромбанк / Премиум — уровень 3 [bankiros]; Газпромбанк / Private Banking [official]; Газпромбанк / Private Banking [pbi]; Газпромбанк / Private Banking [bankiros]; Озон Банк / Ultra Bronze [official]; Озон Банк / Ultra Bronze [pbi]; Озон Банк / Ultra Silver [official]; Озон Банк / Ultra Silver [pbi]; Озон Банк / Ultra Gold [official]; Озон Банк / Ultra Gold [pbi]; Озон Банк / Ultra Platinum [official]; Озон Банк / Ultra Platinum [pbi]; Райффайзен Банк / Premium (за плату) [official]; Райффайзен Банк / Premium (за плату) [pbi]; Райффайзен Банк / Premium (за траты) [official]; Райффайзен Банк / Premium (за траты) [pbi]; Райффайзен Банк / Premium (за остаток) [official]; Райффайзен Банк / Premium (за остаток) [pbi]; Яндекс Плюс / Яндекс Плюс [official]; premiumbanking.info (обзорная)</t>
         </is>
       </c>
     </row>
@@ -52604,7 +53170,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Ozon Premium / Ozon Premium [official]: unavailable: HTTP 403; Wildberries (Клуб покупателей) / WB Клуб [official]: unavailable: HTTP 498</t>
+          <t>Сбер / СберПремьер — уровень 1 [banki_ru]: blocked_robots: запрещено robots.txt; Сбер / СберПремьер — уровень 2 [banki_ru]: blocked_robots: запрещено robots.txt; Сбер / СберПремьер — уровень 3 [banki_ru]: blocked_robots: запрещено robots.txt; Сбер / СберПервый — уровень 4 [banki_ru]: blocked_robots: запрещено robots.txt; Сбер / СберПервый — уровень 5 [banki_ru]: blocked_robots: запрещено robots.txt; Сбер / Sber Private Banking — уровень 6 [banki_ru]: blocked_robots: запрещено robots.txt; Т-Банк / Premium Bronze [banki_ru]: blocked_robots: запрещено robots.txt; Т-Банк / Premium Silver [banki_ru]: blocked_robots: запрещено robots.txt; Т-Банк / Premium Gold [banki_ru]: blocked_robots: запрещено robots.txt; Т-Банк / Private (Diamond) [banki_ru]: blocked_robots: запрещено robots.txt; Альфа-Банк / Alfa Only — уровень 1 [banki_ru]: blocked_robots: запрещено robots.txt; Альфа-Банк / Alfa Only — уровень 2 [banki_ru]: blocked_robots: запрещено robots.txt; Альфа-Банк / Alfa Only — уровень 3 [banki_ru]: blocked_robots: запрещено robots.txt; Альфа-Банк / Alfa Only — уровень 4 [banki_ru]: blocked_robots: запрещено robots.txt; Альфа-Банк / A-Club (private) [banki_ru]: blocked_robots: запрещено robots.txt; ВТБ / Привилегия — уровень 1 [banki_ru]: blocked_robots: запрещено robots.txt; ВТБ / Привилегия — уровень 2 [banki_ru]: blocked_robots: запрещено robots.txt; ВТБ / Привилегия — уровень 3 [banki_ru]: blocked_robots: запрещено robots.txt; ВТБ / Привилегия — уровень 4 [banki_ru]: blocked_robots: запрещено robots.txt; ВТБ / Прайм+ — уровень 5 [banki_ru]: blocked_robots: запрещено robots.txt; ВТБ / Прайм+ — уровень 6 [banki_ru]: blocked_robots: запрещено robots.txt; ВТБ / Прайм+ — уровень 7 [banki_ru]: blocked_robots: запрещено robots.txt; ВТБ / Прайм+ — уровень 8 [banki_ru]: blocked_robots: запрещено robots.txt; Газпромбанк / Премиум — уровень 1 [banki_ru]: blocked_robots: запрещено robots.txt; Газпромбанк / Премиум — уровень 2 [banki_ru]: blocked_robots: запрещено robots.txt; Газпромбанк / Премиум — уровень 3 [banki_ru]: blocked_robots: запрещено robots.txt; Газпромбанк / Private Banking [banki_ru]: blocked_robots: запрещено robots.txt; Райффайзен Банк / Premium (за плату) [banki_ru]: blocked_robots: запрещено robots.txt; Райффайзен Банк / Premium (за траты) [banki_ru]: blocked_robots: запрещено robots.txt; Райффайзен Банк / Premium (за остаток) [banki_ru]: blocked_robots: запрещено robots.txt; Ozon Premium / Ozon Premium [official]: unavailable: HTTP 403; Wildberries (Клуб покупателей) / WB Клуб [official]: unavailable: HTTP 498; Frank RG (рейтинги Premium/Private Banking): unavailable: ConnectionError: ('Connection aborted.', ConnectionResetError(54, 'Connection reset by peer'))</t>
         </is>
       </c>
     </row>
@@ -52616,7 +53182,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>477</t>
         </is>
       </c>
     </row>
@@ -52628,7 +53194,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -52640,7 +53206,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>2026-07-02T15:19:28</t>
+          <t>2026-07-02T15:19:39</t>
         </is>
       </c>
     </row>
@@ -52652,7 +53218,7 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>bank</t>
+          <t>lifestyle</t>
         </is>
       </c>
     </row>
@@ -52664,7 +53230,7 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Озон Банк / Ultra Bronze [official]; Озон Банк / Ultra Bronze [pbi]; Озон Банк / Ultra Silver [official]; Озон Банк / Ultra Silver [pbi]; Озон Банк / Ultra Gold [official]; Озон Банк / Ultra Gold [pbi]; Озон Банк / Ultra Platinum [official]; Озон Банк / Ultra Platinum [pbi]</t>
+          <t>Яндекс Плюс / Яндекс Плюс [official]</t>
         </is>
       </c>
     </row>
@@ -52676,7 +53242,7 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Ozon Premium / Ozon Premium [official]: unavailable: HTTP 403; Wildberries (Клуб покупателей) / WB Клуб [official]: unavailable: HTTP 498</t>
         </is>
       </c>
     </row>
@@ -52688,7 +53254,7 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>17</t>
         </is>
       </c>
     </row>
@@ -52700,7 +53266,7 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -52712,7 +53278,7 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>2026-07-02T15:19:07</t>
+          <t>2026-07-02T15:19:28</t>
         </is>
       </c>
     </row>
@@ -52736,7 +53302,7 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>Альфа-Банк / Alfa Only — уровень 1 [official]; Альфа-Банк / Alfa Only — уровень 1 [pbi]; Альфа-Банк / Alfa Only — уровень 1 [bankiros]; Альфа-Банк / Alfa Only — уровень 2 [official]; Альфа-Банк / Alfa Only — уровень 2 [pbi]; Альфа-Банк / Alfa Only — уровень 2 [bankiros]; Альфа-Банк / Alfa Only — уровень 3 [official]; Альфа-Банк / Alfa Only — уровень 3 [pbi]; Альфа-Банк / Alfa Only — уровень 3 [bankiros]; Альфа-Банк / Alfa Only — уровень 4 [official]; Альфа-Банк / Alfa Only — уровень 4 [pbi]; Альфа-Банк / Alfa Only — уровень 4 [bankiros]; Альфа-Банк / A-Club (private) [official]; Альфа-Банк / A-Club (private) [pbi]; Альфа-Банк / A-Club (private) [bankiros]</t>
+          <t>Озон Банк / Ultra Bronze [official]; Озон Банк / Ultra Bronze [pbi]; Озон Банк / Ultra Silver [official]; Озон Банк / Ultra Silver [pbi]; Озон Банк / Ultra Gold [official]; Озон Банк / Ultra Gold [pbi]; Озон Банк / Ultra Platinum [official]; Озон Банк / Ultra Platinum [pbi]</t>
         </is>
       </c>
     </row>
@@ -52748,7 +53314,7 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Альфа-Банк / Alfa Only — уровень 1 [banki_ru]: blocked_robots: запрещено robots.txt; Альфа-Банк / Alfa Only — уровень 2 [banki_ru]: blocked_robots: запрещено robots.txt; Альфа-Банк / Alfa Only — уровень 3 [banki_ru]: blocked_robots: запрещено robots.txt; Альфа-Банк / Alfa Only — уровень 4 [banki_ru]: blocked_robots: запрещено robots.txt; Альфа-Банк / A-Club (private) [banki_ru]: blocked_robots: запрещено robots.txt</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -52760,7 +53326,7 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>52</t>
         </is>
       </c>
     </row>
@@ -52772,7 +53338,7 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -52784,7 +53350,7 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>2026-07-02T15:14:35</t>
+          <t>2026-07-02T15:19:07</t>
         </is>
       </c>
     </row>
@@ -52796,7 +53362,7 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>bank</t>
         </is>
       </c>
     </row>
@@ -52808,7 +53374,7 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Сбер / СберПремьер — уровень 1 [official]; Сбер / СберПремьер — уровень 1 [official]; Сбер / СберПремьер — уровень 1 [official]; Сбер / СберПремьер — уровень 1 [pbi]; Сбер / СберПремьер — уровень 1 [sravni_ru]; Сбер / СберПремьер — уровень 1 [bankiros]; Сбер / СберПремьер — уровень 2 [official]; Сбер / СберПремьер — уровень 2 [official]; Сбер / СберПремьер — уровень 2 [official]; Сбер / СберПремьер — уровень 2 [pbi]; Сбер / СберПремьер — уровень 2 [sravni_ru]; Сбер / СберПремьер — уровень 2 [bankiros]; Сбер / СберПремьер — уровень 3 [official]; Сбер / СберПремьер — уровень 3 [official]; Сбер / СберПремьер — уровень 3 [official]; Сбер / СберПремьер — уровень 3 [pbi]; Сбер / СберПремьер — уровень 3 [sravni_ru]; Сбер / СберПремьер — уровень 3 [bankiros]; Сбер / СберПервый — уровень 4 [official]; Сбер / СберПервый — уровень 4 [official]; Сбер / СберПервый — уровень 4 [official]; Сбер / СберПервый — уровень 4 [pbi]; Сбер / СберПервый — уровень 4 [sravni_ru]; Сбер / СберПервый — уровень 4 [bankiros]; Сбер / СберПервый — уровень 5 [official]; Сбер / СберПервый — уровень 5 [official]; Сбер / СберПервый — уровень 5 [official]; Сбер / СберПервый — уровень 5 [pbi]; Сбер / СберПервый — уровень 5 [sravni_ru]; Сбер / СберПервый — уровень 5 [bankiros]; Сбер / Sber Private Banking — уровень 6 [official]; Сбер / Sber Private Banking — уровень 6 [official]; Сбер / Sber Private Banking — уровень 6 [pbi]; Сбер / Sber Private Banking — уровень 6 [sravni_ru]; Сбер / Sber Private Banking — уровень 6 [bankiros]; Т-Банк / Premium Bronze [official]; Т-Банк / Premium Bronze [pbi]; Т-Банк / Premium Silver [official]; Т-Банк / Premium Silver [pbi]; Т-Банк / Premium Gold [official]; Т-Банк / Premium Gold [pbi]; Т-Банк / Private (Diamond) [official]; Т-Банк / Private (Diamond) [pbi]; Альфа-Банк / Alfa Only — уровень 1 [official]; Альфа-Банк / Alfa Only — уровень 1 [pbi]; Альфа-Банк / Alfa Only — уровень 1 [bankiros]; Альфа-Банк / Alfa Only — уровень 2 [official]; Альфа-Банк / Alfa Only — уровень 2 [pbi]; Альфа-Банк / Alfa Only — уровень 2 [bankiros]; Альфа-Банк / Alfa Only — уровень 3 [official]; Альфа-Банк / Alfa Only — уровень 3 [pbi]; Альфа-Банк / Alfa Only — уровень 3 [bankiros]; Альфа-Банк / Alfa Only — уровень 4 [official]; Альфа-Банк / Alfa Only — уровень 4 [pbi]; Альфа-Банк / Alfa Only — уровень 4 [bankiros]; Альфа-Банк / A-Club (private) [official]; Альфа-Банк / A-Club (private) [pbi]; Альфа-Банк / A-Club (private) [bankiros]; ВТБ / Привилегия — уровень 1 [official]; ВТБ / Привилегия — уровень 1 [pbi]; ВТБ / Привилегия — уровень 1 [bankiros]; ВТБ / Привилегия — уровень 2 [official]; ВТБ / Привилегия — уровень 2 [pbi]; ВТБ / Привилегия — уровень 2 [bankiros]; ВТБ / Привилегия — уровень 3 [official]; ВТБ / Привилегия — уровень 3 [pbi]; ВТБ / Привилегия — уровень 3 [bankiros]; ВТБ / Привилегия — уровень 4 [official]; ВТБ / Привилегия — уровень 4 [pbi]; ВТБ / Привилегия — уровень 4 [bankiros]; ВТБ / Прайм+ — уровень 5 [official]; ВТБ / Прайм+ — уровень 5 [pbi]; ВТБ / Прайм+ — уровень 5 [bankiros]; ВТБ / Прайм+ — уровень 6 [official]; ВТБ / Прайм+ — уровень 6 [pbi]; ВТБ / Прайм+ — уровень 6 [bankiros]; ВТБ / Прайм+ — уровень 7 [official]; ВТБ / Прайм+ — уровень 7 [pbi]; ВТБ / Прайм+ — уровень 7 [bankiros]; ВТБ / Прайм+ — уровень 8 [official]; ВТБ / Прайм+ — уровень 8 [pbi]; ВТБ / Прайм+ — уровень 8 [bankiros]; Газпромбанк / Премиум — уровень 1 [official]; Газпромбанк / Премиум — уровень 1 [pbi]; Газпромбанк / Премиум — уровень 1 [bankiros]; Газпромбанк / Премиум — уровень 2 [official]; Газпромбанк / Премиум — уровень 2 [pbi]; Газпромбанк / Премиум — уровень 2 [bankiros]; Газпромбанк / Премиум — уровень 3 [official]; Газпромбанк / Премиум — уровень 3 [pbi]; Газпромбанк / Премиум — уровень 3 [bankiros]; Газпромбанк / Private Banking [official]; Газпромбанк / Private Banking [pbi]; Газпромбанк / Private Banking [bankiros]; Озон Банк / Ultra Bronze [official]; Озон Банк / Ultra Bronze [pbi]; Озон Банк / Ultra Silver [official]; Озон Банк / Ultra Silver [pbi]; Озон Банк / Ultra Gold [official]; Озон Банк / Ultra Gold [pbi]; Озон Банк / Ultra Platinum [official]; Озон Банк / Ultra Platinum [pbi]; Райффайзен Банк / Premium (за плату) [official]; Райффайзен Банк / Premium (за плату) [pbi]; Райффайзен Банк / Premium (за траты) [official]; Райффайзен Банк / Premium (за траты) [pbi]; Райффайзен Банк / Premium (за остаток) [official]; Райффайзен Банк / Premium (за остаток) [pbi]; Яндекс Плюс / Яндекс Плюс [official]; premiumbanking.info (обзорная)</t>
+          <t>Альфа-Банк / Alfa Only — уровень 1 [official]; Альфа-Банк / Alfa Only — уровень 1 [pbi]; Альфа-Банк / Alfa Only — уровень 1 [bankiros]; Альфа-Банк / Alfa Only — уровень 2 [official]; Альфа-Банк / Alfa Only — уровень 2 [pbi]; Альфа-Банк / Alfa Only — уровень 2 [bankiros]; Альфа-Банк / Alfa Only — уровень 3 [official]; Альфа-Банк / Alfa Only — уровень 3 [pbi]; Альфа-Банк / Alfa Only — уровень 3 [bankiros]; Альфа-Банк / Alfa Only — уровень 4 [official]; Альфа-Банк / Alfa Only — уровень 4 [pbi]; Альфа-Банк / Alfa Only — уровень 4 [bankiros]; Альфа-Банк / A-Club (private) [official]; Альфа-Банк / A-Club (private) [pbi]; Альфа-Банк / A-Club (private) [bankiros]</t>
         </is>
       </c>
     </row>
@@ -52820,7 +53386,7 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>Сбер / СберПремьер — уровень 1 [banki_ru]: blocked_robots: запрещено robots.txt; Сбер / СберПремьер — уровень 2 [banki_ru]: blocked_robots: запрещено robots.txt; Сбер / СберПремьер — уровень 3 [banki_ru]: blocked_robots: запрещено robots.txt; Сбер / СберПервый — уровень 4 [banki_ru]: blocked_robots: запрещено robots.txt; Сбер / СберПервый — уровень 5 [banki_ru]: blocked_robots: запрещено robots.txt; Сбер / Sber Private Banking — уровень 6 [banki_ru]: blocked_robots: запрещено robots.txt; Т-Банк / Premium Bronze [banki_ru]: blocked_robots: запрещено robots.txt; Т-Банк / Premium Silver [banki_ru]: blocked_robots: запрещено robots.txt; Т-Банк / Premium Gold [banki_ru]: blocked_robots: запрещено robots.txt; Т-Банк / Private (Diamond) [banki_ru]: blocked_robots: запрещено robots.txt; Альфа-Банк / Alfa Only — уровень 1 [banki_ru]: blocked_robots: запрещено robots.txt; Альфа-Банк / Alfa Only — уровень 2 [banki_ru]: blocked_robots: запрещено robots.txt; Альфа-Банк / Alfa Only — уровень 3 [banki_ru]: blocked_robots: запрещено robots.txt; Альфа-Банк / Alfa Only — уровень 4 [banki_ru]: blocked_robots: запрещено robots.txt; Альфа-Банк / A-Club (private) [banki_ru]: blocked_robots: запрещено robots.txt; ВТБ / Привилегия — уровень 1 [banki_ru]: blocked_robots: запрещено robots.txt; ВТБ / Привилегия — уровень 2 [banki_ru]: blocked_robots: запрещено robots.txt; ВТБ / Привилегия — уровень 3 [banki_ru]: blocked_robots: запрещено robots.txt; ВТБ / Привилегия — уровень 4 [banki_ru]: blocked_robots: запрещено robots.txt; ВТБ / Прайм+ — уровень 5 [banki_ru]: blocked_robots: запрещено robots.txt; ВТБ / Прайм+ — уровень 6 [banki_ru]: blocked_robots: запрещено robots.txt; ВТБ / Прайм+ — уровень 7 [banki_ru]: blocked_robots: запрещено robots.txt; ВТБ / Прайм+ — уровень 8 [banki_ru]: blocked_robots: запрещено robots.txt; Газпромбанк / Премиум — уровень 1 [banki_ru]: blocked_robots: запрещено robots.txt; Газпромбанк / Премиум — уровень 2 [banki_ru]: blocked_robots: запрещено robots.txt; Газпромбанк / Премиум — уровень 3 [banki_ru]: blocked_robots: запрещено robots.txt; Газпромбанк / Private Banking [banki_ru]: blocked_robots: запрещено robots.txt; Райффайзен Банк / Premium (за плату) [banki_ru]: blocked_robots: запрещено robots.txt; Райффайзен Банк / Premium (за траты) [banki_ru]: blocked_robots: запрещено robots.txt; Райффайзен Банк / Premium (за остаток) [banki_ru]: blocked_robots: запрещено robots.txt; Ozon Premium / Ozon Premium [official]: unavailable: HTTP 403; Wildberries (Клуб покупателей) / WB Клуб [official]: unavailable: HTTP 498; Frank RG (рейтинги Premium/Private Banking): unavailable: ConnectionError: ('Connection aborted.', ConnectionResetError(54, 'Connection reset by peer'))</t>
+          <t>Альфа-Банк / Alfa Only — уровень 1 [banki_ru]: blocked_robots: запрещено robots.txt; Альфа-Банк / Alfa Only — уровень 2 [banki_ru]: blocked_robots: запрещено robots.txt; Альфа-Банк / Alfa Only — уровень 3 [banki_ru]: blocked_robots: запрещено robots.txt; Альфа-Банк / Alfa Only — уровень 4 [banki_ru]: blocked_robots: запрещено robots.txt; Альфа-Банк / A-Club (private) [banki_ru]: blocked_robots: запрещено robots.txt</t>
         </is>
       </c>
     </row>
@@ -52832,7 +53398,7 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>458</t>
+          <t>67</t>
         </is>
       </c>
     </row>
@@ -52844,7 +53410,7 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -52856,7 +53422,7 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>2026-07-02T14:02:05</t>
+          <t>2026-07-02T15:14:35</t>
         </is>
       </c>
     </row>
@@ -52880,7 +53446,7 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>Сбер / СберПремьер — уровень 1 [official]; Сбер / СберПремьер — уровень 1 [official]; Сбер / СберПремьер — уровень 1 [official]; Сбер / СберПремьер — уровень 1 [pbi]; Сбер / СберПремьер — уровень 1 [sravni_ru]; Сбер / СберПремьер — уровень 1 [bankiros]; Сбер / СберПремьер — уровень 2 [official]; Сбер / СберПремьер — уровень 2 [official]; Сбер / СберПремьер — уровень 2 [official]; Сбер / СберПремьер — уровень 2 [pbi]; Сбер / СберПремьер — уровень 2 [sravni_ru]; Сбер / СберПремьер — уровень 2 [bankiros]; Сбер / СберПремьер — уровень 3 [official]; Сбер / СберПремьер — уровень 3 [official]; Сбер / СберПремьер — уровень 3 [official]; Сбер / СберПремьер — уровень 3 [pbi]; Сбер / СберПремьер — уровень 3 [sravni_ru]; Сбер / СберПремьер — уровень 3 [bankiros]; Сбер / СберПервый — уровень 4 [official]; Сбер / СберПервый — уровень 4 [official]; Сбер / СберПервый — уровень 4 [official]; Сбер / СберПервый — уровень 4 [pbi]; Сбер / СберПервый — уровень 4 [sravni_ru]; Сбер / СберПервый — уровень 4 [bankiros]; Сбер / СберПервый — уровень 5 [official]; Сбер / СберПервый — уровень 5 [official]; Сбер / СберПервый — уровень 5 [official]; Сбер / СберПервый — уровень 5 [pbi]; Сбер / СберПервый — уровень 5 [sravni_ru]; Сбер / СберПервый — уровень 5 [bankiros]; Сбер / Sber Private Banking — уровень 6 [official]; Сбер / Sber Private Banking — уровень 6 [official]; Сбер / Sber Private Banking — уровень 6 [pbi]; Сбер / Sber Private Banking — уровень 6 [sravni_ru]; Сбер / Sber Private Banking — уровень 6 [bankiros]; Т-Банк / Premium Bronze [official]; Т-Банк / Premium Bronze [pbi]; Т-Банк / Premium Silver [official]; Т-Банк / Premium Silver [pbi]; Т-Банк / Premium Gold [official]; Т-Банк / Premium Gold [pbi]; Т-Банк / Private (Diamond) [official]; Т-Банк / Private (Diamond) [pbi]; Альфа-Банк / Alfa Only — уровень 1 [official]; Альфа-Банк / Alfa Only — уровень 1 [pbi]; Альфа-Банк / Alfa Only — уровень 1 [bankiros]; Альфа-Банк / Alfa Only — уровень 2 [official]; Альфа-Банк / Alfa Only — уровень 2 [pbi]; Альфа-Банк / Alfa Only — уровень 2 [bankiros]; Альфа-Банк / Alfa Only — уровень 3 [official]; Альфа-Банк / Alfa Only — уровень 3 [pbi]; Альфа-Банк / Alfa Only — уровень 3 [bankiros]; Альфа-Банк / Alfa Only — уровень 4 [official]; Альфа-Банк / Alfa Only — уровень 4 [pbi]; Альфа-Банк / Alfa Only — уровень 4 [bankiros]; Альфа-Банк / A-Club (private) [official]; Альфа-Банк / A-Club (private) [bankiros]; ВТБ / Привилегия — уровень 1 [official]; ВТБ / Привилегия — уровень 1 [pbi]; ВТБ / Привилегия — уровень 1 [bankiros]; ВТБ / Привилегия — уровень 2 [official]; ВТБ / Привилегия — уровень 2 [pbi]; ВТБ / Привилегия — уровень 2 [bankiros]; ВТБ / Привилегия — уровень 3 [official]; ВТБ / Привилегия — уровень 3 [pbi]; ВТБ / Привилегия — уровень 3 [bankiros]; ВТБ / Привилегия — уровень 4 [official]; ВТБ / Привилегия — уровень 4 [pbi]; ВТБ / Привилегия — уровень 4 [bankiros]; ВТБ / Прайм+ — уровень 5 [official]; ВТБ / Прайм+ — уровень 5 [pbi]; ВТБ / Прайм+ — уровень 5 [bankiros]; ВТБ / Прайм+ — уровень 6 [official]; ВТБ / Прайм+ — уровень 6 [pbi]; ВТБ / Прайм+ — уровень 6 [bankiros]; ВТБ / Прайм+ — уровень 7 [official]; ВТБ / Прайм+ — уровень 7 [pbi]; ВТБ / Прайм+ — уровень 7 [bankiros]; ВТБ / Прайм+ — уровень 8 [official]; ВТБ / Прайм+ — уровень 8 [pbi]; ВТБ / Прайм+ — уровень 8 [bankiros]; Газпромбанк / Премиум — уровень 1 [official]; Газпромбанк / Премиум — уровень 1 [pbi]; Газпромбанк / Премиум — уровень 1 [bankiros]; Газпромбанк / Премиум — уровень 2 [official]; Газпромбанк / Премиум — уровень 2 [pbi]; Газпромбанк / Премиум — уровень 2 [bankiros]; Газпромбанк / Премиум — уровень 3 [official]; Газпромбанк / Премиум — уровень 3 [pbi]; Газпромбанк / Премиум — уровень 3 [bankiros]; Газпромбанк / Private Banking [official]; Газпромбанк / Private Banking [pbi]; Газпромбанк / Private Banking [bankiros]; Озон Банк / Ultra Bronze [official]; Озон Банк / Ultra Bronze [pbi]; Озон Банк / Ultra Silver [official]; Озон Банк / Ultra Silver [pbi]; Озон Банк / Ultra Gold [official]; Озон Банк / Ultra Gold [pbi]; Озон Банк / Ultra Platinum [official]; Озон Банк / Ultra Platinum [pbi]; Райффайзен Банк / Premium (за плату) [official]; Райффайзен Банк / Premium (за плату) [pbi]; Райффайзен Банк / Premium (за траты) [official]; Райффайзен Банк / Premium (за траты) [pbi]; Райффайзен Банк / Premium (за остаток) [official]; Райффайзен Банк / Premium (за остаток) [pbi]; Яндекс Плюс / Яндекс Плюс [official]; premiumbanking.info (обзорная)</t>
+          <t>Сбер / СберПремьер — уровень 1 [official]; Сбер / СберПремьер — уровень 1 [official]; Сбер / СберПремьер — уровень 1 [official]; Сбер / СберПремьер — уровень 1 [pbi]; Сбер / СберПремьер — уровень 1 [sravni_ru]; Сбер / СберПремьер — уровень 1 [bankiros]; Сбер / СберПремьер — уровень 2 [official]; Сбер / СберПремьер — уровень 2 [official]; Сбер / СберПремьер — уровень 2 [official]; Сбер / СберПремьер — уровень 2 [pbi]; Сбер / СберПремьер — уровень 2 [sravni_ru]; Сбер / СберПремьер — уровень 2 [bankiros]; Сбер / СберПремьер — уровень 3 [official]; Сбер / СберПремьер — уровень 3 [official]; Сбер / СберПремьер — уровень 3 [official]; Сбер / СберПремьер — уровень 3 [pbi]; Сбер / СберПремьер — уровень 3 [sravni_ru]; Сбер / СберПремьер — уровень 3 [bankiros]; Сбер / СберПервый — уровень 4 [official]; Сбер / СберПервый — уровень 4 [official]; Сбер / СберПервый — уровень 4 [official]; Сбер / СберПервый — уровень 4 [pbi]; Сбер / СберПервый — уровень 4 [sravni_ru]; Сбер / СберПервый — уровень 4 [bankiros]; Сбер / СберПервый — уровень 5 [official]; Сбер / СберПервый — уровень 5 [official]; Сбер / СберПервый — уровень 5 [official]; Сбер / СберПервый — уровень 5 [pbi]; Сбер / СберПервый — уровень 5 [sravni_ru]; Сбер / СберПервый — уровень 5 [bankiros]; Сбер / Sber Private Banking — уровень 6 [official]; Сбер / Sber Private Banking — уровень 6 [official]; Сбер / Sber Private Banking — уровень 6 [pbi]; Сбер / Sber Private Banking — уровень 6 [sravni_ru]; Сбер / Sber Private Banking — уровень 6 [bankiros]; Т-Банк / Premium Bronze [official]; Т-Банк / Premium Bronze [pbi]; Т-Банк / Premium Silver [official]; Т-Банк / Premium Silver [pbi]; Т-Банк / Premium Gold [official]; Т-Банк / Premium Gold [pbi]; Т-Банк / Private (Diamond) [official]; Т-Банк / Private (Diamond) [pbi]; Альфа-Банк / Alfa Only — уровень 1 [official]; Альфа-Банк / Alfa Only — уровень 1 [pbi]; Альфа-Банк / Alfa Only — уровень 1 [bankiros]; Альфа-Банк / Alfa Only — уровень 2 [official]; Альфа-Банк / Alfa Only — уровень 2 [pbi]; Альфа-Банк / Alfa Only — уровень 2 [bankiros]; Альфа-Банк / Alfa Only — уровень 3 [official]; Альфа-Банк / Alfa Only — уровень 3 [pbi]; Альфа-Банк / Alfa Only — уровень 3 [bankiros]; Альфа-Банк / Alfa Only — уровень 4 [official]; Альфа-Банк / Alfa Only — уровень 4 [pbi]; Альфа-Банк / Alfa Only — уровень 4 [bankiros]; Альфа-Банк / A-Club (private) [official]; Альфа-Банк / A-Club (private) [pbi]; Альфа-Банк / A-Club (private) [bankiros]; ВТБ / Привилегия — уровень 1 [official]; ВТБ / Привилегия — уровень 1 [pbi]; ВТБ / Привилегия — уровень 1 [bankiros]; ВТБ / Привилегия — уровень 2 [official]; ВТБ / Привилегия — уровень 2 [pbi]; ВТБ / Привилегия — уровень 2 [bankiros]; ВТБ / Привилегия — уровень 3 [official]; ВТБ / Привилегия — уровень 3 [pbi]; ВТБ / Привилегия — уровень 3 [bankiros]; ВТБ / Привилегия — уровень 4 [official]; ВТБ / Привилегия — уровень 4 [pbi]; ВТБ / Привилегия — уровень 4 [bankiros]; ВТБ / Прайм+ — уровень 5 [official]; ВТБ / Прайм+ — уровень 5 [pbi]; ВТБ / Прайм+ — уровень 5 [bankiros]; ВТБ / Прайм+ — уровень 6 [official]; ВТБ / Прайм+ — уровень 6 [pbi]; ВТБ / Прайм+ — уровень 6 [bankiros]; ВТБ / Прайм+ — уровень 7 [official]; ВТБ / Прайм+ — уровень 7 [pbi]; ВТБ / Прайм+ — уровень 7 [bankiros]; ВТБ / Прайм+ — уровень 8 [official]; ВТБ / Прайм+ — уровень 8 [pbi]; ВТБ / Прайм+ — уровень 8 [bankiros]; Газпромбанк / Премиум — уровень 1 [official]; Газпромбанк / Премиум — уровень 1 [pbi]; Газпромбанк / Премиум — уровень 1 [bankiros]; Газпромбанк / Премиум — уровень 2 [official]; Газпромбанк / Премиум — уровень 2 [pbi]; Газпромбанк / Премиум — уровень 2 [bankiros]; Газпромбанк / Премиум — уровень 3 [official]; Газпромбанк / Премиум — уровень 3 [pbi]; Газпромбанк / Премиум — уровень 3 [bankiros]; Газпромбанк / Private Banking [official]; Газпромбанк / Private Banking [pbi]; Газпромбанк / Private Banking [bankiros]; Озон Банк / Ultra Bronze [official]; Озон Банк / Ultra Bronze [pbi]; Озон Банк / Ultra Silver [official]; Озон Банк / Ultra Silver [pbi]; Озон Банк / Ultra Gold [official]; Озон Банк / Ultra Gold [pbi]; Озон Банк / Ultra Platinum [official]; Озон Банк / Ultra Platinum [pbi]; Райффайзен Банк / Premium (за плату) [official]; Райффайзен Банк / Premium (за плату) [pbi]; Райффайзен Банк / Premium (за траты) [official]; Райффайзен Банк / Premium (за траты) [pbi]; Райффайзен Банк / Premium (за остаток) [official]; Райффайзен Банк / Premium (за остаток) [pbi]; Яндекс Плюс / Яндекс Плюс [official]; premiumbanking.info (обзорная)</t>
         </is>
       </c>
     </row>
@@ -52904,7 +53470,7 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>458</t>
         </is>
       </c>
     </row>
@@ -52916,7 +53482,7 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>165</t>
         </is>
       </c>
     </row>
@@ -52928,7 +53494,7 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>2026-07-02T13:56:58</t>
+          <t>2026-07-02T14:02:05</t>
         </is>
       </c>
     </row>
@@ -52976,7 +53542,7 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>377</t>
         </is>
       </c>
     </row>
@@ -52988,7 +53554,7 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>16</t>
         </is>
       </c>
     </row>
@@ -53000,7 +53566,7 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>2026-07-02T13:32:45</t>
+          <t>2026-07-02T13:56:58</t>
         </is>
       </c>
     </row>
@@ -53024,7 +53590,7 @@
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>Сбер / СберПремьер — уровень 1 [official]; Сбер / СберПремьер — уровень 1 [official]; Сбер / СберПремьер — уровень 1 [pbi]; Сбер / СберПремьер — уровень 1 [sravni_ru]; Сбер / СберПремьер — уровень 1 [bankiros]; Сбер / СберПремьер — уровень 2 [official]; Сбер / СберПремьер — уровень 2 [official]; Сбер / СберПремьер — уровень 2 [pbi]; Сбер / СберПремьер — уровень 2 [sravni_ru]; Сбер / СберПремьер — уровень 2 [bankiros]; Сбер / СберПремьер — уровень 3 [official]; Сбер / СберПремьер — уровень 3 [official]; Сбер / СберПремьер — уровень 3 [pbi]; Сбер / СберПремьер — уровень 3 [sravni_ru]; Сбер / СберПремьер — уровень 3 [bankiros]; Сбер / СберПервый — уровень 4 [official]; Сбер / СберПервый — уровень 4 [official]; Сбер / СберПервый — уровень 4 [pbi]; Сбер / СберПервый — уровень 4 [sravni_ru]; Сбер / СберПервый — уровень 4 [bankiros]; Сбер / СберПервый — уровень 5 [official]; Сбер / СберПервый — уровень 5 [official]; Сбер / СберПервый — уровень 5 [pbi]; Сбер / СберПервый — уровень 5 [sravni_ru]; Сбер / СберПервый — уровень 5 [bankiros]; Сбер / Sber Private Banking — уровень 6 [official]; Сбер / Sber Private Banking — уровень 6 [pbi]; Сбер / Sber Private Banking — уровень 6 [sravni_ru]; Сбер / Sber Private Banking — уровень 6 [bankiros]; Т-Банк / Premium Bronze [official]; Т-Банк / Premium Bronze [pbi]; Т-Банк / Premium Silver [official]; Т-Банк / Premium Silver [pbi]; Т-Банк / Premium Gold [official]; Т-Банк / Premium Gold [pbi]; Т-Банк / Private (Diamond) [official]; Т-Банк / Private (Diamond) [pbi]; Альфа-Банк / Alfa Only — уровень 1 [official]; Альфа-Банк / Alfa Only — уровень 1 [pbi]; Альфа-Банк / Alfa Only — уровень 1 [bankiros]; Альфа-Банк / Alfa Only — уровень 2 [official]; Альфа-Банк / Alfa Only — уровень 2 [pbi]; Альфа-Банк / Alfa Only — уровень 2 [bankiros]; Альфа-Банк / Alfa Only — уровень 3 [official]; Альфа-Банк / Alfa Only — уровень 3 [pbi]; Альфа-Банк / Alfa Only — уровень 3 [bankiros]; Альфа-Банк / Alfa Only — уровень 4 [official]; Альфа-Банк / Alfa Only — уровень 4 [pbi]; Альфа-Банк / Alfa Only — уровень 4 [bankiros]; Альфа-Банк / A-Club (private) [official]; Альфа-Банк / A-Club (private) [bankiros]; ВТБ / Привилегия — уровень 1 [official]; ВТБ / Привилегия — уровень 1 [pbi]; ВТБ / Привилегия — уровень 1 [bankiros]; ВТБ / Привилегия — уровень 2 [official]; ВТБ / Привилегия — уровень 2 [pbi]; ВТБ / Привилегия — уровень 2 [bankiros]; ВТБ / Привилегия — уровень 3 [official]; ВТБ / Привилегия — уровень 3 [pbi]; ВТБ / Привилегия — уровень 3 [bankiros]; ВТБ / Привилегия — уровень 4 [official]; ВТБ / Привилегия — уровень 4 [pbi]; ВТБ / Привилегия — уровень 4 [bankiros]; ВТБ / Прайм+ — уровень 5 [official]; ВТБ / Прайм+ — уровень 5 [pbi]; ВТБ / Прайм+ — уровень 5 [bankiros]; ВТБ / Прайм+ — уровень 6 [official]; ВТБ / Прайм+ — уровень 6 [pbi]; ВТБ / Прайм+ — уровень 6 [bankiros]; ВТБ / Прайм+ — уровень 7 [official]; ВТБ / Прайм+ — уровень 7 [pbi]; ВТБ / Прайм+ — уровень 7 [bankiros]; ВТБ / Прайм+ — уровень 8 [official]; ВТБ / Прайм+ — уровень 8 [pbi]; ВТБ / Прайм+ — уровень 8 [bankiros]; Газпромбанк / Премиум — уровень 1 [official]; Газпромбанк / Премиум — уровень 1 [pbi]; Газпромбанк / Премиум — уровень 1 [bankiros]; Газпромбанк / Премиум — уровень 2 [official]; Газпромбанк / Премиум — уровень 2 [pbi]; Газпромбанк / Премиум — уровень 2 [bankiros]; Газпромбанк / Премиум — уровень 3 [official]; Газпромбанк / Премиум — уровень 3 [pbi]; Газпромбанк / Премиум — уровень 3 [bankiros]; Газпромбанк / Private Banking [official]; Газпромбанк / Private Banking [pbi]; Газпромбанк / Private Banking [bankiros]; Озон Банк / Ultra Bronze [official]; Озон Банк / Ultra Bronze [pbi]; Озон Банк / Ultra Silver [official]; Озон Банк / Ultra Silver [pbi]; Озон Банк / Ultra Gold [official]; Озон Банк / Ultra Gold [pbi]; Озон Банк / Ultra Platinum [official]; Озон Банк / Ultra Platinum [pbi]; Райффайзен Банк / Premium (за плату) [official]; Райффайзен Банк / Premium (за плату) [pbi]; Райффайзен Банк / Premium (за траты) [official]; Райффайзен Банк / Premium (за траты) [pbi]; Райффайзен Банк / Premium (за остаток) [official]; Райффайзен Банк / Premium (за остаток) [pbi]; Яндекс Плюс / Яндекс Плюс [official]; premiumbanking.info (обзорная)</t>
+          <t>Сбер / СберПремьер — уровень 1 [official]; Сбер / СберПремьер — уровень 1 [official]; Сбер / СберПремьер — уровень 1 [official]; Сбер / СберПремьер — уровень 1 [pbi]; Сбер / СберПремьер — уровень 1 [sravni_ru]; Сбер / СберПремьер — уровень 1 [bankiros]; Сбер / СберПремьер — уровень 2 [official]; Сбер / СберПремьер — уровень 2 [official]; Сбер / СберПремьер — уровень 2 [official]; Сбер / СберПремьер — уровень 2 [pbi]; Сбер / СберПремьер — уровень 2 [sravni_ru]; Сбер / СберПремьер — уровень 2 [bankiros]; Сбер / СберПремьер — уровень 3 [official]; Сбер / СберПремьер — уровень 3 [official]; Сбер / СберПремьер — уровень 3 [official]; Сбер / СберПремьер — уровень 3 [pbi]; Сбер / СберПремьер — уровень 3 [sravni_ru]; Сбер / СберПремьер — уровень 3 [bankiros]; Сбер / СберПервый — уровень 4 [official]; Сбер / СберПервый — уровень 4 [official]; Сбер / СберПервый — уровень 4 [official]; Сбер / СберПервый — уровень 4 [pbi]; Сбер / СберПервый — уровень 4 [sravni_ru]; Сбер / СберПервый — уровень 4 [bankiros]; Сбер / СберПервый — уровень 5 [official]; Сбер / СберПервый — уровень 5 [official]; Сбер / СберПервый — уровень 5 [official]; Сбер / СберПервый — уровень 5 [pbi]; Сбер / СберПервый — уровень 5 [sravni_ru]; Сбер / СберПервый — уровень 5 [bankiros]; Сбер / Sber Private Banking — уровень 6 [official]; Сбер / Sber Private Banking — уровень 6 [official]; Сбер / Sber Private Banking — уровень 6 [pbi]; Сбер / Sber Private Banking — уровень 6 [sravni_ru]; Сбер / Sber Private Banking — уровень 6 [bankiros]; Т-Банк / Premium Bronze [official]; Т-Банк / Premium Bronze [pbi]; Т-Банк / Premium Silver [official]; Т-Банк / Premium Silver [pbi]; Т-Банк / Premium Gold [official]; Т-Банк / Premium Gold [pbi]; Т-Банк / Private (Diamond) [official]; Т-Банк / Private (Diamond) [pbi]; Альфа-Банк / Alfa Only — уровень 1 [official]; Альфа-Банк / Alfa Only — уровень 1 [pbi]; Альфа-Банк / Alfa Only — уровень 1 [bankiros]; Альфа-Банк / Alfa Only — уровень 2 [official]; Альфа-Банк / Alfa Only — уровень 2 [pbi]; Альфа-Банк / Alfa Only — уровень 2 [bankiros]; Альфа-Банк / Alfa Only — уровень 3 [official]; Альфа-Банк / Alfa Only — уровень 3 [pbi]; Альфа-Банк / Alfa Only — уровень 3 [bankiros]; Альфа-Банк / Alfa Only — уровень 4 [official]; Альфа-Банк / Alfa Only — уровень 4 [pbi]; Альфа-Банк / Alfa Only — уровень 4 [bankiros]; Альфа-Банк / A-Club (private) [official]; Альфа-Банк / A-Club (private) [bankiros]; ВТБ / Привилегия — уровень 1 [official]; ВТБ / Привилегия — уровень 1 [pbi]; ВТБ / Привилегия — уровень 1 [bankiros]; ВТБ / Привилегия — уровень 2 [official]; ВТБ / Привилегия — уровень 2 [pbi]; ВТБ / Привилегия — уровень 2 [bankiros]; ВТБ / Привилегия — уровень 3 [official]; ВТБ / Привилегия — уровень 3 [pbi]; ВТБ / Привилегия — уровень 3 [bankiros]; ВТБ / Привилегия — уровень 4 [official]; ВТБ / Привилегия — уровень 4 [pbi]; ВТБ / Привилегия — уровень 4 [bankiros]; ВТБ / Прайм+ — уровень 5 [official]; ВТБ / Прайм+ — уровень 5 [pbi]; ВТБ / Прайм+ — уровень 5 [bankiros]; ВТБ / Прайм+ — уровень 6 [official]; ВТБ / Прайм+ — уровень 6 [pbi]; ВТБ / Прайм+ — уровень 6 [bankiros]; ВТБ / Прайм+ — уровень 7 [official]; ВТБ / Прайм+ — уровень 7 [pbi]; ВТБ / Прайм+ — уровень 7 [bankiros]; ВТБ / Прайм+ — уровень 8 [official]; ВТБ / Прайм+ — уровень 8 [pbi]; ВТБ / Прайм+ — уровень 8 [bankiros]; Газпромбанк / Премиум — уровень 1 [official]; Газпромбанк / Премиум — уровень 1 [pbi]; Газпромбанк / Премиум — уровень 1 [bankiros]; Газпромбанк / Премиум — уровень 2 [official]; Газпромбанк / Премиум — уровень 2 [pbi]; Газпромбанк / Премиум — уровень 2 [bankiros]; Газпромбанк / Премиум — уровень 3 [official]; Газпромбанк / Премиум — уровень 3 [pbi]; Газпромбанк / Премиум — уровень 3 [bankiros]; Газпромбанк / Private Banking [official]; Газпромбанк / Private Banking [pbi]; Газпромбанк / Private Banking [bankiros]; Озон Банк / Ultra Bronze [official]; Озон Банк / Ultra Bronze [pbi]; Озон Банк / Ultra Silver [official]; Озон Банк / Ultra Silver [pbi]; Озон Банк / Ultra Gold [official]; Озон Банк / Ultra Gold [pbi]; Озон Банк / Ultra Platinum [official]; Озон Банк / Ultra Platinum [pbi]; Райффайзен Банк / Premium (за плату) [official]; Райффайзен Банк / Premium (за плату) [pbi]; Райффайзен Банк / Premium (за траты) [official]; Райффайзен Банк / Premium (за траты) [pbi]; Райффайзен Банк / Premium (за остаток) [official]; Райффайзен Банк / Premium (за остаток) [pbi]; Яндекс Плюс / Яндекс Плюс [official]; premiumbanking.info (обзорная)</t>
         </is>
       </c>
     </row>
@@ -53048,7 +53614,7 @@
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>361</t>
         </is>
       </c>
     </row>
@@ -53060,7 +53626,7 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>63</t>
         </is>
       </c>
     </row>
@@ -53072,7 +53638,7 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>2026-07-02T13:27:28</t>
+          <t>2026-07-02T13:32:45</t>
         </is>
       </c>
     </row>
@@ -53120,7 +53686,7 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>393</t>
         </is>
       </c>
     </row>
@@ -53132,7 +53698,7 @@
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -53144,7 +53710,7 @@
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>2026-07-02T13:16:14</t>
+          <t>2026-07-02T13:27:28</t>
         </is>
       </c>
     </row>
@@ -53192,7 +53758,7 @@
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>347</t>
+          <t>361</t>
         </is>
       </c>
     </row>
@@ -53204,7 +53770,7 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -53216,7 +53782,7 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>2026-07-02T13:15:56</t>
+          <t>2026-07-02T13:16:14</t>
         </is>
       </c>
     </row>
@@ -53228,7 +53794,7 @@
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>bank</t>
+          <t>all</t>
         </is>
       </c>
     </row>
@@ -53240,7 +53806,7 @@
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>Райффайзен Банк / Premium (за плату) [official]; Райффайзен Банк / Premium (за плату) [pbi]; Райффайзен Банк / Premium (за траты) [official]; Райффайзен Банк / Premium (за траты) [pbi]; Райффайзен Банк / Premium (за остаток) [official]; Райффайзен Банк / Premium (за остаток) [pbi]</t>
+          <t>Сбер / СберПремьер — уровень 1 [official]; Сбер / СберПремьер — уровень 1 [official]; Сбер / СберПремьер — уровень 1 [pbi]; Сбер / СберПремьер — уровень 1 [sravni_ru]; Сбер / СберПремьер — уровень 1 [bankiros]; Сбер / СберПремьер — уровень 2 [official]; Сбер / СберПремьер — уровень 2 [official]; Сбер / СберПремьер — уровень 2 [pbi]; Сбер / СберПремьер — уровень 2 [sravni_ru]; Сбер / СберПремьер — уровень 2 [bankiros]; Сбер / СберПремьер — уровень 3 [official]; Сбер / СберПремьер — уровень 3 [official]; Сбер / СберПремьер — уровень 3 [pbi]; Сбер / СберПремьер — уровень 3 [sravni_ru]; Сбер / СберПремьер — уровень 3 [bankiros]; Сбер / СберПервый — уровень 4 [official]; Сбер / СберПервый — уровень 4 [official]; Сбер / СберПервый — уровень 4 [pbi]; Сбер / СберПервый — уровень 4 [sravni_ru]; Сбер / СберПервый — уровень 4 [bankiros]; Сбер / СберПервый — уровень 5 [official]; Сбер / СберПервый — уровень 5 [official]; Сбер / СберПервый — уровень 5 [pbi]; Сбер / СберПервый — уровень 5 [sravni_ru]; Сбер / СберПервый — уровень 5 [bankiros]; Сбер / Sber Private Banking — уровень 6 [official]; Сбер / Sber Private Banking — уровень 6 [pbi]; Сбер / Sber Private Banking — уровень 6 [sravni_ru]; Сбер / Sber Private Banking — уровень 6 [bankiros]; Т-Банк / Premium Bronze [official]; Т-Банк / Premium Bronze [pbi]; Т-Банк / Premium Silver [official]; Т-Банк / Premium Silver [pbi]; Т-Банк / Premium Gold [official]; Т-Банк / Premium Gold [pbi]; Т-Банк / Private (Diamond) [official]; Т-Банк / Private (Diamond) [pbi]; Альфа-Банк / Alfa Only — уровень 1 [official]; Альфа-Банк / Alfa Only — уровень 1 [pbi]; Альфа-Банк / Alfa Only — уровень 1 [bankiros]; Альфа-Банк / Alfa Only — уровень 2 [official]; Альфа-Банк / Alfa Only — уровень 2 [pbi]; Альфа-Банк / Alfa Only — уровень 2 [bankiros]; Альфа-Банк / Alfa Only — уровень 3 [official]; Альфа-Банк / Alfa Only — уровень 3 [pbi]; Альфа-Банк / Alfa Only — уровень 3 [bankiros]; Альфа-Банк / Alfa Only — уровень 4 [official]; Альфа-Банк / Alfa Only — уровень 4 [pbi]; Альфа-Банк / Alfa Only — уровень 4 [bankiros]; Альфа-Банк / A-Club (private) [official]; Альфа-Банк / A-Club (private) [bankiros]; ВТБ / Привилегия — уровень 1 [official]; ВТБ / Привилегия — уровень 1 [pbi]; ВТБ / Привилегия — уровень 1 [bankiros]; ВТБ / Привилегия — уровень 2 [official]; ВТБ / Привилегия — уровень 2 [pbi]; ВТБ / Привилегия — уровень 2 [bankiros]; ВТБ / Привилегия — уровень 3 [official]; ВТБ / Привилегия — уровень 3 [pbi]; ВТБ / Привилегия — уровень 3 [bankiros]; ВТБ / Привилегия — уровень 4 [official]; ВТБ / Привилегия — уровень 4 [pbi]; ВТБ / Привилегия — уровень 4 [bankiros]; ВТБ / Прайм+ — уровень 5 [official]; ВТБ / Прайм+ — уровень 5 [pbi]; ВТБ / Прайм+ — уровень 5 [bankiros]; ВТБ / Прайм+ — уровень 6 [official]; ВТБ / Прайм+ — уровень 6 [pbi]; ВТБ / Прайм+ — уровень 6 [bankiros]; ВТБ / Прайм+ — уровень 7 [official]; ВТБ / Прайм+ — уровень 7 [pbi]; ВТБ / Прайм+ — уровень 7 [bankiros]; ВТБ / Прайм+ — уровень 8 [official]; ВТБ / Прайм+ — уровень 8 [pbi]; ВТБ / Прайм+ — уровень 8 [bankiros]; Газпромбанк / Премиум — уровень 1 [official]; Газпромбанк / Премиум — уровень 1 [pbi]; Газпромбанк / Премиум — уровень 1 [bankiros]; Газпромбанк / Премиум — уровень 2 [official]; Газпромбанк / Премиум — уровень 2 [pbi]; Газпромбанк / Премиум — уровень 2 [bankiros]; Газпромбанк / Премиум — уровень 3 [official]; Газпромбанк / Премиум — уровень 3 [pbi]; Газпромбанк / Премиум — уровень 3 [bankiros]; Газпромбанк / Private Banking [official]; Газпромбанк / Private Banking [pbi]; Газпромбанк / Private Banking [bankiros]; Озон Банк / Ultra Bronze [official]; Озон Банк / Ultra Bronze [pbi]; Озон Банк / Ultra Silver [official]; Озон Банк / Ultra Silver [pbi]; Озон Банк / Ultra Gold [official]; Озон Банк / Ultra Gold [pbi]; Озон Банк / Ultra Platinum [official]; Озон Банк / Ultra Platinum [pbi]; Райффайзен Банк / Premium (за плату) [official]; Райффайзен Банк / Premium (за плату) [pbi]; Райффайзен Банк / Premium (за траты) [official]; Райффайзен Банк / Premium (за траты) [pbi]; Райффайзен Банк / Premium (за остаток) [official]; Райффайзен Банк / Premium (за остаток) [pbi]; Яндекс Плюс / Яндекс Плюс [official]; premiumbanking.info (обзорная)</t>
         </is>
       </c>
     </row>
@@ -53252,7 +53818,7 @@
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>Райффайзен Банк / Premium (за плату) [banki_ru]: blocked_robots: запрещено robots.txt; Райффайзен Банк / Premium (за траты) [banki_ru]: blocked_robots: запрещено robots.txt; Райффайзен Банк / Premium (за остаток) [banki_ru]: blocked_robots: запрещено robots.txt</t>
+          <t>Сбер / СберПремьер — уровень 1 [banki_ru]: blocked_robots: запрещено robots.txt; Сбер / СберПремьер — уровень 2 [banki_ru]: blocked_robots: запрещено robots.txt; Сбер / СберПремьер — уровень 3 [banki_ru]: blocked_robots: запрещено robots.txt; Сбер / СберПервый — уровень 4 [banki_ru]: blocked_robots: запрещено robots.txt; Сбер / СберПервый — уровень 5 [banki_ru]: blocked_robots: запрещено robots.txt; Сбер / Sber Private Banking — уровень 6 [banki_ru]: blocked_robots: запрещено robots.txt; Т-Банк / Premium Bronze [banki_ru]: blocked_robots: запрещено robots.txt; Т-Банк / Premium Silver [banki_ru]: blocked_robots: запрещено robots.txt; Т-Банк / Premium Gold [banki_ru]: blocked_robots: запрещено robots.txt; Т-Банк / Private (Diamond) [banki_ru]: blocked_robots: запрещено robots.txt; Альфа-Банк / Alfa Only — уровень 1 [banki_ru]: blocked_robots: запрещено robots.txt; Альфа-Банк / Alfa Only — уровень 2 [banki_ru]: blocked_robots: запрещено robots.txt; Альфа-Банк / Alfa Only — уровень 3 [banki_ru]: blocked_robots: запрещено robots.txt; Альфа-Банк / Alfa Only — уровень 4 [banki_ru]: blocked_robots: запрещено robots.txt; Альфа-Банк / A-Club (private) [banki_ru]: blocked_robots: запрещено robots.txt; ВТБ / Привилегия — уровень 1 [banki_ru]: blocked_robots: запрещено robots.txt; ВТБ / Привилегия — уровень 2 [banki_ru]: blocked_robots: запрещено robots.txt; ВТБ / Привилегия — уровень 3 [banki_ru]: blocked_robots: запрещено robots.txt; ВТБ / Привилегия — уровень 4 [banki_ru]: blocked_robots: запрещено robots.txt; ВТБ / Прайм+ — уровень 5 [banki_ru]: blocked_robots: запрещено robots.txt; ВТБ / Прайм+ — уровень 6 [banki_ru]: blocked_robots: запрещено robots.txt; ВТБ / Прайм+ — уровень 7 [banki_ru]: blocked_robots: запрещено robots.txt; ВТБ / Прайм+ — уровень 8 [banki_ru]: blocked_robots: запрещено robots.txt; Газпромбанк / Премиум — уровень 1 [banki_ru]: blocked_robots: запрещено robots.txt; Газпромбанк / Премиум — уровень 2 [banki_ru]: blocked_robots: запрещено robots.txt; Газпромбанк / Премиум — уровень 3 [banki_ru]: blocked_robots: запрещено robots.txt; Газпромбанк / Private Banking [banki_ru]: blocked_robots: запрещено robots.txt; Райффайзен Банк / Premium (за плату) [banki_ru]: blocked_robots: запрещено robots.txt; Райффайзен Банк / Premium (за траты) [banki_ru]: blocked_robots: запрещено robots.txt; Райффайзен Банк / Premium (за остаток) [banki_ru]: blocked_robots: запрещено robots.txt; Ozon Premium / Ozon Premium [official]: unavailable: HTTP 403; Wildberries (Клуб покупателей) / WB Клуб [official]: unavailable: HTTP 498; Frank RG (рейтинги Premium/Private Banking): unavailable: ConnectionError: ('Connection aborted.', ConnectionResetError(54, 'Connection reset by peer'))</t>
         </is>
       </c>
     </row>
@@ -53264,7 +53830,7 @@
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>347</t>
         </is>
       </c>
     </row>
@@ -53276,7 +53842,7 @@
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>72</t>
         </is>
       </c>
     </row>
@@ -53288,7 +53854,7 @@
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>2026-07-02T12:40:50</t>
+          <t>2026-07-02T13:15:56</t>
         </is>
       </c>
     </row>
@@ -53300,7 +53866,7 @@
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>bank</t>
         </is>
       </c>
     </row>
@@ -53312,7 +53878,7 @@
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>Сбер / СберПремьер — уровень 1; Сбер / СберПремьер — уровень 2; Сбер / СберПремьер — уровень 3; Сбер / СберПервый — уровень 4; Сбер / СберПервый — уровень 5; Сбер / Sber Private Banking — уровень 6; Т-Банк / Premium Bronze; Т-Банк / Premium Silver; Т-Банк / Premium Gold; Т-Банк / Private (Diamond); Альфа-Банк / Alfa Only — уровень 1; Альфа-Банк / Alfa Only — уровень 2; Альфа-Банк / Alfa Only — уровень 3; Альфа-Банк / Alfa Only — уровень 4; Альфа-Банк / A-Club (private); ВТБ / Привилегия — уровень 1; ВТБ / Привилегия — уровень 2; ВТБ / Привилегия — уровень 3; ВТБ / Привилегия — уровень 4; ВТБ / Прайм+ — уровень 5; ВТБ / Прайм+ — уровень 6; ВТБ / Прайм+ — уровень 7; ВТБ / Прайм+ — уровень 8; Газпромбанк / Премиум — уровень 1; Газпромбанк / Премиум — уровень 2; Газпромбанк / Премиум — уровень 3; Газпромбанк / Private Banking; Озон Банк / Ultra Bronze; Озон Банк / Ultra Silver; Озон Банк / Ultra Gold; Озон Банк / Ultra Platinum; Райффайзен Банк / Premium (за плату); Райффайзен Банк / Premium (за траты); Райффайзен Банк / Premium (за остаток); Яндекс Плюс / Яндекс Плюс; premiumbanking.info (приоритетный агрегатор)</t>
+          <t>Райффайзен Банк / Premium (за плату) [official]; Райффайзен Банк / Premium (за плату) [pbi]; Райффайзен Банк / Premium (за траты) [official]; Райффайзен Банк / Premium (за траты) [pbi]; Райффайзен Банк / Premium (за остаток) [official]; Райффайзен Банк / Premium (за остаток) [pbi]</t>
         </is>
       </c>
     </row>
@@ -53324,7 +53890,7 @@
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>Ozon Premium / Ozon Premium: unavailable: HTTP 403; Wildberries (Клуб покупателей) / WB Клуб: unavailable: HTTP 498; Frank RG: unavailable: ConnectionError: ('Connection aborted.', ConnectionResetError(54, 'Connection reset by peer'))</t>
+          <t>Райффайзен Банк / Premium (за плату) [banki_ru]: blocked_robots: запрещено robots.txt; Райффайзен Банк / Premium (за траты) [banki_ru]: blocked_robots: запрещено robots.txt; Райффайзен Банк / Premium (за остаток) [banki_ru]: blocked_robots: запрещено robots.txt</t>
         </is>
       </c>
     </row>
@@ -53336,7 +53902,7 @@
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -53348,7 +53914,7 @@
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12</t>
         </is>
       </c>
     </row>
@@ -53360,7 +53926,7 @@
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>2026-07-02T12:20:53</t>
+          <t>2026-07-02T12:40:50</t>
         </is>
       </c>
     </row>
@@ -53420,7 +53986,7 @@
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>297</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -53432,7 +53998,7 @@
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>2026-07-02T12:17:15</t>
+          <t>2026-07-02T12:20:53</t>
         </is>
       </c>
     </row>
@@ -53444,7 +54010,7 @@
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>lifestyle</t>
+          <t>all</t>
         </is>
       </c>
     </row>
@@ -53456,7 +54022,7 @@
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>Яндекс Плюс / Яндекс Плюс</t>
+          <t>Сбер / СберПремьер — уровень 1; Сбер / СберПремьер — уровень 2; Сбер / СберПремьер — уровень 3; Сбер / СберПервый — уровень 4; Сбер / СберПервый — уровень 5; Сбер / Sber Private Banking — уровень 6; Т-Банк / Premium Bronze; Т-Банк / Premium Silver; Т-Банк / Premium Gold; Т-Банк / Private (Diamond); Альфа-Банк / Alfa Only — уровень 1; Альфа-Банк / Alfa Only — уровень 2; Альфа-Банк / Alfa Only — уровень 3; Альфа-Банк / Alfa Only — уровень 4; Альфа-Банк / A-Club (private); ВТБ / Привилегия — уровень 1; ВТБ / Привилегия — уровень 2; ВТБ / Привилегия — уровень 3; ВТБ / Привилегия — уровень 4; ВТБ / Прайм+ — уровень 5; ВТБ / Прайм+ — уровень 6; ВТБ / Прайм+ — уровень 7; ВТБ / Прайм+ — уровень 8; Газпромбанк / Премиум — уровень 1; Газпромбанк / Премиум — уровень 2; Газпромбанк / Премиум — уровень 3; Газпромбанк / Private Banking; Озон Банк / Ultra Bronze; Озон Банк / Ultra Silver; Озон Банк / Ultra Gold; Озон Банк / Ultra Platinum; Райффайзен Банк / Premium (за плату); Райффайзен Банк / Premium (за траты); Райффайзен Банк / Premium (за остаток); Яндекс Плюс / Яндекс Плюс; premiumbanking.info (приоритетный агрегатор)</t>
         </is>
       </c>
     </row>
@@ -53468,7 +54034,7 @@
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>Ozon Premium / Ozon Premium: unavailable: HTTP 403; Wildberries (Клуб покупателей) / WB Клуб: unavailable: HTTP 498</t>
+          <t>Ozon Premium / Ozon Premium: unavailable: HTTP 403; Wildberries (Клуб покупателей) / WB Клуб: unavailable: HTTP 498; Frank RG: unavailable: ConnectionError: ('Connection aborted.', ConnectionResetError(54, 'Connection reset by peer'))</t>
         </is>
       </c>
     </row>
@@ -53480,7 +54046,7 @@
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>279</t>
         </is>
       </c>
     </row>
@@ -53492,7 +54058,7 @@
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>297</t>
         </is>
       </c>
     </row>
@@ -53504,7 +54070,7 @@
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>2026-07-02T12:13:51</t>
+          <t>2026-07-02T12:17:15</t>
         </is>
       </c>
     </row>
@@ -53516,7 +54082,7 @@
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>lifestyle</t>
         </is>
       </c>
     </row>
@@ -53528,7 +54094,7 @@
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>Сбер / СберПремьер — уровень 1; Сбер / СберПремьер — уровень 2; Сбер / СберПремьер — уровень 3; Сбер / СберПервый — уровень 4; Сбер / СберПервый — уровень 5; Сбер / Sber Private Banking — уровень 6; Т-Банк / Premium Bronze; Т-Банк / Premium Silver; Т-Банк / Premium Gold; Т-Банк / Private (Diamond); Альфа-Банк / Alfa Only — уровень 1; Альфа-Банк / Alfa Only — уровень 2; Альфа-Банк / Alfa Only — уровень 3; Альфа-Банк / Alfa Only — уровень 4; Альфа-Банк / A-Club (private); ВТБ / Привилегия — уровень 1; ВТБ / Привилегия — уровень 2; ВТБ / Привилегия — уровень 3; ВТБ / Привилегия — уровень 4; ВТБ / Прайм+ — уровень 5; ВТБ / Прайм+ — уровень 6; ВТБ / Прайм+ — уровень 7; ВТБ / Прайм+ — уровень 8; Газпромбанк / Премиум — уровень 1; Газпромбанк / Премиум — уровень 2; Газпромбанк / Премиум — уровень 3; Газпромбанк / Private Banking; Озон Банк / Ultra Bronze; Озон Банк / Ultra Silver; Озон Банк / Ultra Gold; Озон Банк / Ultra Platinum; Райффайзен Банк / Premium (за плату); Райффайзен Банк / Premium (за траты); Райффайзен Банк / Premium (за остаток); Яндекс Плюс / Яндекс Плюс; premiumbanking.info (приоритетный агрегатор)</t>
+          <t>Яндекс Плюс / Яндекс Плюс</t>
         </is>
       </c>
     </row>
@@ -53540,7 +54106,7 @@
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>Ozon Premium / Ozon Premium: unavailable: HTTP 403; Wildberries (Клуб покупателей) / WB Клуб: unavailable: HTTP 498; Frank RG: unavailable: ConnectionError: ('Connection aborted.', ConnectionResetError(54, 'Connection reset by peer'))</t>
+          <t>Ozon Premium / Ozon Premium: unavailable: HTTP 403; Wildberries (Клуб покупателей) / WB Клуб: unavailable: HTTP 498</t>
         </is>
       </c>
     </row>
@@ -53552,7 +54118,7 @@
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>277</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -53564,7 +54130,7 @@
       </c>
       <c r="B126" s="4" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -53576,7 +54142,7 @@
       </c>
       <c r="B128" s="4" t="inlineStr">
         <is>
-          <t>2026-07-02T12:06:13</t>
+          <t>2026-07-02T12:13:51</t>
         </is>
       </c>
     </row>
@@ -53600,7 +54166,7 @@
       </c>
       <c r="B130" s="4" t="inlineStr">
         <is>
-          <t>Т-Банк / Premium; Т-Банк / Private (Diamond); Газпромбанк / Премиум; Газпромбанк / Private Banking; Озон Банк / Bronze; Озон Банк / Silver; Озон Банк / Gold; Озон Банк / Platinum; Райффайзен Банк / Premium; Яндекс Плюс / Яндекс Плюс; premiumbanking.info (приоритетный агрегатор)</t>
+          <t>Сбер / СберПремьер — уровень 1; Сбер / СберПремьер — уровень 2; Сбер / СберПремьер — уровень 3; Сбер / СберПервый — уровень 4; Сбер / СберПервый — уровень 5; Сбер / Sber Private Banking — уровень 6; Т-Банк / Premium Bronze; Т-Банк / Premium Silver; Т-Банк / Premium Gold; Т-Банк / Private (Diamond); Альфа-Банк / Alfa Only — уровень 1; Альфа-Банк / Alfa Only — уровень 2; Альфа-Банк / Alfa Only — уровень 3; Альфа-Банк / Alfa Only — уровень 4; Альфа-Банк / A-Club (private); ВТБ / Привилегия — уровень 1; ВТБ / Привилегия — уровень 2; ВТБ / Привилегия — уровень 3; ВТБ / Привилегия — уровень 4; ВТБ / Прайм+ — уровень 5; ВТБ / Прайм+ — уровень 6; ВТБ / Прайм+ — уровень 7; ВТБ / Прайм+ — уровень 8; Газпромбанк / Премиум — уровень 1; Газпромбанк / Премиум — уровень 2; Газпромбанк / Премиум — уровень 3; Газпромбанк / Private Banking; Озон Банк / Ultra Bronze; Озон Банк / Ultra Silver; Озон Банк / Ultra Gold; Озон Банк / Ultra Platinum; Райффайзен Банк / Premium (за плату); Райффайзен Банк / Premium (за траты); Райффайзен Банк / Premium (за остаток); Яндекс Плюс / Яндекс Плюс; premiumbanking.info (приоритетный агрегатор)</t>
         </is>
       </c>
     </row>
@@ -53612,7 +54178,7 @@
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>Сбер / СберПремьер (уровни 1–3): unavailable: HTTP 404; Сбер / СберПервый (уровни 4–5): unavailable: HTTP 404; Сбер / Sber Private Banking (уровень 6): unavailable: ConnectionError: HTTPSConnectionPool(host='www.sberbank-pb.ru', port=443): Max retries exceeded with url: / (Caused by NameResolutionError("HTTPSConnection(host='www.sberbank-pb.ru', port=443): Failed to resolve 'www.sberbank-pb.ru' ([Errno 8] nodename nor servname provided, or not known)")); Альфа-Банк / Alfa Only: js_required: страница требует JS-рендеринга (playwright недоступен); Альфа-Банк / A-Club (private): js_required: страница требует JS-рендеринга (playwright недоступен); ВТБ / Привилегия: unavailable: HTTP 404; ВТБ / Прайм: unavailable: HTTP 404; ВТБ / Прайм+: unavailable: HTTP 404; Ozon Premium / Ozon Premium: unavailable: HTTP 403; Wildberries (Клуб покупателей) / WB Клуб: unavailable: HTTP 498; Frank RG: unavailable: ConnectionError: ('Connection aborted.', ConnectionResetError(54, 'Connection reset by peer'))</t>
+          <t>Ozon Premium / Ozon Premium: unavailable: HTTP 403; Wildberries (Клуб покупателей) / WB Клуб: unavailable: HTTP 498; Frank RG: unavailable: ConnectionError: ('Connection aborted.', ConnectionResetError(54, 'Connection reset by peer'))</t>
         </is>
       </c>
     </row>
@@ -53624,7 +54190,7 @@
       </c>
       <c r="B132" s="4" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>277</t>
         </is>
       </c>
     </row>
@@ -53635,6 +54201,78 @@
         </is>
       </c>
       <c r="B133" s="4" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="14" t="inlineStr">
+        <is>
+          <t>Дата запуска</t>
+        </is>
+      </c>
+      <c r="B135" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-02T12:06:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="14" t="inlineStr">
+        <is>
+          <t>Режим</t>
+        </is>
+      </c>
+      <c r="B136" s="4" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="14" t="inlineStr">
+        <is>
+          <t>Источники OK</t>
+        </is>
+      </c>
+      <c r="B137" s="4" t="inlineStr">
+        <is>
+          <t>Т-Банк / Premium; Т-Банк / Private (Diamond); Газпромбанк / Премиум; Газпромбанк / Private Banking; Озон Банк / Bronze; Озон Банк / Silver; Озон Банк / Gold; Озон Банк / Platinum; Райффайзен Банк / Premium; Яндекс Плюс / Яндекс Плюс; premiumbanking.info (приоритетный агрегатор)</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="14" t="inlineStr">
+        <is>
+          <t>Источники с ошибками</t>
+        </is>
+      </c>
+      <c r="B138" s="4" t="inlineStr">
+        <is>
+          <t>Сбер / СберПремьер (уровни 1–3): unavailable: HTTP 404; Сбер / СберПервый (уровни 4–5): unavailable: HTTP 404; Сбер / Sber Private Banking (уровень 6): unavailable: ConnectionError: HTTPSConnectionPool(host='www.sberbank-pb.ru', port=443): Max retries exceeded with url: / (Caused by NameResolutionError("HTTPSConnection(host='www.sberbank-pb.ru', port=443): Failed to resolve 'www.sberbank-pb.ru' ([Errno 8] nodename nor servname provided, or not known)")); Альфа-Банк / Alfa Only: js_required: страница требует JS-рендеринга (playwright недоступен); Альфа-Банк / A-Club (private): js_required: страница требует JS-рендеринга (playwright недоступен); ВТБ / Привилегия: unavailable: HTTP 404; ВТБ / Прайм: unavailable: HTTP 404; ВТБ / Прайм+: unavailable: HTTP 404; Ozon Premium / Ozon Premium: unavailable: HTTP 403; Wildberries (Клуб покупателей) / WB Клуб: unavailable: HTTP 498; Frank RG: unavailable: ConnectionError: ('Connection aborted.', ConnectionResetError(54, 'Connection reset by peer'))</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="14" t="inlineStr">
+        <is>
+          <t>Полей обновлено</t>
+        </is>
+      </c>
+      <c r="B139" s="4" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="14" t="inlineStr">
+        <is>
+          <t>Изменений найдено</t>
+        </is>
+      </c>
+      <c r="B140" s="4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -56341,22 +56979,22 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.9</t>
         </is>
       </c>
     </row>
@@ -56698,52 +57336,56 @@
           <t>Кэшбэк (ставка, категории, механика)</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>Кэшбэк 1–15% рублями в 3 категориях (4 для зарплатных клиентов) на выбор из 9; по отдельным категориям лимиты (например, «Такси» — до 1 000 ₽/мес)
 [источник: Ручная проверка (первоисточник), проверено: 2026-07-02]
-[прим.: Начисляется рублями, не мультибонусами]</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
+[прим.: Начисляется рублями, не мультибонусами; числа расходятся с Bankiros.ru]</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>Кэшбэк 1–15% рублями в 3 категориях (4 для зарплатных клиентов) на выбор из 9; по отдельным категориям лимиты (например, «Такси» — до 1 000 ₽/мес)
 [источник: Ручная проверка (первоисточник), проверено: 2026-07-02]
-[прим.: Начисляется рублями, не мультибонусами]</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
+[прим.: Начисляется рублями, не мультибонусами; числа расходятся с Bankiros.ru]</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t>Кэшбэк 1–15% рублями в 3 категориях (4 для зарплатных клиентов) на выбор из 9; по отдельным категориям лимиты (например, «Такси» — до 1 000 ₽/мес)
 [источник: Ручная проверка (первоисточник), проверено: 2026-07-02]
-[прим.: Начисляется рублями, не мультибонусами]</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
+[прим.: Начисляется рублями, не мультибонусами; числа расходятся с Bankiros.ru]</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
         <is>
           <t>Кэшбэк 1–15% рублями в 3 категориях (4 для зарплатных клиентов) на выбор из 9; по отдельным категориям лимиты (например, «Такси» — до 1 000 ₽/мес)
 [источник: Ручная проверка (первоисточник), проверено: 2026-07-02]
-[прим.: Начисляется рублями, не мультибонусами]</t>
-        </is>
-      </c>
-      <c r="F12" s="7" t="inlineStr">
-        <is>
-          <t>не найдено</t>
-        </is>
-      </c>
-      <c r="G12" s="7" t="inlineStr">
-        <is>
-          <t>не найдено</t>
-        </is>
-      </c>
-      <c r="H12" s="7" t="inlineStr">
-        <is>
-          <t>не найдено</t>
-        </is>
-      </c>
-      <c r="I12" s="7" t="inlineStr">
-        <is>
-          <t>не найдено</t>
+[прим.: Начисляется рублями, не мультибонусами; числа расходятся с Bankiros.ru]</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>Карта с беспроцентным периодом до 110 дней и повышенным кешбэком | Как перевести Мультибонусы втб на карту? | Личный кабинет Мультибонус ВТБ
+[источник: Bankiros.ru, проверено: 2026-07-02]</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>Карта с беспроцентным периодом до 110 дней и повышенным кешбэком | Как перевести Мультибонусы втб на карту? | Личный кабинет Мультибонус ВТБ
+[источник: Bankiros.ru, проверено: 2026-07-02]</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>Карта с беспроцентным периодом до 110 дней и повышенным кешбэком | Как перевести Мультибонусы втб на карту? | Личный кабинет Мультибонус ВТБ
+[источник: Bankiros.ru, проверено: 2026-07-02]</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>Карта с беспроцентным периодом до 110 дней и повышенным кешбэком | Как перевести Мультибонусы втб на карту? | Личный кабинет Мультибонус ВТБ
+[источник: Bankiros.ru, проверено: 2026-07-02]</t>
         </is>
       </c>
     </row>
@@ -56777,24 +57419,28 @@
 [источник: Ручная проверка (первоисточник), проверено: 2026-07-02]</t>
         </is>
       </c>
-      <c r="F13" s="7" t="inlineStr">
-        <is>
-          <t>не найдено</t>
-        </is>
-      </c>
-      <c r="G13" s="7" t="inlineStr">
-        <is>
-          <t>не найдено</t>
-        </is>
-      </c>
-      <c r="H13" s="7" t="inlineStr">
-        <is>
-          <t>не найдено</t>
-        </is>
-      </c>
-      <c r="I13" s="7" t="inlineStr">
-        <is>
-          <t>не найдено</t>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>Банки-партнеры ВТБ: где снять наличные без комиссии | Снятие наличных в банкомате без карты
+[источник: Bankiros.ru, проверено: 2026-07-02]</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>Банки-партнеры ВТБ: где снять наличные без комиссии | Снятие наличных в банкомате без карты
+[источник: Bankiros.ru, проверено: 2026-07-02]</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>Банки-партнеры ВТБ: где снять наличные без комиссии | Снятие наличных в банкомате без карты
+[источник: Bankiros.ru, проверено: 2026-07-02]</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>Банки-партнеры ВТБ: где снять наличные без комиссии | Снятие наличных в банкомате без карты
+[источник: Bankiros.ru, проверено: 2026-07-02]</t>
         </is>
       </c>
     </row>
@@ -56804,48 +57450,56 @@
           <t>Спецусловия по вкладам / накопительным счетам</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>Накопительный ВТБ-Счёт до 13,75% годовых (повышенная ставка за покупки по карте); опция «Сбережения»: надбавка +1–3 п.п. к ставке в зависимости от оборота по карте. Ставки на дату проверки
-[источник: Ручная проверка (первоисточник), проверено: 2026-07-02]</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
+[источник: Ручная проверка (первоисточник), проверено: 2026-07-02]
+[прим.: числа расходятся с Bankiros.ru]</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>Накопительный ВТБ-Счёт до 13,75% годовых (повышенная ставка за покупки по карте); опция «Сбережения»: надбавка +1–3 п.п. к ставке в зависимости от оборота по карте. Ставки на дату проверки
-[источник: Ручная проверка (первоисточник), проверено: 2026-07-02]</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
+[источник: Ручная проверка (первоисточник), проверено: 2026-07-02]
+[прим.: числа расходятся с Bankiros.ru]</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
         <is>
           <t>Накопительный ВТБ-Счёт до 13,75% годовых (повышенная ставка за покупки по карте); опция «Сбережения»: надбавка +1–3 п.п. к ставке в зависимости от оборота по карте. Ставки на дату проверки
-[источник: Ручная проверка (первоисточник), проверено: 2026-07-02]</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
+[источник: Ручная проверка (первоисточник), проверено: 2026-07-02]
+[прим.: числа расходятся с Bankiros.ru]</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
         <is>
           <t>Накопительный ВТБ-Счёт до 13,75% годовых (повышенная ставка за покупки по карте); опция «Сбережения»: надбавка +1–3 п.п. к ставке в зависимости от оборота по карте. Ставки на дату проверки
-[источник: Ручная проверка (первоисточник), проверено: 2026-07-02]</t>
-        </is>
-      </c>
-      <c r="F14" s="7" t="inlineStr">
-        <is>
-          <t>не найдено</t>
-        </is>
-      </c>
-      <c r="G14" s="7" t="inlineStr">
-        <is>
-          <t>не найдено</t>
-        </is>
-      </c>
-      <c r="H14" s="7" t="inlineStr">
-        <is>
-          <t>не найдено</t>
-        </is>
-      </c>
-      <c r="I14" s="7" t="inlineStr">
-        <is>
-          <t>не найдено</t>
+[источник: Ручная проверка (первоисточник), проверено: 2026-07-02]
+[прим.: числа расходятся с Bankiros.ru]</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>Более 1500 вкладов в 357 банках России | Выгодные вклады | Накопительные счета
+[источник: Bankiros.ru, проверено: 2026-07-02]</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>Более 1500 вкладов в 357 банках России | Выгодные вклады | Накопительные счета
+[источник: Bankiros.ru, проверено: 2026-07-02]</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>Более 1500 вкладов в 357 банках России | Выгодные вклады | Накопительные счета
+[источник: Bankiros.ru, проверено: 2026-07-02]</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>Более 1500 вкладов в 357 банках России | Выгодные вклады | Накопительные счета
+[источник: Bankiros.ru, проверено: 2026-07-02]</t>
         </is>
       </c>
     </row>
@@ -56934,24 +57588,28 @@
 [источник: Ручная проверка (первоисточник), проверено: 2026-07-02]</t>
         </is>
       </c>
-      <c r="F16" s="7" t="inlineStr">
-        <is>
-          <t>не найдено</t>
-        </is>
-      </c>
-      <c r="G16" s="7" t="inlineStr">
-        <is>
-          <t>не найдено</t>
-        </is>
-      </c>
-      <c r="H16" s="7" t="inlineStr">
-        <is>
-          <t>не найдено</t>
-        </is>
-      </c>
-      <c r="I16" s="7" t="inlineStr">
-        <is>
-          <t>не найдено</t>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>Онлайн-заявка на автокредит | Выгодные автокредиты | Легковые автомобили
+[источник: Bankiros.ru, проверено: 2026-07-02]</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>Онлайн-заявка на автокредит | Выгодные автокредиты | Легковые автомобили
+[источник: Bankiros.ru, проверено: 2026-07-02]</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>Онлайн-заявка на автокредит | Выгодные автокредиты | Легковые автомобили
+[источник: Bankiros.ru, проверено: 2026-07-02]</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>Онлайн-заявка на автокредит | Выгодные автокредиты | Легковые автомобили
+[источник: Bankiros.ru, проверено: 2026-07-02]</t>
         </is>
       </c>
     </row>
@@ -57236,44 +57894,52 @@
           <t>Дата последнего изменения условий</t>
         </is>
       </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>не найдено</t>
-        </is>
-      </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>не найдено</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>не найдено</t>
-        </is>
-      </c>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>не найдено</t>
-        </is>
-      </c>
-      <c r="F22" s="7" t="inlineStr">
-        <is>
-          <t>не найдено</t>
-        </is>
-      </c>
-      <c r="G22" s="7" t="inlineStr">
-        <is>
-          <t>не найдено</t>
-        </is>
-      </c>
-      <c r="H22" s="7" t="inlineStr">
-        <is>
-          <t>не найдено</t>
-        </is>
-      </c>
-      <c r="I22" s="7" t="inlineStr">
-        <is>
-          <t>не найдено</t>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Обновлено 02.07
+[источник: Bankiros.ru, проверено: 2026-07-02]</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>Обновлено 02.07
+[источник: Bankiros.ru, проверено: 2026-07-02]</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>Обновлено 02.07
+[источник: Bankiros.ru, проверено: 2026-07-02]</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>Обновлено 02.07
+[источник: Bankiros.ru, проверено: 2026-07-02]</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>Обновлено 02.07
+[источник: Bankiros.ru, проверено: 2026-07-02]</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>Обновлено 02.07
+[источник: Bankiros.ru, проверено: 2026-07-02]</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>Обновлено 02.07
+[источник: Bankiros.ru, проверено: 2026-07-02]</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>Обновлено 02.07
+[источник: Bankiros.ru, проверено: 2026-07-02]</t>
         </is>
       </c>
     </row>
